--- a/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
+++ b/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Users\amano\Documents\01_趣味\無線\アマチュア無線\◇1アマ対策\AmateurRadioOperator\AmateurFirstClassRadioOperatorExam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C472658-1513-4B14-A28A-67784D73E569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16180EF1-C361-40EF-9B41-FEA0152C85A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-7240" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5751,14 +5751,15 @@
         <v>11</v>
       </c>
       <c r="G5" s="18">
-        <v>6</v>
+        <f>G4+1</f>
+        <v>4</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>171</v>
       </c>
       <c r="I5" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K006</v>
+        <v>K004</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>6</v>
@@ -5798,14 +5799,15 @@
         <v>2</v>
       </c>
       <c r="G6" s="18">
-        <v>7</v>
+        <f t="shared" ref="G6:G69" si="7">G5+1</f>
+        <v>5</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>501</v>
       </c>
       <c r="I6" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K007</v>
+        <v>K005</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>6</v>
@@ -5848,24 +5850,25 @@
         <v>2</v>
       </c>
       <c r="G7" s="18">
-        <v>8</v>
+        <f t="shared" si="7"/>
+        <v>6</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>544</v>
       </c>
       <c r="I7" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K008</v>
+        <v>K006</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K7" s="2">
-        <f t="shared" ref="K7" si="7">COUNTA(P7:AS7)</f>
+        <f t="shared" ref="K7" si="8">COUNTA(P7:AS7)</f>
         <v>1</v>
       </c>
       <c r="L7" s="2">
-        <f t="shared" ref="L7" si="8">COUNTA(Q7:AT7)</f>
+        <f t="shared" ref="L7" si="9">COUNTA(Q7:AT7)</f>
         <v>1</v>
       </c>
       <c r="M7" s="2" cm="1">
@@ -5895,14 +5898,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="18">
-        <v>9</v>
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>503</v>
       </c>
       <c r="I8" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K009</v>
+        <v>K007</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>6</v>
@@ -5948,24 +5952,25 @@
         <v>2</v>
       </c>
       <c r="G9" s="18">
-        <v>10</v>
+        <f t="shared" si="7"/>
+        <v>8</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>532</v>
       </c>
       <c r="I9" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K010</v>
+        <v>K008</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K9" s="2">
-        <f t="shared" ref="K9" si="9">COUNTA(P9:AS9)</f>
+        <f t="shared" ref="K9" si="10">COUNTA(P9:AS9)</f>
         <v>1</v>
       </c>
       <c r="L9" s="2">
-        <f t="shared" ref="L9" si="10">COUNTA(Q9:AT9)</f>
+        <f t="shared" ref="L9" si="11">COUNTA(Q9:AT9)</f>
         <v>1</v>
       </c>
       <c r="M9" s="2" cm="1">
@@ -5995,14 +6000,15 @@
         <v>2</v>
       </c>
       <c r="G10" s="18">
-        <v>11</v>
+        <f t="shared" si="7"/>
+        <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>260</v>
       </c>
       <c r="I10" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K011</v>
+        <v>K009</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>6</v>
@@ -6045,24 +6051,25 @@
         <v>2</v>
       </c>
       <c r="G11" s="18">
-        <v>12</v>
+        <f t="shared" si="7"/>
+        <v>10</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>354</v>
       </c>
       <c r="I11" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K012</v>
+        <v>K010</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K11" s="2">
-        <f t="shared" ref="K11" si="11">COUNTA(P11:AS11)</f>
+        <f t="shared" ref="K11" si="12">COUNTA(P11:AS11)</f>
         <v>1</v>
       </c>
       <c r="L11" s="2">
-        <f t="shared" ref="L11" si="12">COUNTA(Q11:AT11)</f>
+        <f t="shared" ref="L11" si="13">COUNTA(Q11:AT11)</f>
         <v>1</v>
       </c>
       <c r="M11" s="2" cm="1">
@@ -6099,14 +6106,15 @@
         <v>11</v>
       </c>
       <c r="G12" s="18">
-        <v>13</v>
+        <f t="shared" si="7"/>
+        <v>11</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>97</v>
       </c>
       <c r="I12" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K013</v>
+        <v>K011</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>6</v>
@@ -6146,14 +6154,15 @@
         <v>2</v>
       </c>
       <c r="G13" s="18">
-        <v>14</v>
+        <f t="shared" si="7"/>
+        <v>12</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>117</v>
       </c>
       <c r="I13" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K014</v>
+        <v>K012</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>6</v>
@@ -6202,14 +6211,15 @@
         <v>2</v>
       </c>
       <c r="G14" s="18">
-        <v>15</v>
+        <f t="shared" si="7"/>
+        <v>13</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>208</v>
       </c>
       <c r="I14" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K015</v>
+        <v>K013</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>6</v>
@@ -6249,14 +6259,15 @@
         <v>2</v>
       </c>
       <c r="G15" s="18">
-        <v>16</v>
+        <f t="shared" si="7"/>
+        <v>14</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>306</v>
       </c>
       <c r="I15" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K016</v>
+        <v>K014</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>5</v>
@@ -6296,24 +6307,25 @@
         <v>2</v>
       </c>
       <c r="G16" s="18">
-        <v>17</v>
+        <f t="shared" si="7"/>
+        <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>453</v>
       </c>
       <c r="I16" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K017</v>
+        <v>K015</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K16" s="2">
-        <f t="shared" ref="K16:K18" si="13">COUNTA(P16:AS16)</f>
+        <f t="shared" ref="K16:K18" si="14">COUNTA(P16:AS16)</f>
         <v>4</v>
       </c>
       <c r="L16" s="2">
-        <f t="shared" ref="L16:L18" si="14">COUNTA(Q16:AT16)</f>
+        <f t="shared" ref="L16:L18" si="15">COUNTA(Q16:AT16)</f>
         <v>4</v>
       </c>
       <c r="M16" s="2" cm="1">
@@ -6359,24 +6371,25 @@
         <v>12</v>
       </c>
       <c r="G17" s="18">
-        <v>18</v>
+        <f t="shared" si="7"/>
+        <v>16</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>82</v>
       </c>
       <c r="I17" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K018</v>
+        <v>K016</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K17" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2</v>
       </c>
       <c r="L17" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="M17" s="2" cm="1">
@@ -6409,24 +6422,25 @@
         <v>2</v>
       </c>
       <c r="G18" s="18">
-        <v>19</v>
+        <f t="shared" si="7"/>
+        <v>17</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>584</v>
       </c>
       <c r="I18" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K019</v>
+        <v>K017</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K18" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="L18" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="M18" s="2" cm="1">
@@ -6456,24 +6470,25 @@
         <v>2</v>
       </c>
       <c r="G19" s="18">
-        <v>20</v>
+        <f t="shared" si="7"/>
+        <v>18</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>479</v>
       </c>
       <c r="I19" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K020</v>
+        <v>K018</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K19" s="2">
-        <f t="shared" ref="K19" si="15">COUNTA(P19:AS19)</f>
+        <f t="shared" ref="K19" si="16">COUNTA(P19:AS19)</f>
         <v>1</v>
       </c>
       <c r="L19" s="2">
-        <f t="shared" ref="L19" si="16">COUNTA(Q19:AT19)</f>
+        <f t="shared" ref="L19" si="17">COUNTA(Q19:AT19)</f>
         <v>1</v>
       </c>
       <c r="M19" s="2" cm="1">
@@ -6503,24 +6518,25 @@
         <v>2</v>
       </c>
       <c r="G20" s="18">
-        <v>21</v>
+        <f t="shared" si="7"/>
+        <v>19</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>524</v>
       </c>
       <c r="I20" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K021</v>
+        <v>K019</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K20" s="2">
-        <f t="shared" ref="K20" si="17">COUNTA(P20:AS20)</f>
+        <f t="shared" ref="K20" si="18">COUNTA(P20:AS20)</f>
         <v>1</v>
       </c>
       <c r="L20" s="2">
-        <f t="shared" ref="L20" si="18">COUNTA(Q20:AT20)</f>
+        <f t="shared" ref="L20" si="19">COUNTA(Q20:AT20)</f>
         <v>1</v>
       </c>
       <c r="M20" s="2" cm="1">
@@ -6550,24 +6566,25 @@
         <v>2</v>
       </c>
       <c r="G21" s="18">
-        <v>22</v>
+        <f t="shared" si="7"/>
+        <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="I21" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K022</v>
+        <v>K020</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K21" s="2">
-        <f t="shared" ref="K21:L27" si="19">COUNTA(P21:AS21)</f>
+        <f t="shared" ref="K21:L27" si="20">COUNTA(P21:AS21)</f>
         <v>5</v>
       </c>
       <c r="L21" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4</v>
       </c>
       <c r="M21" s="2" cm="1">
@@ -6609,24 +6626,25 @@
         <v>2</v>
       </c>
       <c r="G22" s="18">
-        <v>23</v>
+        <f t="shared" si="7"/>
+        <v>21</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>533</v>
       </c>
       <c r="I22" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K023</v>
+        <v>K021</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>81</v>
       </c>
       <c r="K22" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="L22" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="M22" s="2" cm="1">
@@ -6666,24 +6684,25 @@
         <v>5</v>
       </c>
       <c r="G23" s="18">
-        <v>24</v>
+        <f t="shared" si="7"/>
+        <v>22</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>53</v>
       </c>
       <c r="I23" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K024</v>
+        <v>K022</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K23" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="L23" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="M23" s="2" cm="1">
@@ -6716,24 +6735,25 @@
         <v>2</v>
       </c>
       <c r="G24" s="18">
-        <v>25</v>
+        <f t="shared" si="7"/>
+        <v>23</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>213</v>
       </c>
       <c r="I24" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K025</v>
+        <v>K023</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K24" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="L24" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="M24" s="2" cm="1">
@@ -6763,24 +6783,25 @@
         <v>2</v>
       </c>
       <c r="G25" s="18">
-        <v>26</v>
+        <f t="shared" si="7"/>
+        <v>24</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>352</v>
       </c>
       <c r="I25" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K026</v>
+        <v>K024</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K25" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="L25" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2</v>
       </c>
       <c r="M25" s="2" cm="1">
@@ -6820,24 +6841,25 @@
         <v>9</v>
       </c>
       <c r="G26" s="18">
-        <v>27</v>
+        <f t="shared" si="7"/>
+        <v>25</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>93</v>
       </c>
       <c r="I26" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K027</v>
+        <v>K025</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K26" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="L26" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="M26" s="2" cm="1">
@@ -6867,24 +6889,25 @@
         <v>92</v>
       </c>
       <c r="G27" s="18">
-        <v>28</v>
+        <f t="shared" si="7"/>
+        <v>26</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>77</v>
       </c>
       <c r="I27" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K028</v>
+        <v>K026</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K27" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3</v>
       </c>
       <c r="L27" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3</v>
       </c>
       <c r="M27" s="2" cm="1">
@@ -6920,24 +6943,25 @@
         <v>92</v>
       </c>
       <c r="G28" s="18">
-        <v>29</v>
+        <f t="shared" si="7"/>
+        <v>27</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>211</v>
       </c>
       <c r="I28" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K029</v>
+        <v>K027</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K28" s="2">
-        <f t="shared" ref="K28:K44" si="20">COUNTA(P28:AS28)</f>
+        <f t="shared" ref="K28:K44" si="21">COUNTA(P28:AS28)</f>
         <v>1</v>
       </c>
       <c r="L28" s="2">
-        <f t="shared" ref="L28:L44" si="21">COUNTA(Q28:AT28)</f>
+        <f t="shared" ref="L28:L44" si="22">COUNTA(Q28:AT28)</f>
         <v>1</v>
       </c>
       <c r="M28" s="2" cm="1">
@@ -6967,24 +6991,25 @@
         <v>92</v>
       </c>
       <c r="G29" s="18">
-        <v>30</v>
+        <f t="shared" si="7"/>
+        <v>28</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>177</v>
       </c>
       <c r="I29" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K030</v>
+        <v>K028</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K29" s="2">
-        <f t="shared" ref="K29:L31" si="22">COUNTA(P29:AS29)</f>
+        <f t="shared" ref="K29:L31" si="23">COUNTA(P29:AS29)</f>
         <v>2</v>
       </c>
       <c r="L29" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
       <c r="M29" s="2" cm="1">
@@ -7017,24 +7042,25 @@
         <v>92</v>
       </c>
       <c r="G30" s="18">
-        <v>31</v>
+        <f t="shared" si="7"/>
+        <v>29</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>366</v>
       </c>
       <c r="I30" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K031</v>
+        <v>K029</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K30" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
       <c r="L30" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>2</v>
       </c>
       <c r="M30" s="2" cm="1">
@@ -7067,24 +7093,25 @@
         <v>92</v>
       </c>
       <c r="G31" s="18">
-        <v>32</v>
+        <f t="shared" si="7"/>
+        <v>30</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>456</v>
       </c>
       <c r="I31" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K032</v>
+        <v>K030</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K31" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="L31" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="M31" s="2" cm="1">
@@ -7114,24 +7141,25 @@
         <v>92</v>
       </c>
       <c r="G32" s="18">
-        <v>33</v>
+        <f t="shared" si="7"/>
+        <v>31</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>504</v>
       </c>
       <c r="I32" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K033</v>
+        <v>K031</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K32" s="2">
-        <f t="shared" ref="K32" si="23">COUNTA(P32:AS32)</f>
+        <f t="shared" ref="K32" si="24">COUNTA(P32:AS32)</f>
         <v>1</v>
       </c>
       <c r="L32" s="2">
-        <f t="shared" ref="L32" si="24">COUNTA(Q32:AT32)</f>
+        <f t="shared" ref="L32" si="25">COUNTA(Q32:AT32)</f>
         <v>1</v>
       </c>
       <c r="M32" s="2" cm="1">
@@ -7161,24 +7189,25 @@
         <v>92</v>
       </c>
       <c r="G33" s="18">
-        <v>34</v>
+        <f t="shared" si="7"/>
+        <v>32</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>582</v>
       </c>
       <c r="I33" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K034</v>
+        <v>K032</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K33" s="2">
-        <f t="shared" ref="K33" si="25">COUNTA(P33:AS33)</f>
+        <f t="shared" ref="K33" si="26">COUNTA(P33:AS33)</f>
         <v>1</v>
       </c>
       <c r="L33" s="2">
-        <f t="shared" ref="L33" si="26">COUNTA(Q33:AT33)</f>
+        <f t="shared" ref="L33" si="27">COUNTA(Q33:AT33)</f>
         <v>1</v>
       </c>
       <c r="M33" s="2" cm="1">
@@ -7215,24 +7244,25 @@
         <v>5</v>
       </c>
       <c r="G34" s="18">
-        <v>35</v>
+        <f t="shared" si="7"/>
+        <v>33</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>174</v>
       </c>
       <c r="I34" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K035</v>
+        <v>K033</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K34" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="L34" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="M34" s="2" cm="1">
@@ -7265,24 +7295,25 @@
         <v>92</v>
       </c>
       <c r="G35" s="18">
-        <v>36</v>
+        <f t="shared" si="7"/>
+        <v>34</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>188</v>
       </c>
       <c r="I35" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K036</v>
+        <v>K034</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K35" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="L35" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="M35" s="2" cm="1">
@@ -7315,24 +7346,25 @@
         <v>92</v>
       </c>
       <c r="G36" s="18">
-        <v>37</v>
+        <f t="shared" si="7"/>
+        <v>35</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>398</v>
       </c>
       <c r="I36" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K037</v>
+        <v>K035</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K36" s="2">
-        <f t="shared" ref="K36" si="27">COUNTA(P36:AS36)</f>
+        <f t="shared" ref="K36" si="28">COUNTA(P36:AS36)</f>
         <v>1</v>
       </c>
       <c r="L36" s="2">
-        <f t="shared" ref="L36" si="28">COUNTA(Q36:AT36)</f>
+        <f t="shared" ref="L36" si="29">COUNTA(Q36:AT36)</f>
         <v>1</v>
       </c>
       <c r="M36" s="2" cm="1">
@@ -7369,24 +7401,25 @@
         <v>14</v>
       </c>
       <c r="G37" s="18">
-        <v>38</v>
+        <f t="shared" si="7"/>
+        <v>36</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>116</v>
       </c>
       <c r="I37" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K038</v>
+        <v>K036</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K37" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="L37" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
       <c r="M37" s="2" cm="1">
@@ -7425,24 +7458,25 @@
         <v>92</v>
       </c>
       <c r="G38" s="18">
-        <v>39</v>
+        <f t="shared" si="7"/>
+        <v>37</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>112</v>
       </c>
       <c r="I38" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K039</v>
+        <v>K037</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K38" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="L38" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3</v>
       </c>
       <c r="M38" s="2" cm="1">
@@ -7481,24 +7515,25 @@
         <v>92</v>
       </c>
       <c r="G39" s="18">
-        <v>40</v>
+        <f t="shared" si="7"/>
+        <v>38</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>173</v>
       </c>
       <c r="I39" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K040</v>
+        <v>K038</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K39" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="L39" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4</v>
       </c>
       <c r="M39" s="2" cm="1">
@@ -7537,24 +7572,25 @@
         <v>92</v>
       </c>
       <c r="G40" s="18">
-        <v>41</v>
+        <f t="shared" si="7"/>
+        <v>39</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>364</v>
       </c>
       <c r="I40" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K041</v>
+        <v>K039</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K40" s="2">
-        <f t="shared" ref="K40" si="29">COUNTA(P40:AS40)</f>
+        <f t="shared" ref="K40" si="30">COUNTA(P40:AS40)</f>
         <v>2</v>
       </c>
       <c r="L40" s="2">
-        <f t="shared" ref="L40" si="30">COUNTA(Q40:AT40)</f>
+        <f t="shared" ref="L40" si="31">COUNTA(Q40:AT40)</f>
         <v>2</v>
       </c>
       <c r="M40" s="2" cm="1">
@@ -7594,14 +7630,15 @@
         <v>4</v>
       </c>
       <c r="G41" s="18">
-        <v>42</v>
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>267</v>
       </c>
       <c r="I41" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K042</v>
+        <v>K040</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -7644,24 +7681,25 @@
         <v>92</v>
       </c>
       <c r="G42" s="18">
-        <v>43</v>
+        <f t="shared" si="7"/>
+        <v>41</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>437</v>
       </c>
       <c r="I42" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K043</v>
+        <v>K041</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K42" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="L42" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2</v>
       </c>
       <c r="M42" s="2" cm="1">
@@ -7694,14 +7732,15 @@
         <v>92</v>
       </c>
       <c r="G43" s="18">
-        <v>44</v>
+        <f t="shared" si="7"/>
+        <v>42</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>455</v>
       </c>
       <c r="I43" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K044</v>
+        <v>K042</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>6</v>
@@ -7754,24 +7793,25 @@
         <v>22</v>
       </c>
       <c r="G44" s="18">
-        <v>45</v>
+        <f t="shared" si="7"/>
+        <v>43</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>186</v>
       </c>
       <c r="I44" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K045</v>
+        <v>K043</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K44" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="L44" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="M44" s="2" cm="1">
@@ -7813,24 +7853,25 @@
         <v>89</v>
       </c>
       <c r="G45" s="18">
-        <v>46</v>
+        <f t="shared" si="7"/>
+        <v>44</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>553</v>
       </c>
       <c r="I45" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K046</v>
+        <v>K044</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K45" s="2">
-        <f t="shared" ref="K45" si="31">COUNTA(P45:AS45)</f>
+        <f t="shared" ref="K45" si="32">COUNTA(P45:AS45)</f>
         <v>2</v>
       </c>
       <c r="L45" s="2">
-        <f t="shared" ref="L45" si="32">COUNTA(Q45:AT45)</f>
+        <f t="shared" ref="L45" si="33">COUNTA(Q45:AT45)</f>
         <v>2</v>
       </c>
       <c r="M45" s="2" cm="1">
@@ -7863,24 +7904,25 @@
         <v>89</v>
       </c>
       <c r="G46" s="18">
-        <v>47</v>
+        <f t="shared" si="7"/>
+        <v>45</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>271</v>
       </c>
       <c r="I46" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K047</v>
+        <v>K045</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K46" s="2">
-        <f t="shared" ref="K46:K76" si="33">COUNTA(P46:AS46)</f>
+        <f t="shared" ref="K46:K76" si="34">COUNTA(P46:AS46)</f>
         <v>2</v>
       </c>
       <c r="L46" s="2">
-        <f t="shared" ref="L46:L76" si="34">COUNTA(Q46:AT46)</f>
+        <f t="shared" ref="L46:L76" si="35">COUNTA(Q46:AT46)</f>
         <v>2</v>
       </c>
       <c r="M46" s="2" cm="1">
@@ -7913,24 +7955,25 @@
         <v>89</v>
       </c>
       <c r="G47" s="18">
-        <v>48</v>
+        <f t="shared" si="7"/>
+        <v>46</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>583</v>
       </c>
       <c r="I47" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K048</v>
+        <v>K046</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K47" s="2">
-        <f t="shared" ref="K47" si="35">COUNTA(P47:AS47)</f>
+        <f t="shared" ref="K47" si="36">COUNTA(P47:AS47)</f>
         <v>1</v>
       </c>
       <c r="L47" s="2">
-        <f t="shared" ref="L47" si="36">COUNTA(Q47:AT47)</f>
+        <f t="shared" ref="L47" si="37">COUNTA(Q47:AT47)</f>
         <v>1</v>
       </c>
       <c r="M47" s="2" cm="1">
@@ -7960,24 +8003,25 @@
         <v>89</v>
       </c>
       <c r="G48" s="18">
-        <v>49</v>
+        <f t="shared" si="7"/>
+        <v>47</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>189</v>
       </c>
       <c r="I48" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K049</v>
+        <v>K047</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K48" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="L48" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
       <c r="M48" s="2" cm="1">
@@ -8010,24 +8054,25 @@
         <v>89</v>
       </c>
       <c r="G49" s="18">
-        <v>50</v>
+        <f t="shared" si="7"/>
+        <v>48</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>165</v>
       </c>
       <c r="I49" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K050</v>
+        <v>K048</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K49" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3</v>
       </c>
       <c r="L49" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
       <c r="M49" s="2" cm="1">
@@ -8063,24 +8108,25 @@
         <v>89</v>
       </c>
       <c r="G50" s="18">
-        <v>51</v>
+        <f t="shared" si="7"/>
+        <v>49</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>190</v>
       </c>
       <c r="I50" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K051</v>
+        <v>K049</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K50" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="L50" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
       <c r="M50" s="2" cm="1">
@@ -8116,24 +8162,25 @@
         <v>223</v>
       </c>
       <c r="G51" s="18">
-        <v>52</v>
+        <f t="shared" si="7"/>
+        <v>50</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I51" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K052</v>
+        <v>K050</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K51" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="L51" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M51" s="2" cm="1">
@@ -8163,24 +8210,25 @@
         <v>89</v>
       </c>
       <c r="G52" s="18">
-        <v>53</v>
+        <f t="shared" si="7"/>
+        <v>51</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>191</v>
       </c>
       <c r="I52" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K053</v>
+        <v>K051</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K52" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="L52" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
       <c r="M52" s="2" cm="1">
@@ -8213,14 +8261,15 @@
         <v>89</v>
       </c>
       <c r="G53" s="18">
-        <v>54</v>
+        <f t="shared" si="7"/>
+        <v>52</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>129</v>
       </c>
       <c r="I53" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K054</v>
+        <v>K052</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>6</v>
@@ -8263,14 +8312,15 @@
         <v>89</v>
       </c>
       <c r="G54" s="18">
-        <v>55</v>
+        <f t="shared" si="7"/>
+        <v>53</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>499</v>
       </c>
       <c r="I54" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K055</v>
+        <v>K053</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -8317,24 +8367,25 @@
         <v>7</v>
       </c>
       <c r="G55" s="18">
-        <v>56</v>
+        <f t="shared" si="7"/>
+        <v>54</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>96</v>
       </c>
       <c r="I55" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K056</v>
+        <v>K054</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K55" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3</v>
       </c>
       <c r="L55" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3</v>
       </c>
       <c r="M55" s="2" cm="1">
@@ -8370,24 +8421,25 @@
         <v>89</v>
       </c>
       <c r="G56" s="18">
-        <v>57</v>
+        <f t="shared" si="7"/>
+        <v>55</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>125</v>
       </c>
       <c r="I56" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K057</v>
+        <v>K055</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K56" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="L56" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M56" s="2" cm="1">
@@ -8420,24 +8472,25 @@
         <v>89</v>
       </c>
       <c r="G57" s="18">
-        <v>58</v>
+        <f t="shared" si="7"/>
+        <v>56</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>555</v>
       </c>
       <c r="I57" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K058</v>
+        <v>K056</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K57" s="2">
-        <f t="shared" ref="K57" si="37">COUNTA(P57:AS57)</f>
+        <f t="shared" ref="K57" si="38">COUNTA(P57:AS57)</f>
         <v>1</v>
       </c>
       <c r="L57" s="2">
-        <f t="shared" ref="L57" si="38">COUNTA(Q57:AT57)</f>
+        <f t="shared" ref="L57" si="39">COUNTA(Q57:AT57)</f>
         <v>1</v>
       </c>
       <c r="M57" s="2" cm="1">
@@ -8467,24 +8520,25 @@
         <v>89</v>
       </c>
       <c r="G58" s="18">
-        <v>59</v>
+        <f t="shared" si="7"/>
+        <v>57</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>226</v>
       </c>
       <c r="I58" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K059</v>
+        <v>K057</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K58" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="L58" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M58" s="2" cm="1">
@@ -8521,24 +8575,25 @@
         <v>11</v>
       </c>
       <c r="G59" s="18">
-        <v>60</v>
+        <f t="shared" si="7"/>
+        <v>58</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>175</v>
       </c>
       <c r="I59" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K060</v>
+        <v>K058</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K59" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="L59" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M59" s="2" cm="1">
@@ -8568,24 +8623,25 @@
         <v>74</v>
       </c>
       <c r="G60" s="18">
-        <v>61</v>
+        <f t="shared" si="7"/>
+        <v>59</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>215</v>
       </c>
       <c r="I60" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K061</v>
+        <v>K059</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K60" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="L60" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
       <c r="M60" s="2" cm="1">
@@ -8618,24 +8674,25 @@
         <v>74</v>
       </c>
       <c r="G61" s="18">
-        <v>62</v>
+        <f t="shared" si="7"/>
+        <v>60</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>447</v>
       </c>
       <c r="I61" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K062</v>
+        <v>K060</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K61" s="2">
-        <f t="shared" ref="K61" si="39">COUNTA(P61:AS61)</f>
+        <f t="shared" ref="K61" si="40">COUNTA(P61:AS61)</f>
         <v>2</v>
       </c>
       <c r="L61" s="2">
-        <f t="shared" ref="L61" si="40">COUNTA(Q61:AT61)</f>
+        <f t="shared" ref="L61" si="41">COUNTA(Q61:AT61)</f>
         <v>2</v>
       </c>
       <c r="M61" s="2" cm="1">
@@ -8668,24 +8725,25 @@
         <v>74</v>
       </c>
       <c r="G62" s="18">
-        <v>63</v>
+        <f t="shared" si="7"/>
+        <v>61</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>448</v>
       </c>
       <c r="I62" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K063</v>
+        <v>K061</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K62" s="2">
-        <f t="shared" ref="K62" si="41">COUNTA(P62:AS62)</f>
+        <f t="shared" ref="K62" si="42">COUNTA(P62:AS62)</f>
         <v>1</v>
       </c>
       <c r="L62" s="2">
-        <f t="shared" ref="L62" si="42">COUNTA(Q62:AT62)</f>
+        <f t="shared" ref="L62" si="43">COUNTA(Q62:AT62)</f>
         <v>1</v>
       </c>
       <c r="M62" s="2" cm="1">
@@ -8715,24 +8773,25 @@
         <v>74</v>
       </c>
       <c r="G63" s="18">
-        <v>64</v>
+        <f t="shared" si="7"/>
+        <v>62</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>319</v>
       </c>
       <c r="I63" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K064</v>
+        <v>K062</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K63" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="L63" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M63" s="2" cm="1">
@@ -8762,24 +8821,25 @@
         <v>74</v>
       </c>
       <c r="G64" s="18">
-        <v>65</v>
+        <f t="shared" si="7"/>
+        <v>63</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>172</v>
       </c>
       <c r="I64" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>K065</v>
+        <v>K063</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K64" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="L64" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M64" s="2" cm="1">
@@ -8809,24 +8869,25 @@
         <v>74</v>
       </c>
       <c r="G65" s="18">
-        <v>66</v>
+        <f t="shared" si="7"/>
+        <v>64</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>110</v>
       </c>
       <c r="I65" s="1" t="str">
-        <f t="shared" ref="I65:I79" si="43">B65&amp;TEXT(G65,"000")</f>
-        <v>K066</v>
+        <f t="shared" ref="I65:I79" si="44">B65&amp;TEXT(G65,"000")</f>
+        <v>K064</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K65" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3</v>
       </c>
       <c r="L65" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
       <c r="M65" s="2" cm="1">
@@ -8834,11 +8895,11 @@
         <v>0</v>
       </c>
       <c r="N65" s="11">
-        <f t="shared" ref="N65:N128" si="44">COUNTA(Q65:AB65)/COUNTA($Q$1:$AB$1)*100</f>
+        <f t="shared" ref="N65:N128" si="45">COUNTA(Q65:AB65)/COUNTA($Q$1:$AB$1)*100</f>
         <v>8.3333333333333321</v>
       </c>
       <c r="O65" s="11" t="str">
-        <f t="shared" ref="O65:O128" si="45">IF(N65&gt;=33,"★★★★★",IF(N65&gt;=25,"★★★★",IF(N65&gt;=15,"★★★",IF(N65&gt;=5,"★★","★"))))</f>
+        <f t="shared" ref="O65:O128" si="46">IF(N65&gt;=33,"★★★★★",IF(N65&gt;=25,"★★★★",IF(N65&gt;=15,"★★★",IF(N65&gt;=5,"★★","★"))))</f>
         <v>★★</v>
       </c>
       <c r="P65" s="1" t="s">
@@ -8869,24 +8930,25 @@
         <v>19</v>
       </c>
       <c r="G66" s="18">
-        <v>67</v>
+        <f t="shared" si="7"/>
+        <v>65</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>94</v>
       </c>
       <c r="I66" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K067</v>
+        <f t="shared" si="44"/>
+        <v>K065</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K66" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="L66" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2</v>
       </c>
       <c r="M66" s="2" cm="1">
@@ -8894,11 +8956,11 @@
         <v>1</v>
       </c>
       <c r="N66" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O66" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="Q66" s="1" t="s">
@@ -8919,36 +8981,37 @@
         <v>74</v>
       </c>
       <c r="G67" s="18">
-        <v>68</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>363</v>
       </c>
       <c r="I67" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K068</v>
+        <f t="shared" si="44"/>
+        <v>K066</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K67" s="2">
-        <f t="shared" si="33"/>
-        <v>9</v>
-      </c>
-      <c r="L67" s="2">
         <f t="shared" si="34"/>
         <v>9</v>
       </c>
+      <c r="L67" s="2">
+        <f t="shared" si="35"/>
+        <v>9</v>
+      </c>
       <c r="M67" s="2" cm="1">
         <f t="array" ref="M67">MATCH(TRUE,P67:AD67&lt;&gt;"",0)-1</f>
         <v>2</v>
       </c>
       <c r="N67" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>75</v>
       </c>
       <c r="O67" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★★★</v>
       </c>
       <c r="R67" s="1" t="s">
@@ -8990,24 +9053,25 @@
         <v>74</v>
       </c>
       <c r="G68" s="18">
-        <v>69</v>
+        <f t="shared" si="7"/>
+        <v>67</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>78</v>
       </c>
       <c r="I68" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K069</v>
+        <f t="shared" si="44"/>
+        <v>K067</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K68" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4</v>
       </c>
       <c r="L68" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>4</v>
       </c>
       <c r="M68" s="2" cm="1">
@@ -9015,11 +9079,11 @@
         <v>3</v>
       </c>
       <c r="N68" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>25</v>
       </c>
       <c r="O68" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★★</v>
       </c>
       <c r="S68" s="1" t="s">
@@ -9046,24 +9110,25 @@
         <v>74</v>
       </c>
       <c r="G69" s="18">
-        <v>70</v>
+        <f t="shared" si="7"/>
+        <v>68</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>122</v>
       </c>
       <c r="I69" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K070</v>
+        <f t="shared" si="44"/>
+        <v>K068</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K69" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="L69" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M69" s="2" cm="1">
@@ -9071,11 +9136,11 @@
         <v>0</v>
       </c>
       <c r="N69" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O69" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="P69" s="1" t="s">
@@ -9096,24 +9161,25 @@
         <v>74</v>
       </c>
       <c r="G70" s="18">
-        <v>71</v>
+        <f t="shared" ref="G70:G79" si="47">G69+1</f>
+        <v>69</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>120</v>
       </c>
       <c r="I70" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K071</v>
+        <f t="shared" si="44"/>
+        <v>K069</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K70" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="L70" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M70" s="2" cm="1">
@@ -9121,11 +9187,11 @@
         <v>0</v>
       </c>
       <c r="N70" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="O70" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★</v>
       </c>
       <c r="P70" s="1" t="s">
@@ -9143,24 +9209,25 @@
         <v>74</v>
       </c>
       <c r="G71" s="18">
-        <v>72</v>
+        <f t="shared" si="47"/>
+        <v>70</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>269</v>
       </c>
       <c r="I71" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K072</v>
+        <f t="shared" si="44"/>
+        <v>K070</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K71" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="L71" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M71" s="2" cm="1">
@@ -9168,11 +9235,11 @@
         <v>5</v>
       </c>
       <c r="N71" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O71" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="U71" s="1" t="s">
@@ -9190,24 +9257,25 @@
         <v>74</v>
       </c>
       <c r="G72" s="18">
-        <v>73</v>
+        <f t="shared" si="47"/>
+        <v>71</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>534</v>
       </c>
       <c r="I72" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K073</v>
+        <f t="shared" si="44"/>
+        <v>K071</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K72" s="2">
-        <f t="shared" ref="K72" si="46">COUNTA(P72:AS72)</f>
+        <f t="shared" ref="K72" si="48">COUNTA(P72:AS72)</f>
         <v>1</v>
       </c>
       <c r="L72" s="2">
-        <f t="shared" ref="L72" si="47">COUNTA(Q72:AT72)</f>
+        <f t="shared" ref="L72" si="49">COUNTA(Q72:AT72)</f>
         <v>1</v>
       </c>
       <c r="M72" s="2" cm="1">
@@ -9215,11 +9283,11 @@
         <v>11</v>
       </c>
       <c r="N72" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O72" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="AA72" s="1" t="s">
@@ -9244,36 +9312,37 @@
         <v>9</v>
       </c>
       <c r="G73" s="18">
-        <v>74</v>
+        <f t="shared" si="47"/>
+        <v>72</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>551</v>
       </c>
       <c r="I73" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K074</v>
+        <f t="shared" si="44"/>
+        <v>K072</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K73" s="2">
-        <f t="shared" si="33"/>
-        <v>3</v>
-      </c>
-      <c r="L73" s="2">
         <f t="shared" si="34"/>
         <v>3</v>
       </c>
+      <c r="L73" s="2">
+        <f t="shared" si="35"/>
+        <v>3</v>
+      </c>
       <c r="M73" s="2" cm="1">
         <f t="array" ref="M73">MATCH(TRUE,P73:AD73&lt;&gt;"",0)-1</f>
         <v>2</v>
       </c>
       <c r="N73" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>25</v>
       </c>
       <c r="O73" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★★</v>
       </c>
       <c r="R73" s="1" t="s">
@@ -9297,36 +9366,37 @@
         <v>74</v>
       </c>
       <c r="G74" s="18">
-        <v>75</v>
+        <f t="shared" si="47"/>
+        <v>73</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>192</v>
       </c>
       <c r="I74" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K075</v>
+        <f t="shared" si="44"/>
+        <v>K073</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K74" s="2">
-        <f t="shared" si="33"/>
-        <v>3</v>
-      </c>
-      <c r="L74" s="2">
         <f t="shared" si="34"/>
         <v>3</v>
       </c>
+      <c r="L74" s="2">
+        <f t="shared" si="35"/>
+        <v>3</v>
+      </c>
       <c r="M74" s="2" cm="1">
         <f t="array" ref="M74">MATCH(TRUE,P74:AD74&lt;&gt;"",0)-1</f>
         <v>1</v>
       </c>
       <c r="N74" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>25</v>
       </c>
       <c r="O74" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★★</v>
       </c>
       <c r="Q74" s="1" t="s">
@@ -9350,24 +9420,25 @@
         <v>74</v>
       </c>
       <c r="G75" s="18">
-        <v>76</v>
+        <f t="shared" si="47"/>
+        <v>74</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>442</v>
       </c>
       <c r="I75" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K076</v>
+        <f t="shared" si="44"/>
+        <v>K074</v>
       </c>
       <c r="J75" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K75" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="L75" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M75" s="2" cm="1">
@@ -9375,11 +9446,11 @@
         <v>9</v>
       </c>
       <c r="N75" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O75" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="Y75" s="1" t="s">
@@ -9397,24 +9468,25 @@
         <v>74</v>
       </c>
       <c r="G76" s="18">
-        <v>77</v>
+        <f t="shared" si="47"/>
+        <v>75</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>307</v>
       </c>
       <c r="I76" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K077</v>
+        <f t="shared" si="44"/>
+        <v>K075</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K76" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="L76" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1</v>
       </c>
       <c r="M76" s="2" cm="1">
@@ -9422,11 +9494,11 @@
         <v>5</v>
       </c>
       <c r="N76" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O76" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="U76" s="1" t="s">
@@ -9444,24 +9516,25 @@
         <v>74</v>
       </c>
       <c r="G77" s="18">
-        <v>78</v>
+        <f t="shared" si="47"/>
+        <v>76</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>526</v>
       </c>
       <c r="I77" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K078</v>
+        <f t="shared" si="44"/>
+        <v>K076</v>
       </c>
       <c r="J77" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K77" s="2">
-        <f t="shared" ref="K77:K78" si="48">COUNTA(P77:AS77)</f>
+        <f t="shared" ref="K77:K78" si="50">COUNTA(P77:AS77)</f>
         <v>1</v>
       </c>
       <c r="L77" s="2">
-        <f t="shared" ref="L77:L78" si="49">COUNTA(Q77:AT77)</f>
+        <f t="shared" ref="L77:L78" si="51">COUNTA(Q77:AT77)</f>
         <v>1</v>
       </c>
       <c r="M77" s="2" cm="1">
@@ -9469,11 +9542,11 @@
         <v>10</v>
       </c>
       <c r="N77" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O77" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="Z77" s="1" t="s">
@@ -9498,24 +9571,25 @@
         <v>3</v>
       </c>
       <c r="G78" s="18">
-        <v>79</v>
+        <f t="shared" si="47"/>
+        <v>77</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>176</v>
       </c>
       <c r="I78" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K079</v>
+        <f t="shared" si="44"/>
+        <v>K077</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K78" s="2">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="L78" s="2">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
       <c r="M78" s="2" cm="1">
@@ -9523,11 +9597,11 @@
         <v>2</v>
       </c>
       <c r="N78" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O78" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="R78" s="1" t="s">
@@ -9545,24 +9619,25 @@
         <v>74</v>
       </c>
       <c r="G79" s="18">
-        <v>80</v>
+        <f t="shared" si="47"/>
+        <v>78</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>356</v>
       </c>
       <c r="I79" s="1" t="str">
-        <f t="shared" si="43"/>
-        <v>K080</v>
+        <f t="shared" si="44"/>
+        <v>K078</v>
       </c>
       <c r="J79" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K79" s="2">
-        <f t="shared" ref="K79" si="50">COUNTA(P79:AS79)</f>
+        <f t="shared" ref="K79" si="52">COUNTA(P79:AS79)</f>
         <v>2</v>
       </c>
       <c r="L79" s="2">
-        <f t="shared" ref="L79" si="51">COUNTA(Q79:AT79)</f>
+        <f t="shared" ref="L79" si="53">COUNTA(Q79:AT79)</f>
         <v>2</v>
       </c>
       <c r="M79" s="2" cm="1">
@@ -9570,11 +9645,11 @@
         <v>7</v>
       </c>
       <c r="N79" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O79" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="W79" s="1" t="s">
@@ -9612,11 +9687,11 @@
         <v>81</v>
       </c>
       <c r="K80" s="2">
-        <f t="shared" ref="K80:K97" si="52">COUNTA(P80:AS80)</f>
+        <f t="shared" ref="K80:K97" si="54">COUNTA(P80:AS80)</f>
         <v>7</v>
       </c>
       <c r="L80" s="2">
-        <f t="shared" ref="L80:L97" si="53">COUNTA(Q80:AT80)</f>
+        <f t="shared" ref="L80:L97" si="55">COUNTA(Q80:AT80)</f>
         <v>6</v>
       </c>
       <c r="M80" s="2" cm="1">
@@ -9624,11 +9699,11 @@
         <v>0</v>
       </c>
       <c r="N80" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>41.666666666666671</v>
       </c>
       <c r="O80" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★★★</v>
       </c>
       <c r="P80" s="1" t="s">
@@ -9671,18 +9746,18 @@
         <v>98</v>
       </c>
       <c r="I81" s="1" t="str">
-        <f t="shared" ref="I81:I144" si="54">B81&amp;TEXT(G81,"000")</f>
+        <f t="shared" ref="I81:I144" si="56">B81&amp;TEXT(G81,"000")</f>
         <v>A002</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K81" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>2</v>
       </c>
       <c r="L81" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="M81" s="2" cm="1">
@@ -9690,11 +9765,11 @@
         <v>1</v>
       </c>
       <c r="N81" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O81" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="Q81" s="1" t="s">
@@ -9715,25 +9790,25 @@
         <v>435</v>
       </c>
       <c r="G82" s="18">
-        <f t="shared" ref="G82:G90" si="55">G81+1</f>
+        <f t="shared" ref="G82:G90" si="57">G81+1</f>
         <v>3</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>80</v>
       </c>
       <c r="I82" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A003</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K82" s="2">
         <f t="shared" si="54"/>
-        <v>A003</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K82" s="2">
-        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="L82" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="M82" s="2" cm="1">
@@ -9741,11 +9816,11 @@
         <v>3</v>
       </c>
       <c r="N82" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O82" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="S82" s="1" t="s">
@@ -9763,25 +9838,25 @@
         <v>435</v>
       </c>
       <c r="G83" s="18">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>4</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>370</v>
       </c>
       <c r="I83" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A004</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K83" s="2">
-        <f t="shared" ref="K83:K84" si="56">COUNTA(P83:AS83)</f>
+        <f t="shared" ref="K83:K84" si="58">COUNTA(P83:AS83)</f>
         <v>1</v>
       </c>
       <c r="L83" s="2">
-        <f t="shared" ref="L83:L84" si="57">COUNTA(Q83:AT83)</f>
+        <f t="shared" ref="L83:L84" si="59">COUNTA(Q83:AT83)</f>
         <v>1</v>
       </c>
       <c r="M83" s="2" cm="1">
@@ -9789,11 +9864,11 @@
         <v>7</v>
       </c>
       <c r="N83" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O83" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="W83" s="1" t="s">
@@ -9811,25 +9886,25 @@
         <v>435</v>
       </c>
       <c r="G84" s="18">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>5</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>279</v>
       </c>
       <c r="I84" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A005</v>
       </c>
       <c r="J84" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K84" s="2">
-        <f t="shared" si="56"/>
+        <f t="shared" si="58"/>
         <v>4</v>
       </c>
       <c r="L84" s="2">
-        <f t="shared" si="57"/>
+        <f t="shared" si="59"/>
         <v>3</v>
       </c>
       <c r="M84" s="2" cm="1">
@@ -9837,11 +9912,11 @@
         <v>0</v>
       </c>
       <c r="N84" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O84" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="P84" s="1" t="s">
@@ -9868,25 +9943,25 @@
         <v>435</v>
       </c>
       <c r="G85" s="18">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>6</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>557</v>
       </c>
       <c r="I85" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A006</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K85" s="2">
         <f t="shared" si="54"/>
-        <v>A006</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K85" s="2">
-        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="L85" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="M85" s="2" cm="1">
@@ -9894,11 +9969,11 @@
         <v>12</v>
       </c>
       <c r="N85" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O85" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="AB85" s="1" t="s">
@@ -9920,25 +9995,25 @@
         <v>8</v>
       </c>
       <c r="G86" s="18">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>7</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>275</v>
       </c>
       <c r="I86" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A007</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K86" s="2">
         <f t="shared" si="54"/>
-        <v>A007</v>
-      </c>
-      <c r="J86" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K86" s="2">
-        <f t="shared" si="52"/>
         <v>2</v>
       </c>
       <c r="L86" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="M86" s="2" cm="1">
@@ -9946,11 +10021,11 @@
         <v>1</v>
       </c>
       <c r="N86" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O86" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="Q86" s="1" t="s">
@@ -9971,25 +10046,25 @@
         <v>62</v>
       </c>
       <c r="G87" s="18">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>8</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>276</v>
       </c>
       <c r="I87" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A008</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K87" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="54"/>
         <v>2</v>
       </c>
       <c r="L87" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="M87" s="2" cm="1">
@@ -9997,11 +10072,11 @@
         <v>5</v>
       </c>
       <c r="N87" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O87" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="U87" s="1" t="s">
@@ -10022,25 +10097,25 @@
         <v>62</v>
       </c>
       <c r="G88" s="18">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>9</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>179</v>
       </c>
       <c r="I88" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A009</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K88" s="2">
         <f t="shared" si="54"/>
-        <v>A009</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K88" s="2">
-        <f t="shared" si="52"/>
         <v>2</v>
       </c>
       <c r="L88" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="M88" s="2" cm="1">
@@ -10048,11 +10123,11 @@
         <v>2</v>
       </c>
       <c r="N88" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O88" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="R88" s="1" t="s">
@@ -10073,25 +10148,25 @@
         <v>62</v>
       </c>
       <c r="G89" s="18">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>10</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>193</v>
       </c>
       <c r="I89" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A010</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="2">
         <f t="shared" si="54"/>
-        <v>A010</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="2">
-        <f t="shared" si="52"/>
         <v>2</v>
       </c>
       <c r="L89" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="M89" s="2" cm="1">
@@ -10099,11 +10174,11 @@
         <v>3</v>
       </c>
       <c r="N89" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O89" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="S89" s="1" t="s">
@@ -10131,25 +10206,25 @@
         <v>8</v>
       </c>
       <c r="G90" s="18">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>11</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>108</v>
       </c>
       <c r="I90" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A011</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K90" s="2">
         <f t="shared" si="54"/>
-        <v>A011</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K90" s="2">
-        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="L90" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="M90" s="2" cm="1">
@@ -10157,11 +10232,11 @@
         <v>1</v>
       </c>
       <c r="N90" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O90" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="Q90" s="1" t="s">
@@ -10185,18 +10260,18 @@
         <v>180</v>
       </c>
       <c r="I91" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A012</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K91" s="2">
         <f t="shared" si="54"/>
-        <v>A012</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K91" s="2">
-        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="L91" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="M91" s="2" cm="1">
@@ -10204,11 +10279,11 @@
         <v>2</v>
       </c>
       <c r="N91" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O91" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="R91" s="1" t="s">
@@ -10232,18 +10307,18 @@
         <v>137</v>
       </c>
       <c r="I92" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A013</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K92" s="2">
         <f t="shared" si="54"/>
-        <v>A013</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K92" s="2">
-        <f t="shared" si="52"/>
         <v>2</v>
       </c>
       <c r="L92" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>1</v>
       </c>
       <c r="M92" s="2" cm="1">
@@ -10251,11 +10326,11 @@
         <v>0</v>
       </c>
       <c r="N92" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O92" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="P92" s="1" t="s">
@@ -10282,18 +10357,18 @@
         <v>247</v>
       </c>
       <c r="I93" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A014</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K93" s="2">
         <f t="shared" si="54"/>
-        <v>A014</v>
-      </c>
-      <c r="J93" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K93" s="2">
-        <f t="shared" si="52"/>
         <v>3</v>
       </c>
       <c r="L93" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>3</v>
       </c>
       <c r="M93" s="2" cm="1">
@@ -10301,11 +10376,11 @@
         <v>4</v>
       </c>
       <c r="N93" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>25</v>
       </c>
       <c r="O93" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★★</v>
       </c>
       <c r="T93" s="1" t="s">
@@ -10335,18 +10410,18 @@
         <v>407</v>
       </c>
       <c r="I94" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A015</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K94" s="2">
-        <f t="shared" ref="K94" si="58">COUNTA(P94:AS94)</f>
+        <f t="shared" ref="K94" si="60">COUNTA(P94:AS94)</f>
         <v>1</v>
       </c>
       <c r="L94" s="2">
-        <f t="shared" ref="L94" si="59">COUNTA(Q94:AT94)</f>
+        <f t="shared" ref="L94" si="61">COUNTA(Q94:AT94)</f>
         <v>1</v>
       </c>
       <c r="M94" s="2" cm="1">
@@ -10354,11 +10429,11 @@
         <v>8</v>
       </c>
       <c r="N94" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O94" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="X94" s="1" t="s">
@@ -10386,18 +10461,18 @@
         <v>133</v>
       </c>
       <c r="I95" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A016</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K95" s="2">
         <f t="shared" si="54"/>
-        <v>A016</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K95" s="2">
-        <f t="shared" si="52"/>
         <v>2</v>
       </c>
       <c r="L95" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="M95" s="2" cm="1">
@@ -10405,11 +10480,11 @@
         <v>1</v>
       </c>
       <c r="N95" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O95" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="Q95" s="1" t="s">
@@ -10436,18 +10511,18 @@
         <v>134</v>
       </c>
       <c r="I96" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A017</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="2">
         <f t="shared" si="54"/>
-        <v>A017</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="2">
-        <f t="shared" si="52"/>
         <v>1</v>
       </c>
       <c r="L96" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="M96" s="2" cm="1">
@@ -10455,11 +10530,11 @@
         <v>0</v>
       </c>
       <c r="N96" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="O96" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★</v>
       </c>
       <c r="P96" s="1" t="s">
@@ -10483,18 +10558,18 @@
         <v>68</v>
       </c>
       <c r="I97" s="1" t="str">
+        <f t="shared" si="56"/>
+        <v>A018</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K97" s="2">
         <f t="shared" si="54"/>
-        <v>A018</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K97" s="2">
-        <f t="shared" si="52"/>
         <v>2</v>
       </c>
       <c r="L97" s="2">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>2</v>
       </c>
       <c r="M97" s="2" cm="1">
@@ -10502,11 +10577,11 @@
         <v>2</v>
       </c>
       <c r="N97" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O97" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="R97" s="1" t="s">
@@ -10533,18 +10608,18 @@
         <v>308</v>
       </c>
       <c r="I98" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A019</v>
       </c>
       <c r="J98" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K98" s="2">
-        <f t="shared" ref="K98" si="60">COUNTA(P98:AS98)</f>
+        <f t="shared" ref="K98" si="62">COUNTA(P98:AS98)</f>
         <v>1</v>
       </c>
       <c r="L98" s="2">
-        <f t="shared" ref="L98" si="61">COUNTA(Q98:AT98)</f>
+        <f t="shared" ref="L98" si="63">COUNTA(Q98:AT98)</f>
         <v>1</v>
       </c>
       <c r="M98" s="2" cm="1">
@@ -10552,11 +10627,11 @@
         <v>5</v>
       </c>
       <c r="N98" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O98" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="U98" s="1" t="s">
@@ -10580,18 +10655,18 @@
         <v>277</v>
       </c>
       <c r="I99" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A020</v>
       </c>
       <c r="J99" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K99" s="2">
-        <f t="shared" ref="K99:L104" si="62">COUNTA(P99:AS99)</f>
+        <f t="shared" ref="K99:L104" si="64">COUNTA(P99:AS99)</f>
         <v>2</v>
       </c>
       <c r="L99" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>2</v>
       </c>
       <c r="M99" s="2" cm="1">
@@ -10599,11 +10674,11 @@
         <v>5</v>
       </c>
       <c r="N99" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O99" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="U99" s="1" t="s">
@@ -10630,18 +10705,18 @@
         <v>195</v>
       </c>
       <c r="I100" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A021</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K100" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="L100" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="M100" s="2" cm="1">
@@ -10649,11 +10724,11 @@
         <v>3</v>
       </c>
       <c r="N100" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O100" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="S100" s="1" t="s">
@@ -10677,18 +10752,18 @@
         <v>231</v>
       </c>
       <c r="I101" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A022</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K101" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>2</v>
       </c>
       <c r="L101" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>2</v>
       </c>
       <c r="M101" s="2" cm="1">
@@ -10696,11 +10771,11 @@
         <v>4</v>
       </c>
       <c r="N101" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O101" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="T101" s="1" t="s">
@@ -10727,18 +10802,18 @@
         <v>431</v>
       </c>
       <c r="I102" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A023</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K102" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>2</v>
       </c>
       <c r="L102" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>2</v>
       </c>
       <c r="M102" s="2" cm="1">
@@ -10746,11 +10821,11 @@
         <v>3</v>
       </c>
       <c r="N102" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O102" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="S102" s="1" t="s">
@@ -10777,18 +10852,18 @@
         <v>432</v>
       </c>
       <c r="I103" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A024</v>
       </c>
       <c r="J103" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K103" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>2</v>
       </c>
       <c r="L103" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="M103" s="2" cm="1">
@@ -10796,11 +10871,11 @@
         <v>0</v>
       </c>
       <c r="N103" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O103" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="P103" s="1" t="s">
@@ -10827,18 +10902,18 @@
         <v>433</v>
       </c>
       <c r="I104" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A025</v>
       </c>
       <c r="J104" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K104" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="L104" s="2">
-        <f t="shared" si="62"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="M104" s="2" cm="1">
@@ -10846,11 +10921,11 @@
         <v>6</v>
       </c>
       <c r="N104" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O104" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="V104" s="1" t="s">
@@ -10874,18 +10949,18 @@
         <v>434</v>
       </c>
       <c r="I105" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A026</v>
       </c>
       <c r="J105" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K105" s="2">
-        <f t="shared" ref="K105" si="63">COUNTA(P105:AS105)</f>
+        <f t="shared" ref="K105" si="65">COUNTA(P105:AS105)</f>
         <v>2</v>
       </c>
       <c r="L105" s="2">
-        <f t="shared" ref="L105" si="64">COUNTA(Q105:AT105)</f>
+        <f t="shared" ref="L105" si="66">COUNTA(Q105:AT105)</f>
         <v>2</v>
       </c>
       <c r="M105" s="2" cm="1">
@@ -10893,11 +10968,11 @@
         <v>7</v>
       </c>
       <c r="N105" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O105" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="W105" s="1" t="s">
@@ -10931,7 +11006,7 @@
         <v>99</v>
       </c>
       <c r="I106" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A027</v>
       </c>
       <c r="J106" s="3" t="s">
@@ -10950,11 +11025,11 @@
         <v>1</v>
       </c>
       <c r="N106" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>25</v>
       </c>
       <c r="O106" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★★</v>
       </c>
       <c r="Q106" s="1" t="s">
@@ -10984,18 +11059,18 @@
         <v>196</v>
       </c>
       <c r="I107" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A028</v>
       </c>
       <c r="J107" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K107" s="2">
-        <f t="shared" ref="K107:K155" si="65">COUNTA(P107:AS107)</f>
+        <f t="shared" ref="K107:K155" si="67">COUNTA(P107:AS107)</f>
         <v>2</v>
       </c>
       <c r="L107" s="2">
-        <f t="shared" ref="L107:L155" si="66">COUNTA(Q107:AT107)</f>
+        <f t="shared" ref="L107:L155" si="68">COUNTA(Q107:AT107)</f>
         <v>2</v>
       </c>
       <c r="M107" s="2" cm="1">
@@ -11003,11 +11078,11 @@
         <v>3</v>
       </c>
       <c r="N107" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O107" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="S107" s="1" t="s">
@@ -11034,18 +11109,18 @@
         <v>461</v>
       </c>
       <c r="I108" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A029</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K108" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="L108" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M108" s="2" cm="1">
@@ -11053,11 +11128,11 @@
         <v>9</v>
       </c>
       <c r="N108" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O108" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="Y108" s="1" t="s">
@@ -11081,18 +11156,18 @@
         <v>507</v>
       </c>
       <c r="I109" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A030</v>
       </c>
       <c r="J109" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K109" s="2">
-        <f t="shared" ref="K109" si="67">COUNTA(P109:AS109)</f>
+        <f t="shared" ref="K109" si="69">COUNTA(P109:AS109)</f>
         <v>1</v>
       </c>
       <c r="L109" s="2">
-        <f t="shared" ref="L109" si="68">COUNTA(Q109:AT109)</f>
+        <f t="shared" ref="L109" si="70">COUNTA(Q109:AT109)</f>
         <v>1</v>
       </c>
       <c r="M109" s="2" cm="1">
@@ -11100,11 +11175,11 @@
         <v>10</v>
       </c>
       <c r="N109" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O109" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="Z109" s="1" t="s">
@@ -11131,18 +11206,18 @@
         <v>326</v>
       </c>
       <c r="I110" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A031</v>
       </c>
       <c r="J110" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K110" s="2">
-        <f t="shared" ref="K110" si="69">COUNTA(P110:AS110)</f>
+        <f t="shared" ref="K110" si="71">COUNTA(P110:AS110)</f>
         <v>2</v>
       </c>
       <c r="L110" s="2">
-        <f t="shared" ref="L110" si="70">COUNTA(Q110:AT110)</f>
+        <f t="shared" ref="L110" si="72">COUNTA(Q110:AT110)</f>
         <v>2</v>
       </c>
       <c r="M110" s="2" cm="1">
@@ -11150,11 +11225,11 @@
         <v>6</v>
       </c>
       <c r="N110" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O110" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="V110" s="1" t="s">
@@ -11181,18 +11256,18 @@
         <v>230</v>
       </c>
       <c r="I111" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A032</v>
       </c>
       <c r="J111" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K111" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>3</v>
       </c>
       <c r="L111" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3</v>
       </c>
       <c r="M111" s="2" cm="1">
@@ -11200,11 +11275,11 @@
         <v>4</v>
       </c>
       <c r="N111" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>25</v>
       </c>
       <c r="O111" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★★</v>
       </c>
       <c r="T111" s="1" t="s">
@@ -11234,18 +11309,18 @@
         <v>281</v>
       </c>
       <c r="I112" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A033</v>
       </c>
       <c r="J112" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K112" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L112" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M112" s="2" cm="1">
@@ -11253,11 +11328,11 @@
         <v>5</v>
       </c>
       <c r="N112" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O112" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="U112" s="1" t="s">
@@ -11288,18 +11363,18 @@
         <v>181</v>
       </c>
       <c r="I113" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A034</v>
       </c>
       <c r="J113" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K113" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L113" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M113" s="2" cm="1">
@@ -11307,11 +11382,11 @@
         <v>2</v>
       </c>
       <c r="N113" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O113" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="R113" s="1" t="s">
@@ -11338,18 +11413,18 @@
         <v>508</v>
       </c>
       <c r="I114" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A035</v>
       </c>
       <c r="J114" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K114" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L114" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M114" s="2" cm="1">
@@ -11357,11 +11432,11 @@
         <v>2</v>
       </c>
       <c r="N114" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O114" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="R114" s="1" t="s">
@@ -11388,18 +11463,18 @@
         <v>131</v>
       </c>
       <c r="I115" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A036</v>
       </c>
       <c r="J115" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K115" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L115" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M115" s="2" cm="1">
@@ -11407,11 +11482,11 @@
         <v>0</v>
       </c>
       <c r="N115" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O115" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="P115" s="1" t="s">
@@ -11438,18 +11513,18 @@
         <v>464</v>
       </c>
       <c r="I116" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A037</v>
       </c>
       <c r="J116" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K116" s="2">
-        <f t="shared" ref="K116" si="71">COUNTA(P116:AS116)</f>
+        <f t="shared" ref="K116" si="73">COUNTA(P116:AS116)</f>
         <v>2</v>
       </c>
       <c r="L116" s="2">
-        <f t="shared" ref="L116" si="72">COUNTA(Q116:AT116)</f>
+        <f t="shared" ref="L116" si="74">COUNTA(Q116:AT116)</f>
         <v>2</v>
       </c>
       <c r="M116" s="2" cm="1">
@@ -11457,11 +11532,11 @@
         <v>1</v>
       </c>
       <c r="N116" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O116" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="Q116" s="1" t="s">
@@ -11488,18 +11563,18 @@
         <v>254</v>
       </c>
       <c r="I117" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A038</v>
       </c>
       <c r="J117" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K117" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>3</v>
       </c>
       <c r="L117" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3</v>
       </c>
       <c r="M117" s="2" cm="1">
@@ -11507,11 +11582,11 @@
         <v>4</v>
       </c>
       <c r="N117" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>25</v>
       </c>
       <c r="O117" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★★</v>
       </c>
       <c r="T117" s="1" t="s">
@@ -11541,18 +11616,18 @@
         <v>282</v>
       </c>
       <c r="I118" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A039</v>
       </c>
       <c r="J118" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K118" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L118" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M118" s="2" cm="1">
@@ -11560,11 +11635,11 @@
         <v>5</v>
       </c>
       <c r="N118" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O118" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="U118" s="1" t="s">
@@ -11591,18 +11666,18 @@
         <v>328</v>
       </c>
       <c r="I119" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A040</v>
       </c>
       <c r="J119" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K119" s="2">
-        <f t="shared" ref="K119" si="73">COUNTA(P119:AS119)</f>
+        <f t="shared" ref="K119" si="75">COUNTA(P119:AS119)</f>
         <v>1</v>
       </c>
       <c r="L119" s="2">
-        <f t="shared" ref="L119" si="74">COUNTA(Q119:AT119)</f>
+        <f t="shared" ref="L119" si="76">COUNTA(Q119:AT119)</f>
         <v>1</v>
       </c>
       <c r="M119" s="2" cm="1">
@@ -11610,11 +11685,11 @@
         <v>6</v>
       </c>
       <c r="N119" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O119" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="V119" s="1" t="s">
@@ -11638,18 +11713,18 @@
         <v>563</v>
       </c>
       <c r="I120" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A041</v>
       </c>
       <c r="J120" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K120" s="2">
-        <f t="shared" ref="K120" si="75">COUNTA(P120:AS120)</f>
+        <f t="shared" ref="K120" si="77">COUNTA(P120:AS120)</f>
         <v>1</v>
       </c>
       <c r="L120" s="2">
-        <f t="shared" ref="L120" si="76">COUNTA(Q120:AT120)</f>
+        <f t="shared" ref="L120" si="78">COUNTA(Q120:AT120)</f>
         <v>1</v>
       </c>
       <c r="M120" s="2" cm="1">
@@ -11657,11 +11732,11 @@
         <v>12</v>
       </c>
       <c r="N120" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O120" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="AB120" s="1" t="s">
@@ -11692,18 +11767,18 @@
         <v>103</v>
       </c>
       <c r="I121" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A042</v>
       </c>
       <c r="J121" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K121" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L121" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M121" s="2" cm="1">
@@ -11711,11 +11786,11 @@
         <v>1</v>
       </c>
       <c r="N121" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O121" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="Q121" s="1" t="s">
@@ -11742,18 +11817,18 @@
         <v>194</v>
       </c>
       <c r="I122" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A043</v>
       </c>
       <c r="J122" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K122" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L122" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M122" s="2" cm="1">
@@ -11761,11 +11836,11 @@
         <v>3</v>
       </c>
       <c r="N122" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O122" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="S122" s="1" t="s">
@@ -11799,18 +11874,18 @@
         <v>100</v>
       </c>
       <c r="I123" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A044</v>
       </c>
       <c r="J123" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K123" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L123" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M123" s="2" cm="1">
@@ -11818,11 +11893,11 @@
         <v>1</v>
       </c>
       <c r="N123" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O123" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="Q123" s="1" t="s">
@@ -11849,18 +11924,18 @@
         <v>178</v>
       </c>
       <c r="I124" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A045</v>
       </c>
       <c r="J124" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K124" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L124" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M124" s="2" cm="1">
@@ -11868,11 +11943,11 @@
         <v>2</v>
       </c>
       <c r="N124" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O124" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="R124" s="1" t="s">
@@ -11899,18 +11974,18 @@
         <v>197</v>
       </c>
       <c r="I125" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A046</v>
       </c>
       <c r="J125" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K125" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L125" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M125" s="2" cm="1">
@@ -11918,11 +11993,11 @@
         <v>3</v>
       </c>
       <c r="N125" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O125" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="S125" s="1" t="s">
@@ -11949,18 +12024,18 @@
         <v>496</v>
       </c>
       <c r="I126" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A047</v>
       </c>
       <c r="J126" s="5" t="s">
         <v>81</v>
       </c>
       <c r="K126" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>4</v>
       </c>
       <c r="L126" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3</v>
       </c>
       <c r="M126" s="2" cm="1">
@@ -11968,11 +12043,11 @@
         <v>0</v>
       </c>
       <c r="N126" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O126" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="P126" s="1" t="s">
@@ -12005,18 +12080,18 @@
         <v>227</v>
       </c>
       <c r="I127" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A048</v>
       </c>
       <c r="J127" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K127" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L127" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M127" s="2" cm="1">
@@ -12024,11 +12099,11 @@
         <v>4</v>
       </c>
       <c r="N127" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O127" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★★</v>
       </c>
       <c r="T127" s="1" t="s">
@@ -12055,18 +12130,18 @@
         <v>535</v>
       </c>
       <c r="I128" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A049</v>
       </c>
       <c r="J128" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K128" s="2">
-        <f t="shared" ref="K128" si="77">COUNTA(P128:AS128)</f>
+        <f t="shared" ref="K128" si="79">COUNTA(P128:AS128)</f>
         <v>1</v>
       </c>
       <c r="L128" s="2">
-        <f t="shared" ref="L128" si="78">COUNTA(Q128:AT128)</f>
+        <f t="shared" ref="L128" si="80">COUNTA(Q128:AT128)</f>
         <v>1</v>
       </c>
       <c r="M128" s="2" cm="1">
@@ -12074,11 +12149,11 @@
         <v>11</v>
       </c>
       <c r="N128" s="11">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O128" s="11" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>★★</v>
       </c>
       <c r="AA128" s="1" t="s">
@@ -12109,18 +12184,18 @@
         <v>256</v>
       </c>
       <c r="I129" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A050</v>
       </c>
       <c r="J129" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K129" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="L129" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M129" s="2" cm="1">
@@ -12128,11 +12203,11 @@
         <v>4</v>
       </c>
       <c r="N129" s="11">
-        <f t="shared" ref="N129:N192" si="79">COUNTA(Q129:AB129)/COUNTA($Q$1:$AB$1)*100</f>
+        <f t="shared" ref="N129:N192" si="81">COUNTA(Q129:AB129)/COUNTA($Q$1:$AB$1)*100</f>
         <v>8.3333333333333321</v>
       </c>
       <c r="O129" s="11" t="str">
-        <f t="shared" ref="O129:O192" si="80">IF(N129&gt;=33,"★★★★★",IF(N129&gt;=25,"★★★★",IF(N129&gt;=15,"★★★",IF(N129&gt;=5,"★★","★"))))</f>
+        <f t="shared" ref="O129:O192" si="82">IF(N129&gt;=33,"★★★★★",IF(N129&gt;=25,"★★★★",IF(N129&gt;=15,"★★★",IF(N129&gt;=5,"★★","★"))))</f>
         <v>★★</v>
       </c>
       <c r="T129" s="1" t="s">
@@ -12156,18 +12231,18 @@
         <v>286</v>
       </c>
       <c r="I130" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A051</v>
       </c>
       <c r="J130" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K130" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="L130" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M130" s="2" cm="1">
@@ -12175,11 +12250,11 @@
         <v>5</v>
       </c>
       <c r="N130" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O130" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="U130" s="1" t="s">
@@ -12203,18 +12278,18 @@
         <v>522</v>
       </c>
       <c r="I131" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A052</v>
       </c>
       <c r="J131" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K131" s="2">
-        <f t="shared" ref="K131" si="81">COUNTA(P131:AS131)</f>
+        <f t="shared" ref="K131" si="83">COUNTA(P131:AS131)</f>
         <v>1</v>
       </c>
       <c r="L131" s="2">
-        <f t="shared" ref="L131" si="82">COUNTA(Q131:AT131)</f>
+        <f t="shared" ref="L131" si="84">COUNTA(Q131:AT131)</f>
         <v>1</v>
       </c>
       <c r="M131" s="2" cm="1">
@@ -12222,11 +12297,11 @@
         <v>10</v>
       </c>
       <c r="N131" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O131" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="Z131" s="1" t="s">
@@ -12254,18 +12329,18 @@
         <v>101</v>
       </c>
       <c r="I132" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A053</v>
       </c>
       <c r="J132" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K132" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>3</v>
       </c>
       <c r="L132" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3</v>
       </c>
       <c r="M132" s="2" cm="1">
@@ -12273,11 +12348,11 @@
         <v>1</v>
       </c>
       <c r="N132" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>25</v>
       </c>
       <c r="O132" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★</v>
       </c>
       <c r="Q132" s="1" t="s">
@@ -12307,18 +12382,18 @@
         <v>72</v>
       </c>
       <c r="I133" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A054</v>
       </c>
       <c r="J133" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K133" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="L133" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M133" s="2" cm="1">
@@ -12326,11 +12401,11 @@
         <v>2</v>
       </c>
       <c r="N133" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O133" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="R133" s="1" t="s">
@@ -12354,18 +12429,18 @@
         <v>334</v>
       </c>
       <c r="I134" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A055</v>
       </c>
       <c r="J134" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K134" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="L134" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M134" s="2" cm="1">
@@ -12373,11 +12448,11 @@
         <v>6</v>
       </c>
       <c r="N134" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O134" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="V134" s="1" t="s">
@@ -12401,18 +12476,18 @@
         <v>139</v>
       </c>
       <c r="I135" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A056</v>
       </c>
       <c r="J135" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K135" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>4</v>
       </c>
       <c r="L135" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3</v>
       </c>
       <c r="M135" s="2" cm="1">
@@ -12420,11 +12495,11 @@
         <v>0</v>
       </c>
       <c r="N135" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O135" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="P135" s="1" t="s">
@@ -12457,18 +12532,18 @@
         <v>237</v>
       </c>
       <c r="I136" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A057</v>
       </c>
       <c r="J136" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K136" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L136" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M136" s="2" cm="1">
@@ -12476,11 +12551,11 @@
         <v>4</v>
       </c>
       <c r="N136" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O136" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="T136" s="1" t="s">
@@ -12514,18 +12589,18 @@
         <v>148</v>
       </c>
       <c r="I137" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A058</v>
       </c>
       <c r="J137" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K137" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L137" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M137" s="2" cm="1">
@@ -12533,11 +12608,11 @@
         <v>1</v>
       </c>
       <c r="N137" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O137" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="Q137" s="1" t="s">
@@ -12564,18 +12639,18 @@
         <v>149</v>
       </c>
       <c r="I138" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A059</v>
       </c>
       <c r="J138" s="5" t="s">
         <v>81</v>
       </c>
       <c r="K138" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>3</v>
       </c>
       <c r="L138" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M138" s="2" cm="1">
@@ -12583,11 +12658,11 @@
         <v>0</v>
       </c>
       <c r="N138" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O138" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="P138" s="1" t="s">
@@ -12617,18 +12692,18 @@
         <v>150</v>
       </c>
       <c r="I139" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A060</v>
       </c>
       <c r="J139" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K139" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L139" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M139" s="2" cm="1">
@@ -12636,11 +12711,11 @@
         <v>3</v>
       </c>
       <c r="N139" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O139" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="S139" s="1" t="s">
@@ -12667,18 +12742,18 @@
         <v>468</v>
       </c>
       <c r="I140" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A061</v>
       </c>
       <c r="J140" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K140" s="2">
-        <f t="shared" ref="K140" si="83">COUNTA(P140:AS140)</f>
+        <f t="shared" ref="K140" si="85">COUNTA(P140:AS140)</f>
         <v>1</v>
       </c>
       <c r="L140" s="2">
-        <f t="shared" ref="L140" si="84">COUNTA(Q140:AT140)</f>
+        <f t="shared" ref="L140" si="86">COUNTA(Q140:AT140)</f>
         <v>1</v>
       </c>
       <c r="M140" s="2" cm="1">
@@ -12686,11 +12761,11 @@
         <v>9</v>
       </c>
       <c r="N140" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O140" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="Y140" s="1" t="s">
@@ -12714,18 +12789,18 @@
         <v>376</v>
       </c>
       <c r="I141" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A062</v>
       </c>
       <c r="J141" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K141" s="2">
-        <f t="shared" ref="K141" si="85">COUNTA(P141:AS141)</f>
+        <f t="shared" ref="K141" si="87">COUNTA(P141:AS141)</f>
         <v>1</v>
       </c>
       <c r="L141" s="2">
-        <f t="shared" ref="L141" si="86">COUNTA(Q141:AT141)</f>
+        <f t="shared" ref="L141" si="88">COUNTA(Q141:AT141)</f>
         <v>1</v>
       </c>
       <c r="M141" s="2" cm="1">
@@ -12733,11 +12808,11 @@
         <v>7</v>
       </c>
       <c r="N141" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O141" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="W141" s="1" t="s">
@@ -12768,18 +12843,18 @@
         <v>104</v>
       </c>
       <c r="I142" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A063</v>
       </c>
       <c r="J142" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K142" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>3</v>
       </c>
       <c r="L142" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3</v>
       </c>
       <c r="M142" s="2" cm="1">
@@ -12787,11 +12862,11 @@
         <v>1</v>
       </c>
       <c r="N142" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>25</v>
       </c>
       <c r="O142" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★</v>
       </c>
       <c r="Q142" s="1" t="s">
@@ -12821,18 +12896,18 @@
         <v>290</v>
       </c>
       <c r="I143" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A064</v>
       </c>
       <c r="J143" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K143" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>3</v>
       </c>
       <c r="L143" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3</v>
       </c>
       <c r="M143" s="2" cm="1">
@@ -12840,11 +12915,11 @@
         <v>2</v>
       </c>
       <c r="N143" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O143" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="R143" s="1" t="s">
@@ -12874,18 +12949,18 @@
         <v>288</v>
       </c>
       <c r="I144" s="1" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>A065</v>
       </c>
       <c r="J144" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K144" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="L144" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M144" s="2" cm="1">
@@ -12893,11 +12968,11 @@
         <v>5</v>
       </c>
       <c r="N144" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O144" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="U144" s="1" t="s">
@@ -12921,18 +12996,18 @@
         <v>414</v>
       </c>
       <c r="I145" s="1" t="str">
-        <f t="shared" ref="I145:I208" si="87">B145&amp;TEXT(G145,"000")</f>
+        <f t="shared" ref="I145:I208" si="89">B145&amp;TEXT(G145,"000")</f>
         <v>A066</v>
       </c>
       <c r="J145" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K145" s="2">
-        <f t="shared" ref="K145" si="88">COUNTA(P145:AS145)</f>
+        <f t="shared" ref="K145" si="90">COUNTA(P145:AS145)</f>
         <v>2</v>
       </c>
       <c r="L145" s="2">
-        <f t="shared" ref="L145" si="89">COUNTA(Q145:AT145)</f>
+        <f t="shared" ref="L145" si="91">COUNTA(Q145:AT145)</f>
         <v>2</v>
       </c>
       <c r="M145" s="2" cm="1">
@@ -12940,11 +13015,11 @@
         <v>8</v>
       </c>
       <c r="N145" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O145" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="X145" s="1" t="s">
@@ -12971,18 +13046,18 @@
         <v>198</v>
       </c>
       <c r="I146" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>A067</v>
       </c>
       <c r="J146" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K146" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L146" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M146" s="2" cm="1">
@@ -12990,11 +13065,11 @@
         <v>3</v>
       </c>
       <c r="N146" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O146" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="S146" s="1" t="s">
@@ -13028,18 +13103,18 @@
         <v>147</v>
       </c>
       <c r="I147" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>A068</v>
       </c>
       <c r="J147" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K147" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L147" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M147" s="2" cm="1">
@@ -13047,11 +13122,11 @@
         <v>0</v>
       </c>
       <c r="N147" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O147" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="P147" s="1" t="s">
@@ -13078,18 +13153,18 @@
         <v>233</v>
       </c>
       <c r="I148" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>A069</v>
       </c>
       <c r="J148" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K148" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>3</v>
       </c>
       <c r="L148" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3</v>
       </c>
       <c r="M148" s="2" cm="1">
@@ -13097,11 +13172,11 @@
         <v>4</v>
       </c>
       <c r="N148" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>25</v>
       </c>
       <c r="O148" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★</v>
       </c>
       <c r="T148" s="1" t="s">
@@ -13131,18 +13206,18 @@
         <v>291</v>
       </c>
       <c r="I149" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>A070</v>
       </c>
       <c r="J149" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K149" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>3</v>
       </c>
       <c r="L149" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>3</v>
       </c>
       <c r="M149" s="2" cm="1">
@@ -13150,11 +13225,11 @@
         <v>5</v>
       </c>
       <c r="N149" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>25</v>
       </c>
       <c r="O149" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★</v>
       </c>
       <c r="U149" s="1" t="s">
@@ -13184,18 +13259,18 @@
         <v>332</v>
       </c>
       <c r="I150" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>A071</v>
       </c>
       <c r="J150" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K150" s="2">
-        <f t="shared" ref="K150" si="90">COUNTA(P150:AS150)</f>
+        <f t="shared" ref="K150" si="92">COUNTA(P150:AS150)</f>
         <v>2</v>
       </c>
       <c r="L150" s="2">
-        <f t="shared" ref="L150" si="91">COUNTA(Q150:AT150)</f>
+        <f t="shared" ref="L150" si="93">COUNTA(Q150:AT150)</f>
         <v>2</v>
       </c>
       <c r="M150" s="2" cm="1">
@@ -13203,11 +13278,11 @@
         <v>6</v>
       </c>
       <c r="N150" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O150" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="V150" s="1" t="s">
@@ -13241,18 +13316,18 @@
         <v>152</v>
       </c>
       <c r="I151" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B001</v>
       </c>
       <c r="J151" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K151" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L151" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M151" s="2" cm="1">
@@ -13260,11 +13335,11 @@
         <v>1</v>
       </c>
       <c r="N151" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O151" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="Q151" s="1" t="s">
@@ -13291,18 +13366,18 @@
         <v>151</v>
       </c>
       <c r="I152" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B002</v>
       </c>
       <c r="J152" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K152" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="L152" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="M152" s="2" cm="1">
@@ -13310,11 +13385,11 @@
         <v>0</v>
       </c>
       <c r="N152" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="O152" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★</v>
       </c>
       <c r="P152" s="1" t="s">
@@ -13338,18 +13413,18 @@
         <v>381</v>
       </c>
       <c r="I153" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B003</v>
       </c>
       <c r="J153" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K153" s="2">
-        <f t="shared" ref="K153" si="92">COUNTA(P153:AS153)</f>
+        <f t="shared" ref="K153" si="94">COUNTA(P153:AS153)</f>
         <v>1</v>
       </c>
       <c r="L153" s="2">
-        <f t="shared" ref="L153" si="93">COUNTA(Q153:AT153)</f>
+        <f t="shared" ref="L153" si="95">COUNTA(Q153:AT153)</f>
         <v>1</v>
       </c>
       <c r="M153" s="2" cm="1">
@@ -13357,11 +13432,11 @@
         <v>7</v>
       </c>
       <c r="N153" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O153" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="W153" s="1" t="s">
@@ -13385,18 +13460,18 @@
         <v>182</v>
       </c>
       <c r="I154" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B004</v>
       </c>
       <c r="J154" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K154" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>1</v>
       </c>
       <c r="L154" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>1</v>
       </c>
       <c r="M154" s="2" cm="1">
@@ -13404,11 +13479,11 @@
         <v>2</v>
       </c>
       <c r="N154" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O154" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="R154" s="1" t="s">
@@ -13432,18 +13507,18 @@
         <v>102</v>
       </c>
       <c r="I155" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B005</v>
       </c>
       <c r="J155" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K155" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>2</v>
       </c>
       <c r="L155" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>2</v>
       </c>
       <c r="M155" s="2" cm="1">
@@ -13451,11 +13526,11 @@
         <v>1</v>
       </c>
       <c r="N155" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O155" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="Q155" s="1" t="s">
@@ -13482,18 +13557,18 @@
         <v>241</v>
       </c>
       <c r="I156" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B006</v>
       </c>
       <c r="J156" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K156" s="2">
-        <f t="shared" ref="K156:L160" si="94">COUNTA(P156:AS156)</f>
+        <f t="shared" ref="K156:L160" si="96">COUNTA(P156:AS156)</f>
         <v>1</v>
       </c>
       <c r="L156" s="2">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="M156" s="2" cm="1">
@@ -13501,11 +13576,11 @@
         <v>4</v>
       </c>
       <c r="N156" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O156" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="T156" s="1" t="s">
@@ -13529,18 +13604,18 @@
         <v>588</v>
       </c>
       <c r="I157" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B007</v>
       </c>
       <c r="J157" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K157" s="2">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="L157" s="2">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="M157" s="2" cm="1">
@@ -13548,11 +13623,11 @@
         <v>13</v>
       </c>
       <c r="N157" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="O157" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★</v>
       </c>
       <c r="AC157" s="1" t="s">
@@ -13576,18 +13651,18 @@
         <v>199</v>
       </c>
       <c r="I158" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B008</v>
       </c>
       <c r="J158" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K158" s="2">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>2</v>
       </c>
       <c r="L158" s="2">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>2</v>
       </c>
       <c r="M158" s="2" cm="1">
@@ -13595,11 +13670,11 @@
         <v>3</v>
       </c>
       <c r="N158" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O158" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="S158" s="1" t="s">
@@ -13626,18 +13701,18 @@
         <v>294</v>
       </c>
       <c r="I159" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B009</v>
       </c>
       <c r="J159" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K159" s="2">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="L159" s="2">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="M159" s="2" cm="1">
@@ -13645,11 +13720,11 @@
         <v>5</v>
       </c>
       <c r="N159" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O159" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="U159" s="1" t="s">
@@ -13673,18 +13748,18 @@
         <v>567</v>
       </c>
       <c r="I160" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B010</v>
       </c>
       <c r="J160" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K160" s="2">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="L160" s="2">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>1</v>
       </c>
       <c r="M160" s="2" cm="1">
@@ -13692,11 +13767,11 @@
         <v>12</v>
       </c>
       <c r="N160" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O160" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="AB160" s="1" t="s">
@@ -13727,18 +13802,18 @@
         <v>159</v>
       </c>
       <c r="I161" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B011</v>
       </c>
       <c r="J161" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K161" s="2">
-        <f t="shared" ref="K161:K215" si="95">COUNTA(P161:AS161)</f>
+        <f t="shared" ref="K161:K215" si="97">COUNTA(P161:AS161)</f>
         <v>2</v>
       </c>
       <c r="L161" s="2">
-        <f t="shared" ref="L161:L215" si="96">COUNTA(Q161:AT161)</f>
+        <f t="shared" ref="L161:L215" si="98">COUNTA(Q161:AT161)</f>
         <v>1</v>
       </c>
       <c r="M161" s="2" cm="1">
@@ -13746,11 +13821,11 @@
         <v>0</v>
       </c>
       <c r="N161" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O161" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="P161" s="1" t="s">
@@ -13777,18 +13852,18 @@
         <v>240</v>
       </c>
       <c r="I162" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B012</v>
       </c>
       <c r="J162" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K162" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L162" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M162" s="2" cm="1">
@@ -13796,11 +13871,11 @@
         <v>4</v>
       </c>
       <c r="N162" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O162" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="T162" s="1" t="s">
@@ -13824,18 +13899,18 @@
         <v>536</v>
       </c>
       <c r="I163" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B013</v>
       </c>
       <c r="J163" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K163" s="2">
-        <f t="shared" ref="K163" si="97">COUNTA(P163:AS163)</f>
+        <f t="shared" ref="K163" si="99">COUNTA(P163:AS163)</f>
         <v>1</v>
       </c>
       <c r="L163" s="2">
-        <f t="shared" ref="L163" si="98">COUNTA(Q163:AT163)</f>
+        <f t="shared" ref="L163" si="100">COUNTA(Q163:AT163)</f>
         <v>1</v>
       </c>
       <c r="M163" s="2" cm="1">
@@ -13843,11 +13918,11 @@
         <v>11</v>
       </c>
       <c r="N163" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O163" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="AA163" s="1" t="s">
@@ -13871,18 +13946,18 @@
         <v>427</v>
       </c>
       <c r="I164" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B014</v>
       </c>
       <c r="J164" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K164" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2</v>
       </c>
       <c r="L164" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M164" s="2" cm="1">
@@ -13890,11 +13965,11 @@
         <v>8</v>
       </c>
       <c r="N164" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O164" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="X164" s="1" t="s">
@@ -13921,18 +13996,18 @@
         <v>483</v>
       </c>
       <c r="I165" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B015</v>
       </c>
       <c r="J165" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K165" s="2">
-        <f t="shared" ref="K165" si="99">COUNTA(P165:AS165)</f>
+        <f t="shared" ref="K165" si="101">COUNTA(P165:AS165)</f>
         <v>1</v>
       </c>
       <c r="L165" s="2">
-        <f t="shared" ref="L165" si="100">COUNTA(Q165:AT165)</f>
+        <f t="shared" ref="L165" si="102">COUNTA(Q165:AT165)</f>
         <v>1</v>
       </c>
       <c r="M165" s="2" cm="1">
@@ -13940,11 +14015,11 @@
         <v>9</v>
       </c>
       <c r="N165" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O165" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="Y165" s="1" t="s">
@@ -13968,18 +14043,18 @@
         <v>528</v>
       </c>
       <c r="I166" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B016</v>
       </c>
       <c r="J166" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K166" s="2">
-        <f t="shared" ref="K166" si="101">COUNTA(P166:AS166)</f>
+        <f t="shared" ref="K166" si="103">COUNTA(P166:AS166)</f>
         <v>2</v>
       </c>
       <c r="L166" s="2">
-        <f t="shared" ref="L166" si="102">COUNTA(Q166:AT166)</f>
+        <f t="shared" ref="L166" si="104">COUNTA(Q166:AT166)</f>
         <v>2</v>
       </c>
       <c r="M166" s="2" cm="1">
@@ -13987,11 +14062,11 @@
         <v>10</v>
       </c>
       <c r="N166" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O166" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="Z166" s="1" t="s">
@@ -14025,18 +14100,18 @@
         <v>486</v>
       </c>
       <c r="I167" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B017</v>
       </c>
       <c r="J167" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K167" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>6</v>
       </c>
       <c r="L167" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>6</v>
       </c>
       <c r="M167" s="2" cm="1">
@@ -14044,11 +14119,11 @@
         <v>1</v>
       </c>
       <c r="N167" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>50</v>
       </c>
       <c r="O167" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★★</v>
       </c>
       <c r="Q167" s="1" t="s">
@@ -14087,18 +14162,18 @@
         <v>513</v>
       </c>
       <c r="I168" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B018</v>
       </c>
       <c r="J168" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K168" s="2">
-        <f t="shared" ref="K168" si="103">COUNTA(P168:AS168)</f>
+        <f t="shared" ref="K168" si="105">COUNTA(P168:AS168)</f>
         <v>1</v>
       </c>
       <c r="L168" s="2">
-        <f t="shared" ref="L168" si="104">COUNTA(Q168:AT168)</f>
+        <f t="shared" ref="L168" si="106">COUNTA(Q168:AT168)</f>
         <v>1</v>
       </c>
       <c r="M168" s="2" cm="1">
@@ -14106,11 +14181,11 @@
         <v>10</v>
       </c>
       <c r="N168" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O168" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="Z168" s="1" t="s">
@@ -14134,18 +14209,18 @@
         <v>183</v>
       </c>
       <c r="I169" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B019</v>
       </c>
       <c r="J169" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K169" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2</v>
       </c>
       <c r="L169" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M169" s="2" cm="1">
@@ -14153,11 +14228,11 @@
         <v>2</v>
       </c>
       <c r="N169" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O169" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="R169" s="1" t="s">
@@ -14184,18 +14259,18 @@
         <v>153</v>
       </c>
       <c r="I170" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B020</v>
       </c>
       <c r="J170" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K170" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3</v>
       </c>
       <c r="L170" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M170" s="2" cm="1">
@@ -14203,11 +14278,11 @@
         <v>0</v>
       </c>
       <c r="N170" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O170" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="P170" s="1" t="s">
@@ -14237,18 +14312,18 @@
         <v>296</v>
       </c>
       <c r="I171" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B021</v>
       </c>
       <c r="J171" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K171" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L171" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M171" s="2" cm="1">
@@ -14256,11 +14331,11 @@
         <v>5</v>
       </c>
       <c r="N171" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O171" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="U171" s="1" t="s">
@@ -14284,18 +14359,18 @@
         <v>340</v>
       </c>
       <c r="I172" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B022</v>
       </c>
       <c r="J172" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K172" s="2">
-        <f t="shared" ref="K172" si="105">COUNTA(P172:AS172)</f>
+        <f t="shared" ref="K172" si="107">COUNTA(P172:AS172)</f>
         <v>2</v>
       </c>
       <c r="L172" s="2">
-        <f t="shared" ref="L172" si="106">COUNTA(Q172:AT172)</f>
+        <f t="shared" ref="L172" si="108">COUNTA(Q172:AT172)</f>
         <v>2</v>
       </c>
       <c r="M172" s="2" cm="1">
@@ -14303,11 +14378,11 @@
         <v>6</v>
       </c>
       <c r="N172" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O172" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="V172" s="1" t="s">
@@ -14334,18 +14409,18 @@
         <v>585</v>
       </c>
       <c r="I173" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B023</v>
       </c>
       <c r="J173" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K173" s="2">
-        <f t="shared" ref="K173" si="107">COUNTA(P173:AS173)</f>
+        <f t="shared" ref="K173" si="109">COUNTA(P173:AS173)</f>
         <v>1</v>
       </c>
       <c r="L173" s="2">
-        <f t="shared" ref="L173" si="108">COUNTA(Q173:AT173)</f>
+        <f t="shared" ref="L173" si="110">COUNTA(Q173:AT173)</f>
         <v>1</v>
       </c>
       <c r="M173" s="2" cm="1">
@@ -14353,11 +14428,11 @@
         <v>13</v>
       </c>
       <c r="N173" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="O173" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★</v>
       </c>
       <c r="AC173" s="1" t="s">
@@ -14388,18 +14463,18 @@
         <v>187</v>
       </c>
       <c r="I174" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B024</v>
       </c>
       <c r="J174" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K174" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2</v>
       </c>
       <c r="L174" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M174" s="2" cm="1">
@@ -14407,11 +14482,11 @@
         <v>2</v>
       </c>
       <c r="N174" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O174" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="R174" s="1" t="s">
@@ -14438,18 +14513,18 @@
         <v>200</v>
       </c>
       <c r="I175" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B025</v>
       </c>
       <c r="J175" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K175" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2</v>
       </c>
       <c r="L175" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M175" s="2" cm="1">
@@ -14457,11 +14532,11 @@
         <v>3</v>
       </c>
       <c r="N175" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O175" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="S175" s="1" t="s">
@@ -14488,18 +14563,18 @@
         <v>337</v>
       </c>
       <c r="I176" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B026</v>
       </c>
       <c r="J176" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K176" s="2">
-        <f t="shared" ref="K176" si="109">COUNTA(P176:AS176)</f>
+        <f t="shared" ref="K176" si="111">COUNTA(P176:AS176)</f>
         <v>1</v>
       </c>
       <c r="L176" s="2">
-        <f t="shared" ref="L176" si="110">COUNTA(Q176:AT176)</f>
+        <f t="shared" ref="L176" si="112">COUNTA(Q176:AT176)</f>
         <v>1</v>
       </c>
       <c r="M176" s="2" cm="1">
@@ -14507,11 +14582,11 @@
         <v>6</v>
       </c>
       <c r="N176" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O176" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="V176" s="1" t="s">
@@ -14542,18 +14617,18 @@
         <v>202</v>
       </c>
       <c r="I177" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B027</v>
       </c>
       <c r="J177" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K177" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>6</v>
       </c>
       <c r="L177" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>5</v>
       </c>
       <c r="M177" s="2" cm="1">
@@ -14561,11 +14636,11 @@
         <v>0</v>
       </c>
       <c r="N177" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>33.333333333333329</v>
       </c>
       <c r="O177" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★★</v>
       </c>
       <c r="P177" s="1" t="s">
@@ -14604,18 +14679,18 @@
         <v>348</v>
       </c>
       <c r="I178" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B028</v>
       </c>
       <c r="J178" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K178" s="2">
-        <f t="shared" ref="K178" si="111">COUNTA(P178:AS178)</f>
+        <f t="shared" ref="K178" si="113">COUNTA(P178:AS178)</f>
         <v>2</v>
       </c>
       <c r="L178" s="2">
-        <f t="shared" ref="L178" si="112">COUNTA(Q178:AT178)</f>
+        <f t="shared" ref="L178" si="114">COUNTA(Q178:AT178)</f>
         <v>2</v>
       </c>
       <c r="M178" s="2" cm="1">
@@ -14623,11 +14698,11 @@
         <v>6</v>
       </c>
       <c r="N178" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O178" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="V178" s="1" t="s">
@@ -14661,18 +14736,18 @@
         <v>169</v>
       </c>
       <c r="I179" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B029</v>
       </c>
       <c r="J179" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K179" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3</v>
       </c>
       <c r="L179" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="M179" s="2" cm="1">
@@ -14680,11 +14755,11 @@
         <v>2</v>
       </c>
       <c r="N179" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>25</v>
       </c>
       <c r="O179" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★</v>
       </c>
       <c r="R179" s="1" t="s">
@@ -14714,18 +14789,18 @@
         <v>299</v>
       </c>
       <c r="I180" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B030</v>
       </c>
       <c r="J180" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K180" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2</v>
       </c>
       <c r="L180" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M180" s="2" cm="1">
@@ -14733,11 +14808,11 @@
         <v>5</v>
       </c>
       <c r="N180" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O180" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="U180" s="1" t="s">
@@ -14764,18 +14839,18 @@
         <v>244</v>
       </c>
       <c r="I181" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B031</v>
       </c>
       <c r="J181" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K181" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>4</v>
       </c>
       <c r="L181" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="M181" s="2" cm="1">
@@ -14783,11 +14858,11 @@
         <v>0</v>
       </c>
       <c r="N181" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>25</v>
       </c>
       <c r="O181" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★</v>
       </c>
       <c r="P181" s="1" t="s">
@@ -14827,18 +14902,18 @@
         <v>201</v>
       </c>
       <c r="I182" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B032</v>
       </c>
       <c r="J182" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K182" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>5</v>
       </c>
       <c r="L182" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>5</v>
       </c>
       <c r="M182" s="2" cm="1">
@@ -14846,11 +14921,11 @@
         <v>1</v>
       </c>
       <c r="N182" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>33.333333333333329</v>
       </c>
       <c r="O182" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★★</v>
       </c>
       <c r="Q182" s="1" t="s">
@@ -14886,18 +14961,18 @@
         <v>184</v>
       </c>
       <c r="I183" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B033</v>
       </c>
       <c r="J183" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K183" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2</v>
       </c>
       <c r="L183" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M183" s="2" cm="1">
@@ -14905,11 +14980,11 @@
         <v>2</v>
       </c>
       <c r="N183" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O183" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★</v>
       </c>
       <c r="R183" s="1" t="s">
@@ -14936,18 +15011,18 @@
         <v>155</v>
       </c>
       <c r="I184" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B034</v>
       </c>
       <c r="J184" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K184" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3</v>
       </c>
       <c r="L184" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M184" s="2" cm="1">
@@ -14955,11 +15030,11 @@
         <v>0</v>
       </c>
       <c r="N184" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O184" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="P184" s="1" t="s">
@@ -14989,18 +15064,18 @@
         <v>75</v>
       </c>
       <c r="I185" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B035</v>
       </c>
       <c r="J185" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K185" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L185" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M185" s="2" cm="1">
@@ -15008,11 +15083,11 @@
         <v>2</v>
       </c>
       <c r="N185" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O185" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="R185" s="1" t="s">
@@ -15036,18 +15111,18 @@
         <v>205</v>
       </c>
       <c r="I186" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B036</v>
       </c>
       <c r="J186" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K186" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3</v>
       </c>
       <c r="L186" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="M186" s="2" cm="1">
@@ -15055,11 +15130,11 @@
         <v>3</v>
       </c>
       <c r="N186" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>25</v>
       </c>
       <c r="O186" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★</v>
       </c>
       <c r="S186" s="1" t="s">
@@ -15089,18 +15164,18 @@
         <v>245</v>
       </c>
       <c r="I187" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B037</v>
       </c>
       <c r="J187" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K187" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L187" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M187" s="2" cm="1">
@@ -15108,11 +15183,11 @@
         <v>4</v>
       </c>
       <c r="N187" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O187" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="T187" s="1" t="s">
@@ -15136,18 +15211,18 @@
         <v>475</v>
       </c>
       <c r="I188" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B038</v>
       </c>
       <c r="J188" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K188" s="2">
-        <f t="shared" ref="K188" si="113">COUNTA(P188:AS188)</f>
+        <f t="shared" ref="K188" si="115">COUNTA(P188:AS188)</f>
         <v>1</v>
       </c>
       <c r="L188" s="2">
-        <f t="shared" ref="L188" si="114">COUNTA(Q188:AT188)</f>
+        <f t="shared" ref="L188" si="116">COUNTA(Q188:AT188)</f>
         <v>1</v>
       </c>
       <c r="M188" s="2" cm="1">
@@ -15155,11 +15230,11 @@
         <v>9</v>
       </c>
       <c r="N188" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O188" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="Y188" s="1" t="s">
@@ -15186,18 +15261,18 @@
         <v>391</v>
       </c>
       <c r="I189" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B039</v>
       </c>
       <c r="J189" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K189" s="2">
-        <f t="shared" ref="K189" si="115">COUNTA(P189:AS189)</f>
+        <f t="shared" ref="K189" si="117">COUNTA(P189:AS189)</f>
         <v>1</v>
       </c>
       <c r="L189" s="2">
-        <f t="shared" ref="L189" si="116">COUNTA(Q189:AT189)</f>
+        <f t="shared" ref="L189" si="118">COUNTA(Q189:AT189)</f>
         <v>1</v>
       </c>
       <c r="M189" s="2" cm="1">
@@ -15205,11 +15280,11 @@
         <v>7</v>
       </c>
       <c r="N189" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O189" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="W189" s="1" t="s">
@@ -15233,18 +15308,18 @@
         <v>571</v>
       </c>
       <c r="I190" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B040</v>
       </c>
       <c r="J190" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K190" s="2">
-        <f t="shared" ref="K190" si="117">COUNTA(P190:AS190)</f>
+        <f t="shared" ref="K190" si="119">COUNTA(P190:AS190)</f>
         <v>1</v>
       </c>
       <c r="L190" s="2">
-        <f t="shared" ref="L190" si="118">COUNTA(Q190:AT190)</f>
+        <f t="shared" ref="L190" si="120">COUNTA(Q190:AT190)</f>
         <v>1</v>
       </c>
       <c r="M190" s="2" cm="1">
@@ -15252,11 +15327,11 @@
         <v>12</v>
       </c>
       <c r="N190" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O190" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="AB190" s="1" t="s">
@@ -15280,18 +15355,18 @@
         <v>538</v>
       </c>
       <c r="I191" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>B041</v>
       </c>
       <c r="J191" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K191" s="2">
-        <f t="shared" ref="K191" si="119">COUNTA(P191:AS191)</f>
+        <f t="shared" ref="K191" si="121">COUNTA(P191:AS191)</f>
         <v>1</v>
       </c>
       <c r="L191" s="2">
-        <f t="shared" ref="L191" si="120">COUNTA(Q191:AT191)</f>
+        <f t="shared" ref="L191" si="122">COUNTA(Q191:AT191)</f>
         <v>1</v>
       </c>
       <c r="M191" s="2" cm="1">
@@ -15299,11 +15374,11 @@
         <v>11</v>
       </c>
       <c r="N191" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O191" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★</v>
       </c>
       <c r="AA191" s="1" t="s">
@@ -15331,18 +15406,18 @@
         <v>106</v>
       </c>
       <c r="I192" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S001</v>
       </c>
       <c r="J192" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K192" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3</v>
       </c>
       <c r="L192" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="M192" s="2" cm="1">
@@ -15350,11 +15425,11 @@
         <v>1</v>
       </c>
       <c r="N192" s="11">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>25</v>
       </c>
       <c r="O192" s="11" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>★★★★</v>
       </c>
       <c r="Q192" s="1" t="s">
@@ -15384,18 +15459,18 @@
         <v>185</v>
       </c>
       <c r="I193" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S002</v>
       </c>
       <c r="J193" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K193" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2</v>
       </c>
       <c r="L193" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M193" s="2" cm="1">
@@ -15403,11 +15478,11 @@
         <v>2</v>
       </c>
       <c r="N193" s="11">
-        <f t="shared" ref="N193:N215" si="121">COUNTA(Q193:AB193)/COUNTA($Q$1:$AB$1)*100</f>
+        <f t="shared" ref="N193:N215" si="123">COUNTA(Q193:AB193)/COUNTA($Q$1:$AB$1)*100</f>
         <v>16.666666666666664</v>
       </c>
       <c r="O193" s="11" t="str">
-        <f t="shared" ref="O193:O215" si="122">IF(N193&gt;=33,"★★★★★",IF(N193&gt;=25,"★★★★",IF(N193&gt;=15,"★★★",IF(N193&gt;=5,"★★","★"))))</f>
+        <f t="shared" ref="O193:O215" si="124">IF(N193&gt;=33,"★★★★★",IF(N193&gt;=25,"★★★★",IF(N193&gt;=15,"★★★",IF(N193&gt;=5,"★★","★"))))</f>
         <v>★★★</v>
       </c>
       <c r="R193" s="1" t="s">
@@ -15434,18 +15509,18 @@
         <v>420</v>
       </c>
       <c r="I194" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S003</v>
       </c>
       <c r="J194" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K194" s="2">
-        <f t="shared" ref="K194" si="123">COUNTA(P194:AS194)</f>
+        <f t="shared" ref="K194" si="125">COUNTA(P194:AS194)</f>
         <v>1</v>
       </c>
       <c r="L194" s="2">
-        <f t="shared" ref="L194" si="124">COUNTA(Q194:AT194)</f>
+        <f t="shared" ref="L194" si="126">COUNTA(Q194:AT194)</f>
         <v>1</v>
       </c>
       <c r="M194" s="2" cm="1">
@@ -15453,11 +15528,11 @@
         <v>8</v>
       </c>
       <c r="N194" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O194" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="X194" s="1" t="s">
@@ -15481,18 +15556,18 @@
         <v>521</v>
       </c>
       <c r="I195" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S004</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>81</v>
       </c>
       <c r="K195" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3</v>
       </c>
       <c r="L195" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M195" s="2" cm="1">
@@ -15500,11 +15575,11 @@
         <v>0</v>
       </c>
       <c r="N195" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O195" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★★</v>
       </c>
       <c r="P195" s="1" t="s">
@@ -15534,18 +15609,18 @@
         <v>539</v>
       </c>
       <c r="I196" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S005</v>
       </c>
       <c r="J196" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K196" s="2">
-        <f t="shared" ref="K196:K197" si="125">COUNTA(P196:AS196)</f>
+        <f t="shared" ref="K196:K197" si="127">COUNTA(P196:AS196)</f>
         <v>1</v>
       </c>
       <c r="L196" s="2">
-        <f t="shared" ref="L196:L197" si="126">COUNTA(Q196:AT196)</f>
+        <f t="shared" ref="L196:L197" si="128">COUNTA(Q196:AT196)</f>
         <v>1</v>
       </c>
       <c r="M196" s="2" cm="1">
@@ -15553,11 +15628,11 @@
         <v>11</v>
       </c>
       <c r="N196" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O196" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="AA196" s="1" t="s">
@@ -15581,18 +15656,18 @@
         <v>167</v>
       </c>
       <c r="I197" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S006</v>
       </c>
       <c r="J197" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K197" s="2">
-        <f t="shared" si="125"/>
+        <f t="shared" si="127"/>
         <v>1</v>
       </c>
       <c r="L197" s="2">
-        <f t="shared" si="126"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="M197" s="2" cm="1">
@@ -15600,11 +15675,11 @@
         <v>0</v>
       </c>
       <c r="N197" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="O197" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★</v>
       </c>
       <c r="P197" s="1" t="s">
@@ -15628,18 +15703,18 @@
         <v>575</v>
       </c>
       <c r="I198" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S007</v>
       </c>
       <c r="J198" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K198" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L198" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M198" s="2" cm="1">
@@ -15647,11 +15722,11 @@
         <v>12</v>
       </c>
       <c r="N198" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O198" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="AB198" s="1" t="s">
@@ -15675,18 +15750,18 @@
         <v>586</v>
       </c>
       <c r="I199" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S008</v>
       </c>
       <c r="J199" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K199" s="2">
-        <f t="shared" ref="K199" si="127">COUNTA(P199:AS199)</f>
+        <f t="shared" ref="K199" si="129">COUNTA(P199:AS199)</f>
         <v>1</v>
       </c>
       <c r="L199" s="2">
-        <f t="shared" ref="L199" si="128">COUNTA(Q199:AT199)</f>
+        <f t="shared" ref="L199" si="130">COUNTA(Q199:AT199)</f>
         <v>1</v>
       </c>
       <c r="M199" s="2" cm="1">
@@ -15694,11 +15769,11 @@
         <v>13</v>
       </c>
       <c r="N199" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="O199" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★</v>
       </c>
       <c r="AC199" s="1" t="s">
@@ -15722,18 +15797,18 @@
         <v>301</v>
       </c>
       <c r="I200" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S009</v>
       </c>
       <c r="J200" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K200" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3</v>
       </c>
       <c r="L200" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="M200" s="2" cm="1">
@@ -15741,11 +15816,11 @@
         <v>3</v>
       </c>
       <c r="N200" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>25</v>
       </c>
       <c r="O200" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★★★</v>
       </c>
       <c r="S200" s="1" t="s">
@@ -15775,18 +15850,18 @@
         <v>304</v>
       </c>
       <c r="I201" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S010</v>
       </c>
       <c r="J201" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K201" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L201" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M201" s="2" cm="1">
@@ -15794,11 +15869,11 @@
         <v>5</v>
       </c>
       <c r="N201" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O201" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="U201" s="1" t="s">
@@ -15822,18 +15897,18 @@
         <v>309</v>
       </c>
       <c r="I202" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S011</v>
       </c>
       <c r="J202" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K202" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L202" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M202" s="2" cm="1">
@@ -15841,11 +15916,11 @@
         <v>5</v>
       </c>
       <c r="N202" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O202" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="U202" s="1" t="s">
@@ -15869,18 +15944,18 @@
         <v>386</v>
       </c>
       <c r="I203" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S012</v>
       </c>
       <c r="J203" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K203" s="2">
-        <f t="shared" ref="K203:K205" si="129">COUNTA(P203:AS203)</f>
+        <f t="shared" ref="K203:K205" si="131">COUNTA(P203:AS203)</f>
         <v>2</v>
       </c>
       <c r="L203" s="2">
-        <f t="shared" ref="L203:L205" si="130">COUNTA(Q203:AT203)</f>
+        <f t="shared" ref="L203:L205" si="132">COUNTA(Q203:AT203)</f>
         <v>2</v>
       </c>
       <c r="M203" s="2" cm="1">
@@ -15888,11 +15963,11 @@
         <v>7</v>
       </c>
       <c r="N203" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O203" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="W203" s="1" t="s">
@@ -15919,18 +15994,18 @@
         <v>422</v>
       </c>
       <c r="I204" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S013</v>
       </c>
       <c r="J204" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K204" s="2">
-        <f t="shared" ref="K204" si="131">COUNTA(P204:AS204)</f>
+        <f t="shared" ref="K204" si="133">COUNTA(P204:AS204)</f>
         <v>1</v>
       </c>
       <c r="L204" s="2">
-        <f t="shared" ref="L204" si="132">COUNTA(Q204:AT204)</f>
+        <f t="shared" ref="L204" si="134">COUNTA(Q204:AT204)</f>
         <v>1</v>
       </c>
       <c r="M204" s="2" cm="1">
@@ -15938,11 +16013,11 @@
         <v>8</v>
       </c>
       <c r="N204" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O204" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="X204" s="1" t="s">
@@ -15966,18 +16041,18 @@
         <v>393</v>
       </c>
       <c r="I205" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S014</v>
       </c>
       <c r="J205" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K205" s="2">
-        <f t="shared" si="129"/>
+        <f t="shared" si="131"/>
         <v>1</v>
       </c>
       <c r="L205" s="2">
-        <f t="shared" si="130"/>
+        <f t="shared" si="132"/>
         <v>1</v>
       </c>
       <c r="M205" s="2" cm="1">
@@ -15985,11 +16060,11 @@
         <v>7</v>
       </c>
       <c r="N205" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O205" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="W205" s="1" t="s">
@@ -16013,18 +16088,18 @@
         <v>587</v>
       </c>
       <c r="I206" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S015</v>
       </c>
       <c r="J206" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K206" s="2">
-        <f t="shared" ref="K206" si="133">COUNTA(P206:AS206)</f>
+        <f t="shared" ref="K206" si="135">COUNTA(P206:AS206)</f>
         <v>1</v>
       </c>
       <c r="L206" s="2">
-        <f t="shared" ref="L206" si="134">COUNTA(Q206:AT206)</f>
+        <f t="shared" ref="L206" si="136">COUNTA(Q206:AT206)</f>
         <v>1</v>
       </c>
       <c r="M206" s="2" cm="1">
@@ -16032,11 +16107,11 @@
         <v>13</v>
       </c>
       <c r="N206" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>0</v>
       </c>
       <c r="O206" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★</v>
       </c>
       <c r="AC206" s="1" t="s">
@@ -16064,18 +16139,18 @@
         <v>73</v>
       </c>
       <c r="I207" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S016</v>
       </c>
       <c r="J207" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K207" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>2</v>
       </c>
       <c r="L207" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M207" s="2" cm="1">
@@ -16083,11 +16158,11 @@
         <v>2</v>
       </c>
       <c r="N207" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O207" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★★</v>
       </c>
       <c r="R207" s="1" t="s">
@@ -16114,18 +16189,18 @@
         <v>203</v>
       </c>
       <c r="I208" s="1" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>S017</v>
       </c>
       <c r="J208" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K208" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L208" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M208" s="2" cm="1">
@@ -16133,11 +16208,11 @@
         <v>3</v>
       </c>
       <c r="N208" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O208" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="S208" s="1" t="s">
@@ -16161,18 +16236,18 @@
         <v>204</v>
       </c>
       <c r="I209" s="1" t="str">
-        <f t="shared" ref="I209:I215" si="135">B209&amp;TEXT(G209,"000")</f>
+        <f t="shared" ref="I209:I215" si="137">B209&amp;TEXT(G209,"000")</f>
         <v>S018</v>
       </c>
       <c r="J209" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K209" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>4</v>
       </c>
       <c r="L209" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>4</v>
       </c>
       <c r="M209" s="2" cm="1">
@@ -16180,11 +16255,11 @@
         <v>3</v>
       </c>
       <c r="N209" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>33.333333333333329</v>
       </c>
       <c r="O209" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★★★★</v>
       </c>
       <c r="S209" s="1" t="s">
@@ -16217,18 +16292,18 @@
         <v>83</v>
       </c>
       <c r="I210" s="1" t="str">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>S019</v>
       </c>
       <c r="J210" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K210" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3</v>
       </c>
       <c r="L210" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>3</v>
       </c>
       <c r="M210" s="2" cm="1">
@@ -16236,11 +16311,11 @@
         <v>3</v>
       </c>
       <c r="N210" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>25</v>
       </c>
       <c r="O210" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★★★</v>
       </c>
       <c r="S210" s="1" t="s">
@@ -16270,18 +16345,18 @@
         <v>163</v>
       </c>
       <c r="I211" s="1" t="str">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>S020</v>
       </c>
       <c r="J211" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K211" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>3</v>
       </c>
       <c r="L211" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2</v>
       </c>
       <c r="M211" s="2" cm="1">
@@ -16289,11 +16364,11 @@
         <v>0</v>
       </c>
       <c r="N211" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>16.666666666666664</v>
       </c>
       <c r="O211" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★★</v>
       </c>
       <c r="P211" s="1" t="s">
@@ -16323,18 +16398,18 @@
         <v>344</v>
       </c>
       <c r="I212" s="1" t="str">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>S021</v>
       </c>
       <c r="J212" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K212" s="2">
-        <f t="shared" ref="K212" si="136">COUNTA(P212:AS212)</f>
+        <f t="shared" ref="K212" si="138">COUNTA(P212:AS212)</f>
         <v>1</v>
       </c>
       <c r="L212" s="2">
-        <f t="shared" ref="L212" si="137">COUNTA(Q212:AT212)</f>
+        <f t="shared" ref="L212" si="139">COUNTA(Q212:AT212)</f>
         <v>1</v>
       </c>
       <c r="M212" s="2" cm="1">
@@ -16342,11 +16417,11 @@
         <v>6</v>
       </c>
       <c r="N212" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O212" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="V212" s="1" t="s">
@@ -16374,18 +16449,18 @@
         <v>107</v>
       </c>
       <c r="I213" s="1" t="str">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>S022</v>
       </c>
       <c r="J213" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K213" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L213" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M213" s="2" cm="1">
@@ -16393,11 +16468,11 @@
         <v>1</v>
       </c>
       <c r="N213" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O213" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="Q213" s="1" t="s">
@@ -16421,18 +16496,18 @@
         <v>105</v>
       </c>
       <c r="I214" s="1" t="str">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>S023</v>
       </c>
       <c r="J214" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K214" s="2">
-        <f t="shared" ref="K214" si="138">COUNTA(P214:AS214)</f>
+        <f t="shared" ref="K214" si="140">COUNTA(P214:AS214)</f>
         <v>3</v>
       </c>
       <c r="L214" s="2">
-        <f t="shared" ref="L214" si="139">COUNTA(Q214:AT214)</f>
+        <f t="shared" ref="L214" si="141">COUNTA(Q214:AT214)</f>
         <v>3</v>
       </c>
       <c r="M214" s="2" cm="1">
@@ -16440,11 +16515,11 @@
         <v>1</v>
       </c>
       <c r="N214" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>25</v>
       </c>
       <c r="O214" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★★★</v>
       </c>
       <c r="Q214" s="1" t="s">
@@ -16474,18 +16549,18 @@
         <v>518</v>
       </c>
       <c r="I215" s="1" t="str">
-        <f t="shared" si="135"/>
+        <f t="shared" si="137"/>
         <v>S024</v>
       </c>
       <c r="J215" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K215" s="2">
-        <f t="shared" si="95"/>
+        <f t="shared" si="97"/>
         <v>1</v>
       </c>
       <c r="L215" s="2">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1</v>
       </c>
       <c r="M215" s="2" cm="1">
@@ -16493,11 +16568,11 @@
         <v>10</v>
       </c>
       <c r="N215" s="11">
-        <f t="shared" si="121"/>
+        <f t="shared" si="123"/>
         <v>8.3333333333333321</v>
       </c>
       <c r="O215" s="11" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="124"/>
         <v>★★</v>
       </c>
       <c r="Z215" s="1" t="s">

--- a/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
+++ b/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Users\amano\Documents\01_趣味\無線\アマチュア無線\◇1アマ対策\AmateurRadioOperator\AmateurFirstClassRadioOperatorExam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16180EF1-C361-40EF-9B41-FEA0152C85A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D546EC-B3BD-4E18-B95E-9D4950C2E4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-7240" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="611">
   <si>
     <t>無線工学の基礎</t>
     <rPh sb="0" eb="4">
@@ -396,16 +396,6 @@
   </si>
   <si>
     <t>B1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>各種の電気現象</t>
-    <rPh sb="0" eb="2">
-      <t>カクシュ</t>
-    </rPh>
-    <rPh sb="3" eb="7">
-      <t>デンキゲンショウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -5014,6 +5004,43 @@
     </rPh>
     <rPh sb="34" eb="36">
       <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>○</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>電気と磁気に関する法則および各種電気現象</t>
+    <rPh sb="0" eb="2">
+      <t>デンキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホウソク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>デンキ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解説
+（○＝あり）</t>
+    <rPh sb="0" eb="2">
+      <t>カイセツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -5459,7 +5486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD434"/>
+  <dimension ref="A1:AF434"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" style="1" bestFit="1" customWidth="1"/>
@@ -5479,7 +5506,7 @@
     <col min="31" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="60">
+    <row r="1" spans="1:32" ht="60">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -5487,98 +5514,101 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G1" s="6"/>
       <c r="H1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q1" s="8" t="s">
         <v>13</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="V1" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="W1" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="X1" s="8" t="s">
-        <v>313</v>
-      </c>
       <c r="Y1" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="Z1" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="AA1" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="AA1" s="9" t="s">
-        <v>441</v>
-      </c>
       <c r="AB1" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="AC1" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="AD1" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="AC1" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="AD1" s="8" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AF1" s="16" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F2" s="2">
         <f>SUM(K2:K3)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="18">
         <v>1</v>
@@ -5617,15 +5647,15 @@
         <v>14</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
       <c r="A3" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>2</v>
@@ -5634,22 +5664,22 @@
         <v>2</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="I3" s="1" t="str">
         <f t="shared" ref="I3:I64" si="2">B3&amp;TEXT(G3,"000")</f>
         <v>K002</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K3" s="2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" s="2">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="2" cm="1">
         <f t="array" ref="M3">MATCH(TRUE,P3:AD3&lt;&gt;"",0)-1</f>
@@ -5664,30 +5694,33 @@
         <v>★★★★★</v>
       </c>
       <c r="P3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="S3" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30">
+        <v>606</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>2</v>
@@ -5697,7 +5730,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I4" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5727,24 +5760,24 @@
         <v>★★★</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32">
       <c r="A5" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F5" s="2">
         <f>SUM(K5:K11)</f>
@@ -5755,7 +5788,7 @@
         <v>4</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I5" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5785,15 +5818,15 @@
         <v>★★</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32">
       <c r="A6" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>2</v>
@@ -5803,7 +5836,7 @@
         <v>5</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="I6" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5836,15 +5869,15 @@
         <v>15</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32">
       <c r="A7" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>2</v>
@@ -5854,7 +5887,7 @@
         <v>6</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I7" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5884,15 +5917,15 @@
         <v>★★</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
       <c r="A8" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>2</v>
@@ -5902,7 +5935,7 @@
         <v>7</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="I8" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5932,21 +5965,21 @@
         <v>★★★★</v>
       </c>
       <c r="S8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="T8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="Y8" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32">
       <c r="A9" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>2</v>
@@ -5956,7 +5989,7 @@
         <v>8</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I9" s="1" t="str">
         <f t="shared" si="2"/>
@@ -5986,15 +6019,15 @@
         <v>★★</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32">
       <c r="A10" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>2</v>
@@ -6004,7 +6037,7 @@
         <v>9</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I10" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6034,18 +6067,18 @@
         <v>★★★</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32">
       <c r="A11" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>2</v>
@@ -6055,7 +6088,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I11" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6085,21 +6118,21 @@
         <v>★★</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32">
       <c r="A12" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F12" s="2">
         <f>SUM(K12:K16)</f>
@@ -6110,7 +6143,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I12" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6143,12 +6176,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:32">
       <c r="A13" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>2</v>
@@ -6158,7 +6191,7 @@
         <v>12</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I13" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6188,24 +6221,24 @@
         <v>★★★★</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>2</v>
@@ -6215,7 +6248,7 @@
         <v>13</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I14" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6245,15 +6278,15 @@
         <v>★★</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32">
       <c r="A15" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>2</v>
@@ -6263,7 +6296,7 @@
         <v>14</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I15" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6293,15 +6326,15 @@
         <v>★★</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32">
       <c r="A16" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>2</v>
@@ -6311,7 +6344,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I16" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6341,41 +6374,41 @@
         <v>★★★★</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32">
       <c r="A17" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F17" s="2">
         <f>SUM(K17:K22)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G17" s="18">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I17" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6408,15 +6441,15 @@
         <v>43</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32">
       <c r="A18" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>2</v>
@@ -6426,7 +6459,7 @@
         <v>17</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="I18" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6456,15 +6489,15 @@
         <v>★</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32">
       <c r="A19" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>2</v>
@@ -6474,7 +6507,7 @@
         <v>18</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I19" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6504,15 +6537,15 @@
         <v>★★</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32">
       <c r="A20" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>2</v>
@@ -6522,7 +6555,7 @@
         <v>19</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I20" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6552,15 +6585,15 @@
         <v>★★</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32">
       <c r="A21" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>2</v>
@@ -6570,7 +6603,7 @@
         <v>20</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>44</v>
+        <v>609</v>
       </c>
       <c r="I21" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6581,11 +6614,11 @@
       </c>
       <c r="K21" s="2">
         <f t="shared" ref="K21:L27" si="20">COUNTA(P21:AS21)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="20"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M21" s="2" cm="1">
         <f t="array" ref="M21">MATCH(TRUE,P21:AD21&lt;&gt;"",0)-1</f>
@@ -6606,21 +6639,24 @@
         <v>43</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29">
+        <v>524</v>
+      </c>
+      <c r="AF21" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32">
       <c r="A22" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>2</v>
@@ -6630,14 +6666,14 @@
         <v>21</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I22" s="1" t="str">
         <f t="shared" si="2"/>
         <v>K021</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K22" s="2">
         <f t="shared" si="20"/>
@@ -6660,24 +6696,24 @@
         <v>★★★</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
       <c r="A23" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="2">
         <f>SUM(K23:K25)</f>
@@ -6688,7 +6724,7 @@
         <v>22</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I23" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6718,18 +6754,18 @@
         <v>★★★</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32">
       <c r="A24" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>2</v>
@@ -6739,7 +6775,7 @@
         <v>23</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I24" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6769,15 +6805,15 @@
         <v>★★</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32">
       <c r="A25" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>2</v>
@@ -6787,7 +6823,7 @@
         <v>24</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I25" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6817,24 +6853,24 @@
         <v>★★★</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32">
       <c r="A26" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F26" s="2">
         <f>SUM(K26:K30)</f>
@@ -6845,7 +6881,7 @@
         <v>25</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I26" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6878,22 +6914,22 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:29">
+    <row r="27" spans="1:32">
       <c r="A27" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G27" s="18">
         <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I27" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6923,31 +6959,31 @@
         <v>★★★★</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32">
       <c r="A28" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G28" s="18">
         <f t="shared" si="7"/>
         <v>27</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I28" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6977,25 +7013,25 @@
         <v>★★</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32">
       <c r="A29" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G29" s="18">
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I29" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7025,28 +7061,28 @@
         <v>★★★</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32">
       <c r="A30" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G30" s="18">
         <f t="shared" si="7"/>
         <v>29</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I30" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7076,28 +7112,28 @@
         <v>★★★</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32">
       <c r="A31" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G31" s="18">
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I31" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7127,25 +7163,25 @@
         <v>★★</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32">
       <c r="A32" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G32" s="18">
         <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="I32" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7175,7 +7211,7 @@
         <v>★★</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -7183,17 +7219,17 @@
         <v>0</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G33" s="18">
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I33" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7223,7 +7259,7 @@
         <v>★</v>
       </c>
       <c r="AC33" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -7231,13 +7267,13 @@
         <v>0</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F34" s="2">
         <f>SUM(K34:K36)</f>
@@ -7248,7 +7284,7 @@
         <v>33</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I34" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7278,10 +7314,10 @@
         <v>★★★</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -7289,17 +7325,17 @@
         <v>0</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G35" s="18">
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I35" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7329,10 +7365,10 @@
         <v>★★★</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -7340,17 +7376,17 @@
         <v>0</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G36" s="18">
         <f t="shared" si="7"/>
         <v>35</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I36" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7380,7 +7416,7 @@
         <v>★★</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -7388,13 +7424,13 @@
         <v>0</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F37" s="2">
         <f>SUM(K37:K40)</f>
@@ -7405,7 +7441,7 @@
         <v>36</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I37" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7435,16 +7471,16 @@
         <v>★★★★</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -7452,17 +7488,17 @@
         <v>0</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G38" s="18">
         <f t="shared" si="7"/>
         <v>37</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I38" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7492,16 +7528,16 @@
         <v>★★★</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="V38" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AC38" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -7509,17 +7545,17 @@
         <v>0</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G39" s="18">
         <f t="shared" si="7"/>
         <v>38</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I39" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7549,16 +7585,16 @@
         <v>★★★★</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AC39" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -7566,17 +7602,17 @@
         <v>0</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G40" s="18">
         <f t="shared" si="7"/>
         <v>39</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I40" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7606,10 +7642,10 @@
         <v>★★</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AC40" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -7617,13 +7653,13 @@
         <v>0</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F41" s="2">
         <f>SUM(K41:K42)</f>
@@ -7634,7 +7670,7 @@
         <v>40</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I41" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7664,10 +7700,10 @@
         <v>★★★</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Z41" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -7675,17 +7711,17 @@
         <v>0</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G42" s="18">
         <f t="shared" si="7"/>
         <v>41</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I42" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7715,10 +7751,10 @@
         <v>★★★</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AA42" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -7726,17 +7762,17 @@
         <v>0</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G43" s="18">
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I43" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7766,10 +7802,10 @@
         <v>★★★</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" spans="1:29">
@@ -7777,16 +7813,16 @@
         <v>0</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F44" s="2">
         <f>SUM(K44:K53)</f>
@@ -7797,7 +7833,7 @@
         <v>43</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I44" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7827,19 +7863,19 @@
         <v>★★★★★</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X44" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AA44" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="45" spans="1:29">
@@ -7847,17 +7883,17 @@
         <v>0</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G45" s="18">
         <f t="shared" si="7"/>
         <v>44</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I45" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7887,10 +7923,10 @@
         <v>★★★</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="46" spans="1:29">
@@ -7898,17 +7934,17 @@
         <v>0</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G46" s="18">
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I46" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7938,10 +7974,10 @@
         <v>★★★</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="47" spans="1:29">
@@ -7949,17 +7985,17 @@
         <v>0</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G47" s="18">
         <f t="shared" si="7"/>
         <v>46</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I47" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7989,7 +8025,7 @@
         <v>★</v>
       </c>
       <c r="AC47" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="48" spans="1:29">
@@ -7997,17 +8033,17 @@
         <v>0</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G48" s="18">
         <f t="shared" si="7"/>
         <v>47</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I48" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8037,10 +8073,10 @@
         <v>★★★</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" spans="1:28">
@@ -8048,17 +8084,17 @@
         <v>0</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G49" s="18">
         <f t="shared" si="7"/>
         <v>48</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I49" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8088,13 +8124,13 @@
         <v>★★★</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y49" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="50" spans="1:28">
@@ -8102,17 +8138,17 @@
         <v>0</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G50" s="18">
         <f t="shared" si="7"/>
         <v>49</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I50" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8142,10 +8178,10 @@
         <v>★★★</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AA50" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="51" spans="1:28">
@@ -8153,20 +8189,20 @@
         <v>0</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G51" s="18">
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I51" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8204,17 +8240,17 @@
         <v>0</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G52" s="18">
         <f t="shared" si="7"/>
         <v>51</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I52" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8244,10 +8280,10 @@
         <v>★★★</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53" spans="1:28">
@@ -8255,17 +8291,17 @@
         <v>0</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G53" s="18">
         <f t="shared" si="7"/>
         <v>52</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I53" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8295,10 +8331,10 @@
         <v>★★</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Z53" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="54" spans="1:28">
@@ -8306,17 +8342,17 @@
         <v>0</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G54" s="18">
         <f t="shared" si="7"/>
         <v>53</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I54" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8346,7 +8382,7 @@
         <v>★★</v>
       </c>
       <c r="Z54" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="55" spans="1:28">
@@ -8354,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C55" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>3</v>
@@ -8371,7 +8407,7 @@
         <v>54</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I55" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8404,10 +8440,10 @@
         <v>22</v>
       </c>
       <c r="X55" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AA55" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="56" spans="1:28">
@@ -8415,17 +8451,17 @@
         <v>0</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C56" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G56" s="18">
         <f t="shared" si="7"/>
         <v>55</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I56" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8455,10 +8491,10 @@
         <v>★★</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="V56" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:28">
@@ -8466,17 +8502,17 @@
         <v>0</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C57" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G57" s="18">
         <f t="shared" si="7"/>
         <v>56</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I57" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8506,7 +8542,7 @@
         <v>★★</v>
       </c>
       <c r="AB57" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="58" spans="1:28">
@@ -8514,17 +8550,17 @@
         <v>0</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C58" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G58" s="18">
         <f t="shared" si="7"/>
         <v>57</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I58" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8554,7 +8590,7 @@
         <v>★★</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:28">
@@ -8562,13 +8598,13 @@
         <v>0</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F59" s="2">
         <f>SUM(K59:K65)</f>
@@ -8579,7 +8615,7 @@
         <v>58</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I59" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8617,17 +8653,17 @@
         <v>0</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G60" s="18">
         <f t="shared" si="7"/>
         <v>59</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I60" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8657,10 +8693,10 @@
         <v>★★★</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Z60" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="61" spans="1:28">
@@ -8668,17 +8704,17 @@
         <v>0</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G61" s="18">
         <f t="shared" si="7"/>
         <v>60</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I61" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8708,10 +8744,10 @@
         <v>★★★</v>
       </c>
       <c r="X61" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AB61" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="62" spans="1:28">
@@ -8719,17 +8755,17 @@
         <v>0</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G62" s="18">
         <f t="shared" si="7"/>
         <v>61</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I62" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8759,7 +8795,7 @@
         <v>★★</v>
       </c>
       <c r="Y62" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="63" spans="1:28">
@@ -8767,17 +8803,17 @@
         <v>0</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C63" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G63" s="18">
         <f t="shared" si="7"/>
         <v>62</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I63" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8807,7 +8843,7 @@
         <v>★★</v>
       </c>
       <c r="V63" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="1:28">
@@ -8815,17 +8851,17 @@
         <v>0</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C64" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G64" s="18">
         <f t="shared" si="7"/>
         <v>63</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I64" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8855,25 +8891,25 @@
         <v>★★</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="65" spans="1:29">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:32">
       <c r="A65" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G65" s="18">
         <f t="shared" si="7"/>
         <v>64</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I65" s="1" t="str">
         <f t="shared" ref="I65:I79" si="44">B65&amp;TEXT(G65,"000")</f>
@@ -8903,27 +8939,27 @@
         <v>★★</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V65" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AC65" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="66" spans="1:29">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="66" spans="1:32">
       <c r="A66" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F66" s="2">
         <f>SUM(K66:K71)</f>
@@ -8934,7 +8970,7 @@
         <v>65</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I66" s="1" t="str">
         <f t="shared" si="44"/>
@@ -8967,25 +9003,25 @@
         <v>18</v>
       </c>
       <c r="X66" s="1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="67" spans="1:29">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="67" spans="1:32">
       <c r="A67" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G67" s="18">
         <f t="shared" si="7"/>
         <v>66</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I67" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9018,46 +9054,46 @@
         <v>43</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Y67" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Z67" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AA67" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AB67" s="1" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="68" spans="1:29">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="68" spans="1:32">
       <c r="A68" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G68" s="18">
         <f t="shared" si="7"/>
         <v>67</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I68" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9087,34 +9123,34 @@
         <v>★★★★</v>
       </c>
       <c r="S68" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="X68" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AC68" s="1" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="69" spans="1:29">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="69" spans="1:32">
       <c r="A69" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C69" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G69" s="18">
         <f t="shared" si="7"/>
         <v>68</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I69" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9144,28 +9180,28 @@
         <v>★★</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U69" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="70" spans="1:29">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="70" spans="1:32">
       <c r="A70" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C70" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G70" s="18">
         <f t="shared" ref="G70:G79" si="47">G69+1</f>
         <v>69</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I70" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9195,25 +9231,25 @@
         <v>★</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="71" spans="1:29">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:32">
       <c r="A71" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G71" s="18">
         <f t="shared" si="47"/>
         <v>70</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I71" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9243,25 +9279,25 @@
         <v>★★</v>
       </c>
       <c r="U71" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="72" spans="1:29">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="72" spans="1:32">
       <c r="A72" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G72" s="18">
         <f t="shared" si="47"/>
         <v>71</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I72" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9291,21 +9327,21 @@
         <v>★★</v>
       </c>
       <c r="AA72" s="1" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="73" spans="1:29">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="73" spans="1:32">
       <c r="A73" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F73" s="2">
         <f>SUM(K73:K77)</f>
@@ -9316,7 +9352,7 @@
         <v>72</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I73" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9346,31 +9382,31 @@
         <v>★★★★</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="V73" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AB73" s="1" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="74" spans="1:32">
       <c r="A74" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C74" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G74" s="18">
         <f t="shared" si="47"/>
         <v>73</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I74" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9403,28 +9439,28 @@
         <v>20</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AA74" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="75" spans="1:29">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="75" spans="1:32">
       <c r="A75" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C75" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G75" s="18">
         <f t="shared" si="47"/>
         <v>74</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I75" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9454,25 +9490,25 @@
         <v>★★</v>
       </c>
       <c r="Y75" s="1" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="76" spans="1:29">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="76" spans="1:32">
       <c r="A76" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G76" s="18">
         <f t="shared" si="47"/>
         <v>75</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I76" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9502,25 +9538,25 @@
         <v>★★</v>
       </c>
       <c r="U76" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="77" spans="1:29">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="77" spans="1:32">
       <c r="A77" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C77" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G77" s="18">
         <f t="shared" si="47"/>
         <v>76</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I77" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9550,21 +9586,21 @@
         <v>★★</v>
       </c>
       <c r="Z77" s="1" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="78" spans="1:29">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="78" spans="1:32">
       <c r="A78" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F78" s="2">
         <f>SUM(K78:K79)</f>
@@ -9575,7 +9611,7 @@
         <v>77</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I78" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9605,25 +9641,25 @@
         <v>★★</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="79" spans="1:29">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79" spans="1:32">
       <c r="A79" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G79" s="18">
         <f t="shared" si="47"/>
         <v>78</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I79" s="1" t="str">
         <f t="shared" si="44"/>
@@ -9653,46 +9689,46 @@
         <v>★★</v>
       </c>
       <c r="W79" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AC79" s="1" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="80" spans="1:29">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="80" spans="1:32">
       <c r="A80" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F80" s="2">
         <f>SUM(K80:K85)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G80" s="18">
         <v>1</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="I80" s="1" t="str">
         <f>B80&amp;TEXT(G80,"000")</f>
         <v>A001</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K80" s="2">
         <f t="shared" ref="K80:K97" si="54">COUNTA(P80:AS80)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L80" s="2">
         <f t="shared" ref="L80:L97" si="55">COUNTA(Q80:AT80)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M80" s="2" cm="1">
         <f t="array" ref="M80">MATCH(TRUE,P80:AD80&lt;&gt;"",0)-1</f>
@@ -9707,25 +9743,28 @@
         <v>★★★★★</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q80" s="1" t="s">
         <v>23</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W80" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y80" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AB80" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AC80" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
+      </c>
+      <c r="AF80" s="1" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="81" spans="1:29">
@@ -9733,17 +9772,17 @@
         <v>7</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G81" s="18">
         <f>G80+1</f>
         <v>2</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I81" s="1" t="str">
         <f t="shared" ref="I81:I144" si="56">B81&amp;TEXT(G81,"000")</f>
@@ -9776,7 +9815,7 @@
         <v>25</v>
       </c>
       <c r="V81" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="82" spans="1:29">
@@ -9784,17 +9823,17 @@
         <v>7</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G82" s="18">
         <f t="shared" ref="G82:G90" si="57">G81+1</f>
         <v>3</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I82" s="1" t="str">
         <f t="shared" si="56"/>
@@ -9824,7 +9863,7 @@
         <v>★★</v>
       </c>
       <c r="S82" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:29">
@@ -9832,17 +9871,17 @@
         <v>7</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G83" s="18">
         <f t="shared" si="57"/>
         <v>4</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I83" s="1" t="str">
         <f t="shared" si="56"/>
@@ -9872,7 +9911,7 @@
         <v>★★</v>
       </c>
       <c r="W83" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="84" spans="1:29">
@@ -9880,17 +9919,17 @@
         <v>7</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G84" s="18">
         <f t="shared" si="57"/>
         <v>5</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I84" s="1" t="str">
         <f t="shared" si="56"/>
@@ -9920,16 +9959,16 @@
         <v>★★★</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U84" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Y84" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AC84" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="85" spans="1:29">
@@ -9937,17 +9976,17 @@
         <v>7</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G85" s="18">
         <f t="shared" si="57"/>
         <v>6</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I85" s="1" t="str">
         <f t="shared" si="56"/>
@@ -9977,7 +10016,7 @@
         <v>★★</v>
       </c>
       <c r="AB85" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="86" spans="1:29">
@@ -9985,10 +10024,10 @@
         <v>7</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F86" s="2">
         <f>SUM(K86:K89)</f>
@@ -9999,7 +10038,7 @@
         <v>7</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I86" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10032,7 +10071,7 @@
         <v>24</v>
       </c>
       <c r="V86" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="87" spans="1:29">
@@ -10040,17 +10079,17 @@
         <v>7</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G87" s="18">
         <f t="shared" si="57"/>
         <v>8</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I87" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10080,10 +10119,10 @@
         <v>★★</v>
       </c>
       <c r="U87" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AC87" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="88" spans="1:29">
@@ -10091,17 +10130,17 @@
         <v>7</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G88" s="18">
         <f t="shared" si="57"/>
         <v>9</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I88" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10131,10 +10170,10 @@
         <v>★★★</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X88" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="89" spans="1:29">
@@ -10142,17 +10181,17 @@
         <v>7</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G89" s="18">
         <f t="shared" si="57"/>
         <v>10</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I89" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10182,10 +10221,10 @@
         <v>★★★</v>
       </c>
       <c r="S89" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="90" spans="1:29">
@@ -10193,13 +10232,13 @@
         <v>7</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F90" s="2">
         <f>SUM(K90:K94)</f>
@@ -10210,7 +10249,7 @@
         <v>11</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I90" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10248,16 +10287,16 @@
         <v>7</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G91" s="18">
         <v>12</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I91" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10287,7 +10326,7 @@
         <v>★★</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="92" spans="1:29">
@@ -10295,16 +10334,16 @@
         <v>7</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G92" s="18">
         <v>13</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I92" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10334,10 +10373,10 @@
         <v>★★</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="X92" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93" spans="1:29">
@@ -10345,16 +10384,16 @@
         <v>7</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G93" s="18">
         <v>14</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I93" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10384,13 +10423,13 @@
         <v>★★★★</v>
       </c>
       <c r="T93" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="W93" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AA93" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="94" spans="1:29">
@@ -10398,16 +10437,16 @@
         <v>7</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G94" s="18">
         <v>15</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I94" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10437,7 +10476,7 @@
         <v>★★</v>
       </c>
       <c r="X94" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="95" spans="1:29">
@@ -10445,10 +10484,10 @@
         <v>7</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F95" s="2">
         <f>SUM(K95:K105)</f>
@@ -10458,7 +10497,7 @@
         <v>16</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I95" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10488,10 +10527,10 @@
         <v>★★</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AC95" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="96" spans="1:29">
@@ -10499,16 +10538,16 @@
         <v>7</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G96" s="18">
         <v>17</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I96" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10538,7 +10577,7 @@
         <v>★</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:29">
@@ -10546,16 +10585,16 @@
         <v>7</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G97" s="18">
         <v>18</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I97" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10585,10 +10624,10 @@
         <v>★★★</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB97" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="98" spans="1:29">
@@ -10596,16 +10635,16 @@
         <v>7</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G98" s="18">
         <v>19</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I98" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10635,7 +10674,7 @@
         <v>★★</v>
       </c>
       <c r="U98" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:29">
@@ -10643,16 +10682,16 @@
         <v>7</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G99" s="18">
         <v>20</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I99" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10682,10 +10721,10 @@
         <v>★★★</v>
       </c>
       <c r="U99" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AA99" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="100" spans="1:29">
@@ -10693,16 +10732,16 @@
         <v>7</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G100" s="18">
         <v>21</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I100" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10732,7 +10771,7 @@
         <v>★★</v>
       </c>
       <c r="S100" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101" spans="1:29">
@@ -10740,16 +10779,16 @@
         <v>7</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G101" s="18">
         <v>22</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I101" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10779,10 +10818,10 @@
         <v>★★★</v>
       </c>
       <c r="T101" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="X101" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="102" spans="1:29">
@@ -10790,16 +10829,16 @@
         <v>7</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G102" s="18">
         <v>23</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I102" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10829,10 +10868,10 @@
         <v>★★★</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="X102" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="103" spans="1:29">
@@ -10840,16 +10879,16 @@
         <v>7</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G103" s="18">
         <v>24</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I103" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10879,10 +10918,10 @@
         <v>★★</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y103" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="104" spans="1:29">
@@ -10890,16 +10929,16 @@
         <v>7</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G104" s="18">
         <v>25</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I104" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10929,7 +10968,7 @@
         <v>★★</v>
       </c>
       <c r="V104" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="105" spans="1:29">
@@ -10937,16 +10976,16 @@
         <v>7</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C105" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G105" s="18">
         <v>26</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I105" s="1" t="str">
         <f t="shared" si="56"/>
@@ -10976,10 +11015,10 @@
         <v>★★★</v>
       </c>
       <c r="W105" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AA105" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="106" spans="1:29">
@@ -10987,13 +11026,13 @@
         <v>7</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F106" s="2">
         <f>SUM(K106:K112)</f>
@@ -11003,7 +11042,7 @@
         <v>27</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I106" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11036,10 +11075,10 @@
         <v>26</v>
       </c>
       <c r="T106" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="W106" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="107" spans="1:29">
@@ -11047,16 +11086,16 @@
         <v>7</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C107" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G107" s="18">
         <v>28</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I107" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11086,10 +11125,10 @@
         <v>★★</v>
       </c>
       <c r="S107" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AC107" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="108" spans="1:29">
@@ -11097,16 +11136,16 @@
         <v>7</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C108" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G108" s="18">
         <v>29</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I108" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11136,7 +11175,7 @@
         <v>★★</v>
       </c>
       <c r="Y108" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="109" spans="1:29">
@@ -11144,16 +11183,16 @@
         <v>7</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C109" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G109" s="18">
         <v>30</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I109" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11183,7 +11222,7 @@
         <v>★★</v>
       </c>
       <c r="Z109" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="110" spans="1:29">
@@ -11191,19 +11230,19 @@
         <v>7</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C110" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G110" s="18">
         <v>31</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I110" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11233,10 +11272,10 @@
         <v>★★★</v>
       </c>
       <c r="V110" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Z110" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="111" spans="1:29">
@@ -11244,16 +11283,16 @@
         <v>7</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C111" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G111" s="18">
         <v>32</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I111" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11283,13 +11322,13 @@
         <v>★★★★</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X111" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AA111" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="112" spans="1:29">
@@ -11297,16 +11336,16 @@
         <v>7</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C112" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G112" s="18">
         <v>33</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I112" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11336,10 +11375,10 @@
         <v>★★★</v>
       </c>
       <c r="U112" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AA112" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="113" spans="1:29">
@@ -11347,10 +11386,10 @@
         <v>7</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F113" s="2">
         <f>SUM(K113:K119)</f>
@@ -11360,7 +11399,7 @@
         <v>34</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I113" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11390,10 +11429,10 @@
         <v>★★★</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X113" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="114" spans="1:29">
@@ -11401,16 +11440,16 @@
         <v>7</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C114" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G114" s="18">
         <v>35</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I114" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11440,10 +11479,10 @@
         <v>★★★</v>
       </c>
       <c r="R114" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Z114" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="115" spans="1:29">
@@ -11451,16 +11490,16 @@
         <v>7</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G115" s="18">
         <v>36</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I115" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11490,10 +11529,10 @@
         <v>★★</v>
       </c>
       <c r="P115" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AB115" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="116" spans="1:29">
@@ -11501,16 +11540,16 @@
         <v>7</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G116" s="18">
         <v>37</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I116" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11543,7 +11582,7 @@
         <v>27</v>
       </c>
       <c r="Y116" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="117" spans="1:29">
@@ -11551,16 +11590,16 @@
         <v>7</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G117" s="18">
         <v>38</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I117" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11590,13 +11629,13 @@
         <v>★★★★</v>
       </c>
       <c r="T117" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AA117" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AB117" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="118" spans="1:29">
@@ -11604,16 +11643,16 @@
         <v>7</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G118" s="18">
         <v>39</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I118" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11643,10 +11682,10 @@
         <v>★★</v>
       </c>
       <c r="U118" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AC118" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="119" spans="1:29">
@@ -11654,16 +11693,16 @@
         <v>7</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C119" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G119" s="18">
         <v>40</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I119" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11693,7 +11732,7 @@
         <v>★★</v>
       </c>
       <c r="V119" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="120" spans="1:29">
@@ -11701,16 +11740,16 @@
         <v>7</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C120" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G120" s="18">
         <v>41</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I120" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11740,7 +11779,7 @@
         <v>★★</v>
       </c>
       <c r="AB120" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="121" spans="1:29">
@@ -11748,13 +11787,13 @@
         <v>7</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F121" s="2">
         <f>SUM(K121:K122)</f>
@@ -11764,7 +11803,7 @@
         <v>42</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I121" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11794,10 +11833,10 @@
         <v>★★★</v>
       </c>
       <c r="Q121" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U121" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="122" spans="1:29">
@@ -11805,7 +11844,7 @@
         <v>7</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C122" s="17" t="s">
         <v>8</v>
@@ -11814,7 +11853,7 @@
         <v>43</v>
       </c>
       <c r="H122" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I122" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11844,10 +11883,10 @@
         <v>★★★</v>
       </c>
       <c r="S122" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB122" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="123" spans="1:29">
@@ -11855,13 +11894,13 @@
         <v>7</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C123" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F123" s="2">
         <f>SUM(K123:K127)</f>
@@ -11871,7 +11910,7 @@
         <v>44</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I123" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11904,7 +11943,7 @@
         <v>28</v>
       </c>
       <c r="Y123" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="124" spans="1:29">
@@ -11912,7 +11951,7 @@
         <v>7</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C124" s="17" t="s">
         <v>8</v>
@@ -11921,7 +11960,7 @@
         <v>45</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I124" s="1" t="str">
         <f t="shared" si="56"/>
@@ -11951,10 +11990,10 @@
         <v>★★★</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="U124" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:29">
@@ -11962,7 +12001,7 @@
         <v>7</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C125" s="17" t="s">
         <v>8</v>
@@ -11971,7 +12010,7 @@
         <v>46</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I125" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12001,10 +12040,10 @@
         <v>★★★</v>
       </c>
       <c r="S125" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="V125" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="126" spans="1:29">
@@ -12012,7 +12051,7 @@
         <v>7</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C126" s="17" t="s">
         <v>8</v>
@@ -12021,14 +12060,14 @@
         <v>47</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="I126" s="1" t="str">
         <f t="shared" si="56"/>
         <v>A047</v>
       </c>
       <c r="J126" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K126" s="2">
         <f t="shared" si="67"/>
@@ -12051,16 +12090,16 @@
         <v>★★★</v>
       </c>
       <c r="P126" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X126" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Z126" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AC126" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="127" spans="1:29">
@@ -12068,7 +12107,7 @@
         <v>7</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C127" s="17" t="s">
         <v>8</v>
@@ -12077,7 +12116,7 @@
         <v>48</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I127" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12107,10 +12146,10 @@
         <v>★★★</v>
       </c>
       <c r="T127" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W127" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="1:29">
@@ -12118,7 +12157,7 @@
         <v>7</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C128" s="17" t="s">
         <v>8</v>
@@ -12127,7 +12166,7 @@
         <v>49</v>
       </c>
       <c r="H128" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I128" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12157,7 +12196,7 @@
         <v>★★</v>
       </c>
       <c r="AA128" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="129" spans="1:29">
@@ -12165,13 +12204,13 @@
         <v>7</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C129" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F129" s="2">
         <f>SUM(K129:K130)</f>
@@ -12181,7 +12220,7 @@
         <v>50</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I129" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12211,7 +12250,7 @@
         <v>★★</v>
       </c>
       <c r="T129" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="130" spans="1:29">
@@ -12219,7 +12258,7 @@
         <v>7</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C130" s="17" t="s">
         <v>8</v>
@@ -12228,7 +12267,7 @@
         <v>51</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I130" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12258,7 +12297,7 @@
         <v>★★</v>
       </c>
       <c r="U130" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="131" spans="1:29">
@@ -12266,7 +12305,7 @@
         <v>7</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C131" s="17" t="s">
         <v>8</v>
@@ -12275,7 +12314,7 @@
         <v>52</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I131" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12305,7 +12344,7 @@
         <v>★★</v>
       </c>
       <c r="Z131" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="132" spans="1:29">
@@ -12313,7 +12352,7 @@
         <v>7</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>9</v>
@@ -12326,7 +12365,7 @@
         <v>53</v>
       </c>
       <c r="H132" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I132" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12359,10 +12398,10 @@
         <v>29</v>
       </c>
       <c r="U132" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Y132" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="133" spans="1:29">
@@ -12370,7 +12409,7 @@
         <v>7</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C133" s="17" t="s">
         <v>9</v>
@@ -12379,7 +12418,7 @@
         <v>54</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I133" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12417,7 +12456,7 @@
         <v>7</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C134" s="17" t="s">
         <v>9</v>
@@ -12426,7 +12465,7 @@
         <v>55</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I134" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12456,7 +12495,7 @@
         <v>★★</v>
       </c>
       <c r="V134" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="135" spans="1:29">
@@ -12464,7 +12503,7 @@
         <v>7</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C135" s="17" t="s">
         <v>9</v>
@@ -12473,7 +12512,7 @@
         <v>56</v>
       </c>
       <c r="H135" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I135" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12503,16 +12542,16 @@
         <v>★★★</v>
       </c>
       <c r="P135" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S135" s="1" t="s">
         <v>33</v>
       </c>
       <c r="Z135" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AC135" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="136" spans="1:29">
@@ -12520,7 +12559,7 @@
         <v>7</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C136" s="17" t="s">
         <v>9</v>
@@ -12529,7 +12568,7 @@
         <v>57</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I136" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12559,10 +12598,10 @@
         <v>★★★</v>
       </c>
       <c r="T136" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AA136" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="137" spans="1:29">
@@ -12570,13 +12609,13 @@
         <v>7</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F137" s="2">
         <f>SUM(K137:K141)</f>
@@ -12586,7 +12625,7 @@
         <v>58</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I137" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12619,7 +12658,7 @@
         <v>30</v>
       </c>
       <c r="T137" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="138" spans="1:29">
@@ -12627,7 +12666,7 @@
         <v>7</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C138" s="17" t="s">
         <v>10</v>
@@ -12636,14 +12675,14 @@
         <v>59</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I138" s="1" t="str">
         <f t="shared" si="56"/>
         <v>A059</v>
       </c>
       <c r="J138" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K138" s="2">
         <f t="shared" si="67"/>
@@ -12666,13 +12705,13 @@
         <v>★★</v>
       </c>
       <c r="P138" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AC138" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="139" spans="1:29">
@@ -12680,7 +12719,7 @@
         <v>7</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C139" s="17" t="s">
         <v>10</v>
@@ -12689,7 +12728,7 @@
         <v>60</v>
       </c>
       <c r="H139" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I139" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12719,10 +12758,10 @@
         <v>★★★</v>
       </c>
       <c r="S139" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V139" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="140" spans="1:29">
@@ -12730,7 +12769,7 @@
         <v>7</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C140" s="17" t="s">
         <v>10</v>
@@ -12739,7 +12778,7 @@
         <v>61</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I140" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12769,7 +12808,7 @@
         <v>★★</v>
       </c>
       <c r="Y140" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="141" spans="1:29">
@@ -12777,7 +12816,7 @@
         <v>7</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C141" s="17" t="s">
         <v>10</v>
@@ -12786,7 +12825,7 @@
         <v>62</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I141" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12816,7 +12855,7 @@
         <v>★★</v>
       </c>
       <c r="W141" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="142" spans="1:29">
@@ -12824,13 +12863,13 @@
         <v>7</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C142" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F142" s="2">
         <f>SUM(K142:K146)</f>
@@ -12840,7 +12879,7 @@
         <v>63</v>
       </c>
       <c r="H142" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I142" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12870,13 +12909,13 @@
         <v>★★★★</v>
       </c>
       <c r="Q142" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W142" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AB142" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="143" spans="1:29">
@@ -12884,7 +12923,7 @@
         <v>7</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C143" s="17" t="s">
         <v>10</v>
@@ -12893,7 +12932,7 @@
         <v>64</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I143" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12923,13 +12962,13 @@
         <v>★★★</v>
       </c>
       <c r="R143" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Y143" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AC143" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="144" spans="1:29">
@@ -12937,7 +12976,7 @@
         <v>7</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C144" s="17" t="s">
         <v>10</v>
@@ -12946,7 +12985,7 @@
         <v>65</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I144" s="1" t="str">
         <f t="shared" si="56"/>
@@ -12976,7 +13015,7 @@
         <v>★★</v>
       </c>
       <c r="U144" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="145" spans="1:29">
@@ -12984,7 +13023,7 @@
         <v>7</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C145" s="17" t="s">
         <v>10</v>
@@ -12993,7 +13032,7 @@
         <v>66</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I145" s="1" t="str">
         <f t="shared" ref="I145:I208" si="89">B145&amp;TEXT(G145,"000")</f>
@@ -13023,10 +13062,10 @@
         <v>★★★</v>
       </c>
       <c r="X145" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AA145" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="146" spans="1:29">
@@ -13034,7 +13073,7 @@
         <v>7</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C146" s="17" t="s">
         <v>10</v>
@@ -13043,7 +13082,7 @@
         <v>67</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I146" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13073,10 +13112,10 @@
         <v>★★★</v>
       </c>
       <c r="S146" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB146" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="147" spans="1:29">
@@ -13084,13 +13123,13 @@
         <v>7</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C147" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F147" s="2">
         <f>SUM(K147:K150)</f>
@@ -13100,7 +13139,7 @@
         <v>68</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I147" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13130,10 +13169,10 @@
         <v>★★</v>
       </c>
       <c r="P147" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AA147" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="148" spans="1:29">
@@ -13141,7 +13180,7 @@
         <v>7</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C148" s="17" t="s">
         <v>10</v>
@@ -13150,7 +13189,7 @@
         <v>69</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I148" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13180,13 +13219,13 @@
         <v>★★★★</v>
       </c>
       <c r="T148" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="W148" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Z148" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="149" spans="1:29">
@@ -13194,7 +13233,7 @@
         <v>7</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C149" s="17" t="s">
         <v>10</v>
@@ -13203,7 +13242,7 @@
         <v>70</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I149" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13233,13 +13272,13 @@
         <v>★★★★</v>
       </c>
       <c r="U149" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="X149" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AB149" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="150" spans="1:29">
@@ -13247,7 +13286,7 @@
         <v>7</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C150" s="17" t="s">
         <v>10</v>
@@ -13256,7 +13295,7 @@
         <v>71</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I150" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13286,10 +13325,10 @@
         <v>★★★</v>
       </c>
       <c r="V150" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Z150" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="151" spans="1:29">
@@ -13297,13 +13336,13 @@
         <v>31</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F151" s="2">
         <f>SUM(K151:K159)</f>
@@ -13313,7 +13352,7 @@
         <v>1</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I151" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13346,7 +13385,7 @@
         <v>33</v>
       </c>
       <c r="X151" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:29">
@@ -13354,7 +13393,7 @@
         <v>31</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C152" s="17" t="s">
         <v>32</v>
@@ -13363,7 +13402,7 @@
         <v>2</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I152" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13393,7 +13432,7 @@
         <v>★</v>
       </c>
       <c r="P152" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="153" spans="1:29">
@@ -13401,7 +13440,7 @@
         <v>31</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C153" s="17" t="s">
         <v>32</v>
@@ -13410,7 +13449,7 @@
         <v>3</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I153" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13440,7 +13479,7 @@
         <v>★★</v>
       </c>
       <c r="W153" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="154" spans="1:29">
@@ -13448,7 +13487,7 @@
         <v>31</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C154" s="17" t="s">
         <v>32</v>
@@ -13457,7 +13496,7 @@
         <v>4</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I154" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13495,7 +13534,7 @@
         <v>31</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C155" s="17" t="s">
         <v>32</v>
@@ -13504,7 +13543,7 @@
         <v>5</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I155" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13537,7 +13576,7 @@
         <v>36</v>
       </c>
       <c r="U155" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="156" spans="1:29">
@@ -13545,7 +13584,7 @@
         <v>31</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C156" s="17" t="s">
         <v>32</v>
@@ -13554,7 +13593,7 @@
         <v>6</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I156" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13592,7 +13631,7 @@
         <v>31</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C157" s="17" t="s">
         <v>32</v>
@@ -13601,7 +13640,7 @@
         <v>7</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="I157" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13631,7 +13670,7 @@
         <v>★</v>
       </c>
       <c r="AC157" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="158" spans="1:29">
@@ -13639,7 +13678,7 @@
         <v>31</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C158" s="17" t="s">
         <v>32</v>
@@ -13648,7 +13687,7 @@
         <v>8</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I158" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13681,7 +13720,7 @@
         <v>36</v>
       </c>
       <c r="V158" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="159" spans="1:29">
@@ -13689,7 +13728,7 @@
         <v>31</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C159" s="17" t="s">
         <v>32</v>
@@ -13698,7 +13737,7 @@
         <v>9</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I159" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13728,7 +13767,7 @@
         <v>★★</v>
       </c>
       <c r="U159" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="160" spans="1:29">
@@ -13736,7 +13775,7 @@
         <v>31</v>
       </c>
       <c r="B160" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C160" s="17" t="s">
         <v>32</v>
@@ -13745,7 +13784,7 @@
         <v>10</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I160" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13775,21 +13814,21 @@
         <v>★★</v>
       </c>
       <c r="AB160" s="1" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="161" spans="1:29">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="161" spans="1:32">
       <c r="A161" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B161" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C161" s="17" t="s">
         <v>32</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F161" s="2">
         <f>SUM(K161:K164)</f>
@@ -13799,7 +13838,7 @@
         <v>11</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I161" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13829,18 +13868,18 @@
         <v>★★</v>
       </c>
       <c r="P161" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AB161" s="1" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="162" spans="1:29">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="162" spans="1:32">
       <c r="A162" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C162" s="17" t="s">
         <v>32</v>
@@ -13849,7 +13888,7 @@
         <v>12</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="I162" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13879,15 +13918,15 @@
         <v>★★</v>
       </c>
       <c r="T162" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="163" spans="1:29">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="163" spans="1:32">
       <c r="A163" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C163" s="17" t="s">
         <v>32</v>
@@ -13896,7 +13935,7 @@
         <v>13</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I163" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13926,15 +13965,15 @@
         <v>★★</v>
       </c>
       <c r="AA163" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="164" spans="1:29">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="164" spans="1:32">
       <c r="A164" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B164" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C164" s="17" t="s">
         <v>32</v>
@@ -13943,7 +13982,7 @@
         <v>14</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I164" s="1" t="str">
         <f t="shared" si="89"/>
@@ -13973,18 +14012,18 @@
         <v>★★</v>
       </c>
       <c r="X164" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AC164" s="1" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="165" spans="1:29">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="165" spans="1:32">
       <c r="A165" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C165" s="17" t="s">
         <v>32</v>
@@ -13993,7 +14032,7 @@
         <v>15</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I165" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14023,15 +14062,15 @@
         <v>★★</v>
       </c>
       <c r="Y165" s="1" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="166" spans="1:29">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="166" spans="1:32">
       <c r="A166" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C166" s="17" t="s">
         <v>32</v>
@@ -14040,7 +14079,7 @@
         <v>16</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I166" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14070,34 +14109,34 @@
         <v>★★★</v>
       </c>
       <c r="Z166" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AA166" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="167" spans="1:29">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="167" spans="1:32">
       <c r="A167" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B167" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F167" s="2">
         <f>SUM(K167:K172)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G167" s="18">
         <v>17</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I167" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14108,11 +14147,11 @@
       </c>
       <c r="K167" s="2">
         <f t="shared" si="97"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L167" s="2">
         <f t="shared" si="98"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M167" s="2" cm="1">
         <f t="array" ref="M167">MATCH(TRUE,P167:AD167&lt;&gt;"",0)-1</f>
@@ -14133,10 +14172,10 @@
         <v>42</v>
       </c>
       <c r="V167" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="W167" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="X167" s="1" t="s">
         <v>35</v>
@@ -14144,13 +14183,16 @@
       <c r="Y167" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="168" spans="1:29">
+      <c r="AF167" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="168" spans="1:32">
       <c r="A168" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B168" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C168" s="17" t="s">
         <v>34</v>
@@ -14159,7 +14201,7 @@
         <v>18</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="I168" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14189,15 +14231,15 @@
         <v>★★</v>
       </c>
       <c r="Z168" s="1" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="169" spans="1:29">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="169" spans="1:32">
       <c r="A169" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C169" s="17" t="s">
         <v>34</v>
@@ -14206,7 +14248,7 @@
         <v>19</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I169" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14239,15 +14281,15 @@
         <v>36</v>
       </c>
       <c r="AA169" s="1" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="170" spans="1:29">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="170" spans="1:32">
       <c r="A170" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C170" s="17" t="s">
         <v>34</v>
@@ -14256,7 +14298,7 @@
         <v>20</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I170" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14286,21 +14328,21 @@
         <v>★★★</v>
       </c>
       <c r="P170" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T170" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AB170" s="1" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="171" spans="1:29">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="171" spans="1:32">
       <c r="A171" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C171" s="17" t="s">
         <v>34</v>
@@ -14309,7 +14351,7 @@
         <v>21</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I171" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14339,15 +14381,15 @@
         <v>★★</v>
       </c>
       <c r="U171" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="172" spans="1:29">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="172" spans="1:32">
       <c r="A172" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C172" s="17" t="s">
         <v>34</v>
@@ -14356,7 +14398,7 @@
         <v>22</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I172" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14386,18 +14428,18 @@
         <v>★★★</v>
       </c>
       <c r="V172" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Z172" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="173" spans="1:29">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="173" spans="1:32">
       <c r="A173" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C173" s="17" t="s">
         <v>34</v>
@@ -14406,7 +14448,7 @@
         <v>23</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="I173" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14436,21 +14478,21 @@
         <v>★</v>
       </c>
       <c r="AC173" s="1" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="174" spans="1:29">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="174" spans="1:32">
       <c r="A174" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C174" s="17" t="s">
         <v>34</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F174" s="2">
         <f>SUM(K174:K176)</f>
@@ -14460,7 +14502,7 @@
         <v>24</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I174" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14490,18 +14532,18 @@
         <v>★★★</v>
       </c>
       <c r="R174" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W174" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="175" spans="1:29">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="175" spans="1:32">
       <c r="A175" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B175" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C175" s="17" t="s">
         <v>34</v>
@@ -14510,7 +14552,7 @@
         <v>25</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I175" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14543,15 +14585,15 @@
         <v>38</v>
       </c>
       <c r="Y175" s="1" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="176" spans="1:29">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="176" spans="1:32">
       <c r="A176" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C176" s="17" t="s">
         <v>34</v>
@@ -14560,7 +14602,7 @@
         <v>26</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I176" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14590,7 +14632,7 @@
         <v>★★</v>
       </c>
       <c r="V176" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="177" spans="1:29">
@@ -14598,13 +14640,13 @@
         <v>31</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F177" s="2">
         <f>SUM(K177:K178)</f>
@@ -14614,7 +14656,7 @@
         <v>27</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I177" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14644,7 +14686,7 @@
         <v>★★★★★</v>
       </c>
       <c r="P177" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q177" s="1" t="s">
         <v>38</v>
@@ -14653,13 +14695,13 @@
         <v>41</v>
       </c>
       <c r="Y177" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="Z177" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AC177" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="178" spans="1:29">
@@ -14667,7 +14709,7 @@
         <v>31</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C178" s="17" t="s">
         <v>37</v>
@@ -14676,7 +14718,7 @@
         <v>28</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I178" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14706,10 +14748,10 @@
         <v>★★★</v>
       </c>
       <c r="V178" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AA178" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="179" spans="1:29">
@@ -14717,13 +14759,13 @@
         <v>31</v>
       </c>
       <c r="B179" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C179" s="17" t="s">
         <v>37</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F179" s="2">
         <f>SUM(K179:K181)</f>
@@ -14733,7 +14775,7 @@
         <v>29</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I179" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14766,10 +14808,10 @@
         <v>39</v>
       </c>
       <c r="W179" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AB179" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="180" spans="1:29">
@@ -14777,7 +14819,7 @@
         <v>31</v>
       </c>
       <c r="B180" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C180" s="17" t="s">
         <v>37</v>
@@ -14786,7 +14828,7 @@
         <v>30</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I180" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14816,10 +14858,10 @@
         <v>★★★</v>
       </c>
       <c r="U180" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X180" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="181" spans="1:29">
@@ -14827,7 +14869,7 @@
         <v>31</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C181" s="17" t="s">
         <v>37</v>
@@ -14836,7 +14878,7 @@
         <v>31</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I181" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14866,16 +14908,16 @@
         <v>★★★★</v>
       </c>
       <c r="P181" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T181" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="V181" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Z181" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="182" spans="1:29">
@@ -14883,13 +14925,13 @@
         <v>31</v>
       </c>
       <c r="B182" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C182" s="17" t="s">
         <v>37</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F182" s="2">
         <f>SUM(K182:K189)</f>
@@ -14899,7 +14941,7 @@
         <v>32</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I182" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14935,13 +14977,13 @@
         <v>39</v>
       </c>
       <c r="X182" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y182" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AC182" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="183" spans="1:29">
@@ -14949,7 +14991,7 @@
         <v>31</v>
       </c>
       <c r="B183" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C183" s="17" t="s">
         <v>37</v>
@@ -14958,7 +15000,7 @@
         <v>33</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I183" s="1" t="str">
         <f t="shared" si="89"/>
@@ -14991,7 +15033,7 @@
         <v>38</v>
       </c>
       <c r="U183" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="184" spans="1:29">
@@ -14999,7 +15041,7 @@
         <v>31</v>
       </c>
       <c r="B184" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C184" s="17" t="s">
         <v>37</v>
@@ -15008,7 +15050,7 @@
         <v>34</v>
       </c>
       <c r="H184" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I184" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15038,13 +15080,13 @@
         <v>★★</v>
       </c>
       <c r="P184" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V184" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AC184" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="185" spans="1:29">
@@ -15052,7 +15094,7 @@
         <v>31</v>
       </c>
       <c r="B185" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C185" s="17" t="s">
         <v>37</v>
@@ -15061,7 +15103,7 @@
         <v>35</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I185" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15091,7 +15133,7 @@
         <v>★★</v>
       </c>
       <c r="R185" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="186" spans="1:29">
@@ -15099,7 +15141,7 @@
         <v>31</v>
       </c>
       <c r="B186" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C186" s="17" t="s">
         <v>37</v>
@@ -15108,7 +15150,7 @@
         <v>36</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I186" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15138,13 +15180,13 @@
         <v>★★★★</v>
       </c>
       <c r="S186" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X186" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Z186" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="187" spans="1:29">
@@ -15152,7 +15194,7 @@
         <v>31</v>
       </c>
       <c r="B187" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C187" s="17" t="s">
         <v>37</v>
@@ -15161,7 +15203,7 @@
         <v>37</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="I187" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15191,7 +15233,7 @@
         <v>★★</v>
       </c>
       <c r="T187" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="188" spans="1:29">
@@ -15199,7 +15241,7 @@
         <v>31</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C188" s="17" t="s">
         <v>37</v>
@@ -15208,7 +15250,7 @@
         <v>38</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="I188" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15238,7 +15280,7 @@
         <v>★★</v>
       </c>
       <c r="Y188" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="189" spans="1:29">
@@ -15246,19 +15288,19 @@
         <v>31</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C189" s="17" t="s">
         <v>37</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G189" s="18">
         <v>39</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I189" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15288,7 +15330,7 @@
         <v>★★</v>
       </c>
       <c r="W189" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="190" spans="1:29">
@@ -15296,7 +15338,7 @@
         <v>31</v>
       </c>
       <c r="B190" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C190" s="17" t="s">
         <v>37</v>
@@ -15305,7 +15347,7 @@
         <v>40</v>
       </c>
       <c r="H190" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I190" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15335,7 +15377,7 @@
         <v>★★</v>
       </c>
       <c r="AB190" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="191" spans="1:29">
@@ -15343,7 +15385,7 @@
         <v>31</v>
       </c>
       <c r="B191" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C191" s="17" t="s">
         <v>37</v>
@@ -15352,7 +15394,7 @@
         <v>41</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I191" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15382,18 +15424,18 @@
         <v>★★</v>
       </c>
       <c r="AA191" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="192" spans="1:29">
       <c r="A192" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B192" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="F192" s="2">
         <f>SUM(K192:K205)</f>
@@ -15403,7 +15445,7 @@
         <v>1</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I192" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15436,27 +15478,27 @@
         <v>41</v>
       </c>
       <c r="T192" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y192" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="193" spans="1:29">
       <c r="A193" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B193" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C193" s="17" t="s">
         <v>601</v>
       </c>
-      <c r="C193" s="17" t="s">
-        <v>602</v>
-      </c>
       <c r="G193" s="18">
         <v>2</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I193" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15489,24 +15531,24 @@
         <v>41</v>
       </c>
       <c r="AB193" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="194" spans="1:29">
       <c r="A194" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B194" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C194" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C194" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G194" s="18">
         <v>3</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I194" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15536,31 +15578,31 @@
         <v>★★</v>
       </c>
       <c r="X194" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="195" spans="1:29">
       <c r="A195" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B195" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C195" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C195" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G195" s="18">
         <v>4</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I195" s="1" t="str">
         <f t="shared" si="89"/>
         <v>S004</v>
       </c>
       <c r="J195" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K195" s="2">
         <f t="shared" si="97"/>
@@ -15583,30 +15625,30 @@
         <v>★★★</v>
       </c>
       <c r="P195" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="W195" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Z195" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="196" spans="1:29">
       <c r="A196" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B196" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C196" s="17" t="s">
         <v>601</v>
       </c>
-      <c r="C196" s="17" t="s">
-        <v>602</v>
-      </c>
       <c r="G196" s="18">
         <v>5</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I196" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15636,24 +15678,24 @@
         <v>★★</v>
       </c>
       <c r="AA196" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="197" spans="1:29">
       <c r="A197" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B197" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C197" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C197" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G197" s="18">
         <v>6</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I197" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15683,24 +15725,24 @@
         <v>★</v>
       </c>
       <c r="P197" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="198" spans="1:29">
       <c r="A198" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B198" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C198" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C198" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G198" s="18">
         <v>7</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="I198" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15730,24 +15772,24 @@
         <v>★★</v>
       </c>
       <c r="AB198" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="199" spans="1:29">
       <c r="A199" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B199" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C199" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C199" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G199" s="18">
         <v>8</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="I199" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15777,24 +15819,24 @@
         <v>★</v>
       </c>
       <c r="AC199" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="200" spans="1:29">
       <c r="A200" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B200" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C200" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C200" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G200" s="18">
         <v>9</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I200" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15827,27 +15869,27 @@
         <v>35</v>
       </c>
       <c r="U200" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Y200" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="201" spans="1:29">
       <c r="A201" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B201" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C201" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C201" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G201" s="18">
         <v>10</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I201" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15877,24 +15919,24 @@
         <v>★★</v>
       </c>
       <c r="U201" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="202" spans="1:29">
       <c r="A202" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B202" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C202" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C202" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G202" s="18">
         <v>11</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I202" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15924,24 +15966,24 @@
         <v>★★</v>
       </c>
       <c r="U202" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="203" spans="1:29">
       <c r="A203" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B203" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C203" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C203" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G203" s="18">
         <v>12</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I203" s="1" t="str">
         <f t="shared" si="89"/>
@@ -15971,27 +16013,27 @@
         <v>★★</v>
       </c>
       <c r="W203" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AC203" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="204" spans="1:29">
       <c r="A204" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B204" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C204" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C204" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G204" s="18">
         <v>13</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I204" s="1" t="str">
         <f t="shared" si="89"/>
@@ -16021,24 +16063,24 @@
         <v>★★</v>
       </c>
       <c r="X204" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="205" spans="1:29">
       <c r="A205" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B205" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C205" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C205" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G205" s="18">
         <v>14</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I205" s="1" t="str">
         <f t="shared" si="89"/>
@@ -16068,24 +16110,24 @@
         <v>★★</v>
       </c>
       <c r="W205" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="206" spans="1:29">
       <c r="A206" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B206" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="C206" s="17" t="s">
         <v>601</v>
-      </c>
-      <c r="C206" s="17" t="s">
-        <v>602</v>
       </c>
       <c r="G206" s="18">
         <v>15</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I206" s="1" t="str">
         <f t="shared" si="89"/>
@@ -16115,18 +16157,18 @@
         <v>★</v>
       </c>
       <c r="AC206" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="207" spans="1:29">
       <c r="A207" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B207" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F207" s="2">
         <f>SUM(K207:K212)</f>
@@ -16136,7 +16178,7 @@
         <v>16</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I207" s="1" t="str">
         <f t="shared" si="89"/>
@@ -16169,24 +16211,24 @@
         <v>40</v>
       </c>
       <c r="Y207" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="208" spans="1:29">
       <c r="A208" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B208" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C208" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G208" s="18">
         <v>17</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I208" s="1" t="str">
         <f t="shared" si="89"/>
@@ -16221,19 +16263,19 @@
     </row>
     <row r="209" spans="1:30">
       <c r="A209" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B209" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C209" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G209" s="18">
         <v>18</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I209" s="1" t="str">
         <f t="shared" ref="I209:I215" si="137">B209&amp;TEXT(G209,"000")</f>
@@ -16266,30 +16308,30 @@
         <v>42</v>
       </c>
       <c r="T209" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="X209" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AA209" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="210" spans="1:30">
       <c r="A210" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B210" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C210" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G210" s="18">
         <v>19</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I210" s="1" t="str">
         <f t="shared" si="137"/>
@@ -16319,30 +16361,30 @@
         <v>★★★★</v>
       </c>
       <c r="S210" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V210" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Z210" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="211" spans="1:30">
       <c r="A211" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B211" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C211" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G211" s="18">
         <v>20</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I211" s="1" t="str">
         <f t="shared" si="137"/>
@@ -16372,30 +16414,30 @@
         <v>★★★</v>
       </c>
       <c r="P211" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T211" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AA211" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="212" spans="1:30">
       <c r="A212" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B212" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C212" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G212" s="18">
         <v>21</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I212" s="1" t="str">
         <f t="shared" si="137"/>
@@ -16425,18 +16467,18 @@
         <v>★★</v>
       </c>
       <c r="V212" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="213" spans="1:30">
       <c r="A213" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B213" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F213" s="2">
         <f>SUM(K213:K215)</f>
@@ -16446,7 +16488,7 @@
         <v>22</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I213" s="1" t="str">
         <f t="shared" si="137"/>
@@ -16481,19 +16523,19 @@
     </row>
     <row r="214" spans="1:30">
       <c r="A214" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B214" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C214" s="17" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G214" s="18">
         <v>23</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I214" s="1" t="str">
         <f t="shared" si="137"/>
@@ -16523,30 +16565,30 @@
         <v>★★★★</v>
       </c>
       <c r="Q214" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z214" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AB214" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="215" spans="1:30">
       <c r="A215" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B215" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C215" s="17" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G215" s="18">
         <v>24</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I215" s="1" t="str">
         <f t="shared" si="137"/>
@@ -16576,7 +16618,7 @@
         <v>★★</v>
       </c>
       <c r="Z215" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="216" spans="1:30">
@@ -16613,12 +16655,12 @@
     </row>
     <row r="218" spans="1:30">
       <c r="N218" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="219" spans="1:30" hidden="1">
       <c r="L219" s="12" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="M219" s="2">
         <f>COUNTIF(O$219:O$435,"★")</f>
@@ -16629,12 +16671,12 @@
         <v>100</v>
       </c>
       <c r="O219" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="220" spans="1:30" hidden="1">
       <c r="L220" s="12" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="M220" s="2">
         <f>COUNTIF(O$219:O$435,"★★")</f>
@@ -16645,12 +16687,12 @@
         <v>94.444444444444443</v>
       </c>
       <c r="O220" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="221" spans="1:30" hidden="1">
       <c r="L221" s="12" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M221" s="2">
         <f>COUNTIF(O$219:O$435,"★★★")</f>
@@ -16661,12 +16703,12 @@
         <v>48.148148148148145</v>
       </c>
       <c r="O221" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="222" spans="1:30" hidden="1">
       <c r="L222" s="12" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="M222" s="2">
         <f>COUNTIF(O$219:O$435,"★★★★")</f>
@@ -16677,12 +16719,12 @@
         <v>16.203703703703702</v>
       </c>
       <c r="O222" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="223" spans="1:30" hidden="1">
       <c r="L223" s="12" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="M223" s="2">
         <f>COUNTIF(O$219:O$435,"★★★★★")</f>
@@ -16693,7 +16735,7 @@
         <v>3.7037037037037033</v>
       </c>
       <c r="O223" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="224" spans="1:30" hidden="1">
@@ -16702,1057 +16744,1057 @@
         <v>216</v>
       </c>
       <c r="O224" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="225" spans="15:15" hidden="1">
       <c r="O225" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="226" spans="15:15" hidden="1">
       <c r="O226" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="227" spans="15:15" hidden="1">
       <c r="O227" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="228" spans="15:15" hidden="1">
       <c r="O228" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="229" spans="15:15" hidden="1">
       <c r="O229" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="230" spans="15:15" hidden="1">
       <c r="O230" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="231" spans="15:15" hidden="1">
       <c r="O231" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="232" spans="15:15" hidden="1">
       <c r="O232" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="233" spans="15:15" hidden="1">
       <c r="O233" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="234" spans="15:15" hidden="1">
       <c r="O234" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="235" spans="15:15" hidden="1">
       <c r="O235" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="236" spans="15:15" hidden="1">
       <c r="O236" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="237" spans="15:15" hidden="1">
       <c r="O237" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="238" spans="15:15" hidden="1">
       <c r="O238" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="239" spans="15:15" hidden="1">
       <c r="O239" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="240" spans="15:15" hidden="1">
       <c r="O240" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="241" spans="15:15" hidden="1">
       <c r="O241" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="242" spans="15:15" hidden="1">
       <c r="O242" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="243" spans="15:15" hidden="1">
       <c r="O243" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="244" spans="15:15" hidden="1">
       <c r="O244" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="245" spans="15:15" hidden="1">
       <c r="O245" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="246" spans="15:15" hidden="1">
       <c r="O246" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="247" spans="15:15" hidden="1">
       <c r="O247" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="248" spans="15:15" hidden="1">
       <c r="O248" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="249" spans="15:15" hidden="1">
       <c r="O249" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="250" spans="15:15" hidden="1">
       <c r="O250" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="251" spans="15:15" hidden="1">
       <c r="O251" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="252" spans="15:15" hidden="1">
       <c r="O252" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="253" spans="15:15" hidden="1">
       <c r="O253" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="254" spans="15:15" hidden="1">
       <c r="O254" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="255" spans="15:15" hidden="1">
       <c r="O255" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="256" spans="15:15" hidden="1">
       <c r="O256" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="257" spans="15:15" hidden="1">
       <c r="O257" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="258" spans="15:15" hidden="1">
       <c r="O258" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="259" spans="15:15" hidden="1">
       <c r="O259" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="260" spans="15:15" hidden="1">
       <c r="O260" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="261" spans="15:15" hidden="1">
       <c r="O261" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="262" spans="15:15" hidden="1">
       <c r="O262" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="263" spans="15:15" hidden="1">
       <c r="O263" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="264" spans="15:15" hidden="1">
       <c r="O264" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="265" spans="15:15" hidden="1">
       <c r="O265" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="266" spans="15:15" hidden="1">
       <c r="O266" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="267" spans="15:15" hidden="1">
       <c r="O267" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="268" spans="15:15" hidden="1">
       <c r="O268" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="269" spans="15:15" hidden="1">
       <c r="O269" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="270" spans="15:15" hidden="1">
       <c r="O270" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="271" spans="15:15" hidden="1">
       <c r="O271" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="272" spans="15:15" hidden="1">
       <c r="O272" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="273" spans="15:15" hidden="1">
       <c r="O273" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="274" spans="15:15" hidden="1">
       <c r="O274" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="275" spans="15:15" hidden="1">
       <c r="O275" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="276" spans="15:15" hidden="1">
       <c r="O276" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="277" spans="15:15" hidden="1">
       <c r="O277" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="278" spans="15:15" hidden="1">
       <c r="O278" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="279" spans="15:15" hidden="1">
       <c r="O279" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="280" spans="15:15" hidden="1">
       <c r="O280" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="281" spans="15:15" hidden="1">
       <c r="O281" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="282" spans="15:15" hidden="1">
       <c r="O282" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="283" spans="15:15" hidden="1">
       <c r="O283" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="284" spans="15:15" hidden="1">
       <c r="O284" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="285" spans="15:15" hidden="1">
       <c r="O285" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="286" spans="15:15" hidden="1">
       <c r="O286" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="287" spans="15:15" hidden="1">
       <c r="O287" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="288" spans="15:15" hidden="1">
       <c r="O288" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="289" spans="15:15" hidden="1">
       <c r="O289" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="290" spans="15:15" hidden="1">
       <c r="O290" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="291" spans="15:15" hidden="1">
       <c r="O291" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="292" spans="15:15" hidden="1">
       <c r="O292" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="293" spans="15:15" hidden="1">
       <c r="O293" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="294" spans="15:15" hidden="1">
       <c r="O294" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="295" spans="15:15" hidden="1">
       <c r="O295" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="296" spans="15:15" hidden="1">
       <c r="O296" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="297" spans="15:15" hidden="1">
       <c r="O297" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="298" spans="15:15" hidden="1">
       <c r="O298" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="299" spans="15:15" hidden="1">
       <c r="O299" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="300" spans="15:15" hidden="1">
       <c r="O300" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="301" spans="15:15" hidden="1">
       <c r="O301" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="302" spans="15:15" hidden="1">
       <c r="O302" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="303" spans="15:15" hidden="1">
       <c r="O303" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="304" spans="15:15" hidden="1">
       <c r="O304" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="305" spans="15:15" hidden="1">
       <c r="O305" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="306" spans="15:15" hidden="1">
       <c r="O306" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="307" spans="15:15" hidden="1">
       <c r="O307" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="308" spans="15:15" hidden="1">
       <c r="O308" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="309" spans="15:15" hidden="1">
       <c r="O309" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="310" spans="15:15" hidden="1">
       <c r="O310" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="311" spans="15:15" hidden="1">
       <c r="O311" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="312" spans="15:15" hidden="1">
       <c r="O312" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="313" spans="15:15" hidden="1">
       <c r="O313" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="314" spans="15:15" hidden="1">
       <c r="O314" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="315" spans="15:15" hidden="1">
       <c r="O315" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="316" spans="15:15" hidden="1">
       <c r="O316" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="317" spans="15:15" hidden="1">
       <c r="O317" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="318" spans="15:15" hidden="1">
       <c r="O318" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="319" spans="15:15" hidden="1">
       <c r="O319" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="320" spans="15:15" hidden="1">
       <c r="O320" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="321" spans="15:15" hidden="1">
       <c r="O321" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="322" spans="15:15" hidden="1">
       <c r="O322" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="323" spans="15:15" hidden="1">
       <c r="O323" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="324" spans="15:15" hidden="1">
       <c r="O324" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="325" spans="15:15" hidden="1">
       <c r="O325" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="326" spans="15:15" hidden="1">
       <c r="O326" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="327" spans="15:15" hidden="1">
       <c r="O327" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="328" spans="15:15" hidden="1">
       <c r="O328" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="329" spans="15:15" hidden="1">
       <c r="O329" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="330" spans="15:15" hidden="1">
       <c r="O330" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="331" spans="15:15" hidden="1">
       <c r="O331" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="332" spans="15:15" hidden="1">
       <c r="O332" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="333" spans="15:15" hidden="1">
       <c r="O333" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="334" spans="15:15" hidden="1">
       <c r="O334" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="335" spans="15:15" hidden="1">
       <c r="O335" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="336" spans="15:15" hidden="1">
       <c r="O336" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="337" spans="15:15" hidden="1">
       <c r="O337" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="338" spans="15:15" hidden="1">
       <c r="O338" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="339" spans="15:15" hidden="1">
       <c r="O339" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="340" spans="15:15" hidden="1">
       <c r="O340" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="341" spans="15:15" hidden="1">
       <c r="O341" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="342" spans="15:15" hidden="1">
       <c r="O342" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="343" spans="15:15" hidden="1">
       <c r="O343" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="344" spans="15:15" hidden="1">
       <c r="O344" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="345" spans="15:15" hidden="1">
       <c r="O345" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="346" spans="15:15" hidden="1">
       <c r="O346" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="347" spans="15:15" hidden="1">
       <c r="O347" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="348" spans="15:15" hidden="1">
       <c r="O348" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="349" spans="15:15" hidden="1">
       <c r="O349" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="350" spans="15:15" hidden="1">
       <c r="O350" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="351" spans="15:15" hidden="1">
       <c r="O351" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="352" spans="15:15" hidden="1">
       <c r="O352" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="353" spans="15:15" hidden="1">
       <c r="O353" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="354" spans="15:15" hidden="1">
       <c r="O354" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="355" spans="15:15" hidden="1">
       <c r="O355" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="356" spans="15:15" hidden="1">
       <c r="O356" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="357" spans="15:15" hidden="1">
       <c r="O357" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="358" spans="15:15" hidden="1">
       <c r="O358" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="359" spans="15:15" hidden="1">
       <c r="O359" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="360" spans="15:15" hidden="1">
       <c r="O360" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="361" spans="15:15" hidden="1">
       <c r="O361" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="362" spans="15:15" hidden="1">
       <c r="O362" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="363" spans="15:15" hidden="1">
       <c r="O363" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="364" spans="15:15" hidden="1">
       <c r="O364" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="365" spans="15:15" hidden="1">
       <c r="O365" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="366" spans="15:15" hidden="1">
       <c r="O366" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="367" spans="15:15" hidden="1">
       <c r="O367" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="368" spans="15:15" hidden="1">
       <c r="O368" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="369" spans="15:15" hidden="1">
       <c r="O369" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="370" spans="15:15" hidden="1">
       <c r="O370" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="371" spans="15:15" hidden="1">
       <c r="O371" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="372" spans="15:15" hidden="1">
       <c r="O372" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="373" spans="15:15" hidden="1">
       <c r="O373" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="374" spans="15:15" hidden="1">
       <c r="O374" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="375" spans="15:15" hidden="1">
       <c r="O375" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="376" spans="15:15" hidden="1">
       <c r="O376" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="377" spans="15:15" hidden="1">
       <c r="O377" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="378" spans="15:15" hidden="1">
       <c r="O378" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="379" spans="15:15" hidden="1">
       <c r="O379" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="380" spans="15:15" hidden="1">
       <c r="O380" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="381" spans="15:15" hidden="1">
       <c r="O381" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="382" spans="15:15" hidden="1">
       <c r="O382" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="383" spans="15:15" hidden="1">
       <c r="O383" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="384" spans="15:15" hidden="1">
       <c r="O384" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="385" spans="15:15" hidden="1">
       <c r="O385" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="386" spans="15:15" hidden="1">
       <c r="O386" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="387" spans="15:15" hidden="1">
       <c r="O387" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="388" spans="15:15" hidden="1">
       <c r="O388" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="389" spans="15:15" hidden="1">
       <c r="O389" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="390" spans="15:15" hidden="1">
       <c r="O390" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="391" spans="15:15" hidden="1">
       <c r="O391" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="392" spans="15:15" hidden="1">
       <c r="O392" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="393" spans="15:15" hidden="1">
       <c r="O393" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="394" spans="15:15" hidden="1">
       <c r="O394" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="395" spans="15:15" hidden="1">
       <c r="O395" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="396" spans="15:15" hidden="1">
       <c r="O396" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="397" spans="15:15" hidden="1">
       <c r="O397" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="398" spans="15:15" hidden="1">
       <c r="O398" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="399" spans="15:15" hidden="1">
       <c r="O399" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="400" spans="15:15" hidden="1">
       <c r="O400" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="401" spans="15:15" hidden="1">
       <c r="O401" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="402" spans="15:15" hidden="1">
       <c r="O402" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="403" spans="15:15" hidden="1">
       <c r="O403" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="404" spans="15:15" hidden="1">
       <c r="O404" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="405" spans="15:15" hidden="1">
       <c r="O405" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="406" spans="15:15" hidden="1">
       <c r="O406" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="407" spans="15:15" hidden="1">
       <c r="O407" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="408" spans="15:15" hidden="1">
       <c r="O408" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="409" spans="15:15" hidden="1">
       <c r="O409" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="410" spans="15:15" hidden="1">
       <c r="O410" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="411" spans="15:15" hidden="1">
       <c r="O411" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="412" spans="15:15" hidden="1">
       <c r="O412" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="413" spans="15:15" hidden="1">
       <c r="O413" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="414" spans="15:15" hidden="1">
       <c r="O414" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="415" spans="15:15" hidden="1">
       <c r="O415" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="416" spans="15:15" hidden="1">
       <c r="O416" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="417" spans="15:15" hidden="1">
       <c r="O417" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="418" spans="15:15" hidden="1">
       <c r="O418" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="419" spans="15:15" hidden="1">
       <c r="O419" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="420" spans="15:15" hidden="1">
       <c r="O420" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="421" spans="15:15" hidden="1">
       <c r="O421" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="422" spans="15:15" hidden="1">
       <c r="O422" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="423" spans="15:15" hidden="1">
       <c r="O423" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="424" spans="15:15" hidden="1">
       <c r="O424" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="425" spans="15:15" hidden="1">
       <c r="O425" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="426" spans="15:15" hidden="1">
       <c r="O426" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="427" spans="15:15" hidden="1">
       <c r="O427" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="428" spans="15:15" hidden="1">
       <c r="O428" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="429" spans="15:15" hidden="1">
       <c r="O429" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="430" spans="15:15" hidden="1">
       <c r="O430" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="431" spans="15:15" hidden="1">
       <c r="O431" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="432" spans="15:15" hidden="1">
       <c r="O432" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="433" spans="15:15" hidden="1">
       <c r="O433" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="434" spans="15:15" hidden="1">
       <c r="O434" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
+++ b/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Users\amano\Documents\01_趣味\無線\アマチュア無線\◇1アマ対策\AmateurRadioOperator\AmateurFirstClassRadioOperatorExam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D546EC-B3BD-4E18-B95E-9D4950C2E4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86300E08-04DF-4BC2-9739-187B359714B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-7240" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="出題傾向" sheetId="1" r:id="rId1"/>
+    <sheet name="LICENSE" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AD$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">出題傾向!$A$1:$AD$215</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -175,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="622">
   <si>
     <t>無線工学の基礎</t>
     <rPh sb="0" eb="4">
@@ -5043,6 +5044,39 @@
       <t>カイセツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    Copyright (C) 2026  Y.AMANO (JS2OUN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    This program is free software: you can redistribute it and/or modify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    it under the terms of the GNU Affero General Public License as</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    published by the Free Software Foundation, either version 3 of the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    License, or any later version.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    This program is distributed in the hope that it will be useful,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    but WITHOUT ANY WARRANTY; without even the implied warranty of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE.  See the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    GNU Affero General Public License for more details.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    You should have received a copy of the GNU Affero General Public License</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    along with this program.  If not, see &lt;https://www.gnu.org/licenses/&gt;.</t>
   </si>
 </sst>
 </file>
@@ -17803,4 +17837,70 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11107E12-4E6B-4758-82B6-13BC49BDFDFC}">
+  <dimension ref="A2:A15"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>621</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
+++ b/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Users\amano\Documents\01_趣味\無線\アマチュア無線\◇1アマ対策\AmateurRadioOperator\AmateurFirstClassRadioOperatorExam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86300E08-04DF-4BC2-9739-187B359714B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668FFFCB-5FEA-4561-A29B-EADFEB2A49F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-7240" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="出題傾向" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="622">
   <si>
     <t>無線工学の基礎</t>
     <rPh sb="0" eb="4">
@@ -5520,6 +5520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF434"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5627,7 +5628,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:32" hidden="1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5749,7 +5750,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:32" hidden="1">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -5800,7 +5801,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="5" spans="1:32">
+    <row r="5" spans="1:32" hidden="1">
       <c r="A5" s="17" t="s">
         <v>0</v>
       </c>
@@ -5855,7 +5856,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:32">
+    <row r="6" spans="1:32" hidden="1">
       <c r="A6" s="17" t="s">
         <v>0</v>
       </c>
@@ -5906,7 +5907,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="7" spans="1:32">
+    <row r="7" spans="1:32" hidden="1">
       <c r="A7" s="17" t="s">
         <v>0</v>
       </c>
@@ -5954,7 +5955,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="8" spans="1:32">
+    <row r="8" spans="1:32" hidden="1">
       <c r="A8" s="17" t="s">
         <v>0</v>
       </c>
@@ -6008,7 +6009,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:32">
+    <row r="9" spans="1:32" hidden="1">
       <c r="A9" s="17" t="s">
         <v>0</v>
       </c>
@@ -6056,7 +6057,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="10" spans="1:32">
+    <row r="10" spans="1:32" hidden="1">
       <c r="A10" s="17" t="s">
         <v>0</v>
       </c>
@@ -6107,7 +6108,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="11" spans="1:32">
+    <row r="11" spans="1:32" hidden="1">
       <c r="A11" s="17" t="s">
         <v>0</v>
       </c>
@@ -6155,7 +6156,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:32" hidden="1">
       <c r="A12" s="17" t="s">
         <v>0</v>
       </c>
@@ -6210,7 +6211,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:32">
+    <row r="13" spans="1:32" hidden="1">
       <c r="A13" s="17" t="s">
         <v>0</v>
       </c>
@@ -6267,7 +6268,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="14" spans="1:32">
+    <row r="14" spans="1:32" hidden="1">
       <c r="A14" s="17" t="s">
         <v>0</v>
       </c>
@@ -6315,7 +6316,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="15" spans="1:32">
+    <row r="15" spans="1:32" hidden="1">
       <c r="A15" s="17" t="s">
         <v>0</v>
       </c>
@@ -6363,7 +6364,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="16" spans="1:32">
+    <row r="16" spans="1:32" hidden="1">
       <c r="A16" s="17" t="s">
         <v>0</v>
       </c>
@@ -6420,7 +6421,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="17" spans="1:32">
+    <row r="17" spans="1:32" hidden="1">
       <c r="A17" s="17" t="s">
         <v>0</v>
       </c>
@@ -6478,7 +6479,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="18" spans="1:32">
+    <row r="18" spans="1:32" hidden="1">
       <c r="A18" s="17" t="s">
         <v>0</v>
       </c>
@@ -6526,7 +6527,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="19" spans="1:32">
+    <row r="19" spans="1:32" hidden="1">
       <c r="A19" s="17" t="s">
         <v>0</v>
       </c>
@@ -6574,7 +6575,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="20" spans="1:32">
+    <row r="20" spans="1:32" hidden="1">
       <c r="A20" s="17" t="s">
         <v>0</v>
       </c>
@@ -6685,7 +6686,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="22" spans="1:32">
+    <row r="22" spans="1:32" hidden="1">
       <c r="A22" s="17" t="s">
         <v>0</v>
       </c>
@@ -6736,7 +6737,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="23" spans="1:32">
+    <row r="23" spans="1:32" hidden="1">
       <c r="A23" s="17" t="s">
         <v>0</v>
       </c>
@@ -6794,7 +6795,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="24" spans="1:32">
+    <row r="24" spans="1:32" hidden="1">
       <c r="A24" s="17" t="s">
         <v>0</v>
       </c>
@@ -6842,7 +6843,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="25" spans="1:32">
+    <row r="25" spans="1:32" hidden="1">
       <c r="A25" s="17" t="s">
         <v>0</v>
       </c>
@@ -6893,7 +6894,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="26" spans="1:32">
+    <row r="26" spans="1:32" hidden="1">
       <c r="A26" s="17" t="s">
         <v>0</v>
       </c>
@@ -6948,7 +6949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:32">
+    <row r="27" spans="1:32" hidden="1">
       <c r="A27" s="17" t="s">
         <v>0</v>
       </c>
@@ -7002,7 +7003,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="1:32">
+    <row r="28" spans="1:32" hidden="1">
       <c r="A28" s="17" t="s">
         <v>0</v>
       </c>
@@ -7050,7 +7051,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:32">
+    <row r="29" spans="1:32" hidden="1">
       <c r="A29" s="17" t="s">
         <v>0</v>
       </c>
@@ -7101,7 +7102,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="30" spans="1:32">
+    <row r="30" spans="1:32" hidden="1">
       <c r="A30" s="17" t="s">
         <v>0</v>
       </c>
@@ -7152,7 +7153,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="31" spans="1:32">
+    <row r="31" spans="1:32" hidden="1">
       <c r="A31" s="17" t="s">
         <v>0</v>
       </c>
@@ -7200,7 +7201,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="32" spans="1:32">
+    <row r="32" spans="1:32" hidden="1">
       <c r="A32" s="17" t="s">
         <v>0</v>
       </c>
@@ -7248,7 +7249,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:29">
+    <row r="33" spans="1:29" hidden="1">
       <c r="A33" s="17" t="s">
         <v>0</v>
       </c>
@@ -7296,7 +7297,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="34" spans="1:29">
+    <row r="34" spans="1:29" hidden="1">
       <c r="A34" s="17" t="s">
         <v>0</v>
       </c>
@@ -7354,7 +7355,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="35" spans="1:29">
+    <row r="35" spans="1:29" hidden="1">
       <c r="A35" s="17" t="s">
         <v>0</v>
       </c>
@@ -7405,7 +7406,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="36" spans="1:29">
+    <row r="36" spans="1:29" hidden="1">
       <c r="A36" s="17" t="s">
         <v>0</v>
       </c>
@@ -7453,7 +7454,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="37" spans="1:29">
+    <row r="37" spans="1:29" hidden="1">
       <c r="A37" s="17" t="s">
         <v>0</v>
       </c>
@@ -7517,7 +7518,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="38" spans="1:29">
+    <row r="38" spans="1:29" hidden="1">
       <c r="A38" s="17" t="s">
         <v>0</v>
       </c>
@@ -7574,7 +7575,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="39" spans="1:29">
+    <row r="39" spans="1:29" hidden="1">
       <c r="A39" s="17" t="s">
         <v>0</v>
       </c>
@@ -7631,7 +7632,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="40" spans="1:29">
+    <row r="40" spans="1:29" hidden="1">
       <c r="A40" s="17" t="s">
         <v>0</v>
       </c>
@@ -7682,7 +7683,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="41" spans="1:29">
+    <row r="41" spans="1:29" hidden="1">
       <c r="A41" s="17" t="s">
         <v>0</v>
       </c>
@@ -7740,7 +7741,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="42" spans="1:29">
+    <row r="42" spans="1:29" hidden="1">
       <c r="A42" s="17" t="s">
         <v>0</v>
       </c>
@@ -7791,7 +7792,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="43" spans="1:29">
+    <row r="43" spans="1:29" hidden="1">
       <c r="A43" s="17" t="s">
         <v>0</v>
       </c>
@@ -7912,7 +7913,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="45" spans="1:29">
+    <row r="45" spans="1:29" hidden="1">
       <c r="A45" s="17" t="s">
         <v>0</v>
       </c>
@@ -7963,7 +7964,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="46" spans="1:29">
+    <row r="46" spans="1:29" hidden="1">
       <c r="A46" s="17" t="s">
         <v>0</v>
       </c>
@@ -8014,7 +8015,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="47" spans="1:29">
+    <row r="47" spans="1:29" hidden="1">
       <c r="A47" s="17" t="s">
         <v>0</v>
       </c>
@@ -8062,7 +8063,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="48" spans="1:29">
+    <row r="48" spans="1:29" hidden="1">
       <c r="A48" s="17" t="s">
         <v>0</v>
       </c>
@@ -8113,7 +8114,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="49" spans="1:28">
+    <row r="49" spans="1:28" hidden="1">
       <c r="A49" s="17" t="s">
         <v>0</v>
       </c>
@@ -8167,7 +8168,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="50" spans="1:28">
+    <row r="50" spans="1:28" hidden="1">
       <c r="A50" s="17" t="s">
         <v>0</v>
       </c>
@@ -8218,7 +8219,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="51" spans="1:28">
+    <row r="51" spans="1:28" hidden="1">
       <c r="A51" s="17" t="s">
         <v>0</v>
       </c>
@@ -8269,7 +8270,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:28">
+    <row r="52" spans="1:28" hidden="1">
       <c r="A52" s="17" t="s">
         <v>0</v>
       </c>
@@ -8320,7 +8321,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="53" spans="1:28">
+    <row r="53" spans="1:28" hidden="1">
       <c r="A53" s="17" t="s">
         <v>0</v>
       </c>
@@ -8371,7 +8372,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="54" spans="1:28">
+    <row r="54" spans="1:28" hidden="1">
       <c r="A54" s="17" t="s">
         <v>0</v>
       </c>
@@ -8419,7 +8420,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="55" spans="1:28">
+    <row r="55" spans="1:28" hidden="1">
       <c r="A55" s="17" t="s">
         <v>0</v>
       </c>
@@ -8480,7 +8481,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="56" spans="1:28">
+    <row r="56" spans="1:28" hidden="1">
       <c r="A56" s="17" t="s">
         <v>0</v>
       </c>
@@ -8531,7 +8532,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="57" spans="1:28">
+    <row r="57" spans="1:28" hidden="1">
       <c r="A57" s="17" t="s">
         <v>0</v>
       </c>
@@ -8579,7 +8580,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="58" spans="1:28">
+    <row r="58" spans="1:28" hidden="1">
       <c r="A58" s="17" t="s">
         <v>0</v>
       </c>
@@ -8627,7 +8628,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:28">
+    <row r="59" spans="1:28" hidden="1">
       <c r="A59" s="17" t="s">
         <v>0</v>
       </c>
@@ -8682,7 +8683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:28">
+    <row r="60" spans="1:28" hidden="1">
       <c r="A60" s="17" t="s">
         <v>0</v>
       </c>
@@ -8733,7 +8734,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="61" spans="1:28">
+    <row r="61" spans="1:28" hidden="1">
       <c r="A61" s="17" t="s">
         <v>0</v>
       </c>
@@ -8784,7 +8785,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="62" spans="1:28">
+    <row r="62" spans="1:28" hidden="1">
       <c r="A62" s="17" t="s">
         <v>0</v>
       </c>
@@ -8832,7 +8833,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="63" spans="1:28">
+    <row r="63" spans="1:28" hidden="1">
       <c r="A63" s="17" t="s">
         <v>0</v>
       </c>
@@ -8880,7 +8881,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="64" spans="1:28">
+    <row r="64" spans="1:28" hidden="1">
       <c r="A64" s="17" t="s">
         <v>0</v>
       </c>
@@ -8928,7 +8929,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="65" spans="1:32">
+    <row r="65" spans="1:32" hidden="1">
       <c r="A65" s="17" t="s">
         <v>0</v>
       </c>
@@ -8982,7 +8983,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="66" spans="1:32">
+    <row r="66" spans="1:32" hidden="1">
       <c r="A66" s="17" t="s">
         <v>0</v>
       </c>
@@ -9112,7 +9113,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="68" spans="1:32">
+    <row r="68" spans="1:32" hidden="1">
       <c r="A68" s="17" t="s">
         <v>0</v>
       </c>
@@ -9169,7 +9170,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="69" spans="1:32">
+    <row r="69" spans="1:32" hidden="1">
       <c r="A69" s="17" t="s">
         <v>0</v>
       </c>
@@ -9220,7 +9221,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="70" spans="1:32">
+    <row r="70" spans="1:32" hidden="1">
       <c r="A70" s="17" t="s">
         <v>0</v>
       </c>
@@ -9268,7 +9269,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:32">
+    <row r="71" spans="1:32" hidden="1">
       <c r="A71" s="17" t="s">
         <v>0</v>
       </c>
@@ -9316,7 +9317,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="72" spans="1:32">
+    <row r="72" spans="1:32" hidden="1">
       <c r="A72" s="17" t="s">
         <v>0</v>
       </c>
@@ -9364,7 +9365,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="73" spans="1:32">
+    <row r="73" spans="1:32" hidden="1">
       <c r="A73" s="17" t="s">
         <v>0</v>
       </c>
@@ -9425,7 +9426,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="74" spans="1:32">
+    <row r="74" spans="1:32" hidden="1">
       <c r="A74" s="17" t="s">
         <v>0</v>
       </c>
@@ -9479,7 +9480,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="75" spans="1:32">
+    <row r="75" spans="1:32" hidden="1">
       <c r="A75" s="17" t="s">
         <v>0</v>
       </c>
@@ -9527,7 +9528,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="76" spans="1:32">
+    <row r="76" spans="1:32" hidden="1">
       <c r="A76" s="17" t="s">
         <v>0</v>
       </c>
@@ -9575,7 +9576,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="77" spans="1:32">
+    <row r="77" spans="1:32" hidden="1">
       <c r="A77" s="17" t="s">
         <v>0</v>
       </c>
@@ -9623,7 +9624,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="78" spans="1:32">
+    <row r="78" spans="1:32" hidden="1">
       <c r="A78" s="17" t="s">
         <v>0</v>
       </c>
@@ -9678,7 +9679,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="1:32">
+    <row r="79" spans="1:32" hidden="1">
       <c r="A79" s="17" t="s">
         <v>0</v>
       </c>
@@ -9801,7 +9802,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="81" spans="1:29">
+    <row r="81" spans="1:29" hidden="1">
       <c r="A81" s="17" t="s">
         <v>7</v>
       </c>
@@ -9852,7 +9853,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="82" spans="1:29">
+    <row r="82" spans="1:29" hidden="1">
       <c r="A82" s="17" t="s">
         <v>7</v>
       </c>
@@ -9900,7 +9901,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:29">
+    <row r="83" spans="1:29" hidden="1">
       <c r="A83" s="17" t="s">
         <v>7</v>
       </c>
@@ -9948,7 +9949,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="84" spans="1:29">
+    <row r="84" spans="1:29" hidden="1">
       <c r="A84" s="17" t="s">
         <v>7</v>
       </c>
@@ -10005,7 +10006,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="85" spans="1:29">
+    <row r="85" spans="1:29" hidden="1">
       <c r="A85" s="17" t="s">
         <v>7</v>
       </c>
@@ -10053,7 +10054,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="86" spans="1:29">
+    <row r="86" spans="1:29" hidden="1">
       <c r="A86" s="17" t="s">
         <v>7</v>
       </c>
@@ -10108,7 +10109,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="87" spans="1:29">
+    <row r="87" spans="1:29" hidden="1">
       <c r="A87" s="17" t="s">
         <v>7</v>
       </c>
@@ -10159,7 +10160,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="88" spans="1:29">
+    <row r="88" spans="1:29" hidden="1">
       <c r="A88" s="17" t="s">
         <v>7</v>
       </c>
@@ -10210,7 +10211,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="89" spans="1:29">
+    <row r="89" spans="1:29" hidden="1">
       <c r="A89" s="17" t="s">
         <v>7</v>
       </c>
@@ -10261,7 +10262,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="90" spans="1:29">
+    <row r="90" spans="1:29" hidden="1">
       <c r="A90" s="17" t="s">
         <v>7</v>
       </c>
@@ -10316,7 +10317,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:29">
+    <row r="91" spans="1:29" hidden="1">
       <c r="A91" s="17" t="s">
         <v>7</v>
       </c>
@@ -10363,7 +10364,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="1:29">
+    <row r="92" spans="1:29" hidden="1">
       <c r="A92" s="17" t="s">
         <v>7</v>
       </c>
@@ -10413,7 +10414,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="93" spans="1:29">
+    <row r="93" spans="1:29" hidden="1">
       <c r="A93" s="17" t="s">
         <v>7</v>
       </c>
@@ -10466,7 +10467,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="94" spans="1:29">
+    <row r="94" spans="1:29" hidden="1">
       <c r="A94" s="17" t="s">
         <v>7</v>
       </c>
@@ -10513,7 +10514,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="95" spans="1:29">
+    <row r="95" spans="1:29" hidden="1">
       <c r="A95" s="17" t="s">
         <v>7</v>
       </c>
@@ -10567,7 +10568,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="96" spans="1:29">
+    <row r="96" spans="1:29" hidden="1">
       <c r="A96" s="17" t="s">
         <v>7</v>
       </c>
@@ -10614,7 +10615,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="97" spans="1:29">
+    <row r="97" spans="1:29" hidden="1">
       <c r="A97" s="17" t="s">
         <v>7</v>
       </c>
@@ -10664,7 +10665,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="98" spans="1:29">
+    <row r="98" spans="1:29" hidden="1">
       <c r="A98" s="17" t="s">
         <v>7</v>
       </c>
@@ -10711,7 +10712,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="99" spans="1:29">
+    <row r="99" spans="1:29" hidden="1">
       <c r="A99" s="17" t="s">
         <v>7</v>
       </c>
@@ -10761,7 +10762,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="100" spans="1:29">
+    <row r="100" spans="1:29" hidden="1">
       <c r="A100" s="17" t="s">
         <v>7</v>
       </c>
@@ -10808,7 +10809,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="101" spans="1:29">
+    <row r="101" spans="1:29" hidden="1">
       <c r="A101" s="17" t="s">
         <v>7</v>
       </c>
@@ -10858,7 +10859,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="102" spans="1:29">
+    <row r="102" spans="1:29" hidden="1">
       <c r="A102" s="17" t="s">
         <v>7</v>
       </c>
@@ -10908,7 +10909,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="103" spans="1:29">
+    <row r="103" spans="1:29" hidden="1">
       <c r="A103" s="17" t="s">
         <v>7</v>
       </c>
@@ -10958,7 +10959,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="104" spans="1:29">
+    <row r="104" spans="1:29" hidden="1">
       <c r="A104" s="17" t="s">
         <v>7</v>
       </c>
@@ -11005,7 +11006,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="105" spans="1:29">
+    <row r="105" spans="1:29" hidden="1">
       <c r="A105" s="17" t="s">
         <v>7</v>
       </c>
@@ -11055,7 +11056,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="106" spans="1:29">
+    <row r="106" spans="1:29" hidden="1">
       <c r="A106" s="17" t="s">
         <v>7</v>
       </c>
@@ -11115,7 +11116,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="107" spans="1:29">
+    <row r="107" spans="1:29" hidden="1">
       <c r="A107" s="17" t="s">
         <v>7</v>
       </c>
@@ -11165,7 +11166,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="108" spans="1:29">
+    <row r="108" spans="1:29" hidden="1">
       <c r="A108" s="17" t="s">
         <v>7</v>
       </c>
@@ -11212,7 +11213,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="109" spans="1:29">
+    <row r="109" spans="1:29" hidden="1">
       <c r="A109" s="17" t="s">
         <v>7</v>
       </c>
@@ -11259,7 +11260,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="110" spans="1:29">
+    <row r="110" spans="1:29" hidden="1">
       <c r="A110" s="17" t="s">
         <v>7</v>
       </c>
@@ -11312,7 +11313,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="111" spans="1:29">
+    <row r="111" spans="1:29" hidden="1">
       <c r="A111" s="17" t="s">
         <v>7</v>
       </c>
@@ -11365,7 +11366,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="112" spans="1:29">
+    <row r="112" spans="1:29" hidden="1">
       <c r="A112" s="17" t="s">
         <v>7</v>
       </c>
@@ -11415,7 +11416,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="113" spans="1:29">
+    <row r="113" spans="1:29" hidden="1">
       <c r="A113" s="17" t="s">
         <v>7</v>
       </c>
@@ -11469,7 +11470,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="114" spans="1:29">
+    <row r="114" spans="1:29" hidden="1">
       <c r="A114" s="17" t="s">
         <v>7</v>
       </c>
@@ -11519,7 +11520,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="115" spans="1:29">
+    <row r="115" spans="1:29" hidden="1">
       <c r="A115" s="17" t="s">
         <v>7</v>
       </c>
@@ -11569,7 +11570,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="116" spans="1:29">
+    <row r="116" spans="1:29" hidden="1">
       <c r="A116" s="17" t="s">
         <v>7</v>
       </c>
@@ -11619,7 +11620,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="117" spans="1:29">
+    <row r="117" spans="1:29" hidden="1">
       <c r="A117" s="17" t="s">
         <v>7</v>
       </c>
@@ -11672,7 +11673,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="118" spans="1:29">
+    <row r="118" spans="1:29" hidden="1">
       <c r="A118" s="17" t="s">
         <v>7</v>
       </c>
@@ -11722,7 +11723,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="119" spans="1:29">
+    <row r="119" spans="1:29" hidden="1">
       <c r="A119" s="17" t="s">
         <v>7</v>
       </c>
@@ -11769,7 +11770,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="120" spans="1:29">
+    <row r="120" spans="1:29" hidden="1">
       <c r="A120" s="17" t="s">
         <v>7</v>
       </c>
@@ -11816,7 +11817,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="121" spans="1:29">
+    <row r="121" spans="1:29" hidden="1">
       <c r="A121" s="17" t="s">
         <v>7</v>
       </c>
@@ -11873,7 +11874,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="122" spans="1:29">
+    <row r="122" spans="1:29" hidden="1">
       <c r="A122" s="17" t="s">
         <v>7</v>
       </c>
@@ -11923,7 +11924,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="123" spans="1:29">
+    <row r="123" spans="1:29" hidden="1">
       <c r="A123" s="17" t="s">
         <v>7</v>
       </c>
@@ -11980,7 +11981,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="124" spans="1:29">
+    <row r="124" spans="1:29" hidden="1">
       <c r="A124" s="17" t="s">
         <v>7</v>
       </c>
@@ -12030,7 +12031,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="125" spans="1:29">
+    <row r="125" spans="1:29" hidden="1">
       <c r="A125" s="17" t="s">
         <v>7</v>
       </c>
@@ -12080,7 +12081,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="126" spans="1:29">
+    <row r="126" spans="1:29" hidden="1">
       <c r="A126" s="17" t="s">
         <v>7</v>
       </c>
@@ -12136,7 +12137,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="127" spans="1:29">
+    <row r="127" spans="1:29" hidden="1">
       <c r="A127" s="17" t="s">
         <v>7</v>
       </c>
@@ -12186,7 +12187,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="128" spans="1:29">
+    <row r="128" spans="1:29" hidden="1">
       <c r="A128" s="17" t="s">
         <v>7</v>
       </c>
@@ -12233,7 +12234,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="129" spans="1:29">
+    <row r="129" spans="1:29" hidden="1">
       <c r="A129" s="17" t="s">
         <v>7</v>
       </c>
@@ -12287,7 +12288,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="130" spans="1:29">
+    <row r="130" spans="1:29" hidden="1">
       <c r="A130" s="17" t="s">
         <v>7</v>
       </c>
@@ -12334,7 +12335,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="131" spans="1:29">
+    <row r="131" spans="1:29" hidden="1">
       <c r="A131" s="17" t="s">
         <v>7</v>
       </c>
@@ -12381,7 +12382,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="132" spans="1:29">
+    <row r="132" spans="1:29" hidden="1">
       <c r="A132" s="17" t="s">
         <v>7</v>
       </c>
@@ -12438,7 +12439,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="133" spans="1:29">
+    <row r="133" spans="1:29" hidden="1">
       <c r="A133" s="17" t="s">
         <v>7</v>
       </c>
@@ -12485,7 +12486,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="134" spans="1:29">
+    <row r="134" spans="1:29" hidden="1">
       <c r="A134" s="17" t="s">
         <v>7</v>
       </c>
@@ -12532,7 +12533,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="135" spans="1:29">
+    <row r="135" spans="1:29" hidden="1">
       <c r="A135" s="17" t="s">
         <v>7</v>
       </c>
@@ -12588,7 +12589,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="136" spans="1:29">
+    <row r="136" spans="1:29" hidden="1">
       <c r="A136" s="17" t="s">
         <v>7</v>
       </c>
@@ -12638,7 +12639,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="137" spans="1:29">
+    <row r="137" spans="1:29" hidden="1">
       <c r="A137" s="17" t="s">
         <v>7</v>
       </c>
@@ -12695,7 +12696,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="138" spans="1:29">
+    <row r="138" spans="1:29" hidden="1">
       <c r="A138" s="17" t="s">
         <v>7</v>
       </c>
@@ -12748,7 +12749,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="139" spans="1:29">
+    <row r="139" spans="1:29" hidden="1">
       <c r="A139" s="17" t="s">
         <v>7</v>
       </c>
@@ -12798,7 +12799,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="140" spans="1:29">
+    <row r="140" spans="1:29" hidden="1">
       <c r="A140" s="17" t="s">
         <v>7</v>
       </c>
@@ -12845,7 +12846,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="141" spans="1:29">
+    <row r="141" spans="1:29" hidden="1">
       <c r="A141" s="17" t="s">
         <v>7</v>
       </c>
@@ -12892,7 +12893,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="142" spans="1:29">
+    <row r="142" spans="1:29" hidden="1">
       <c r="A142" s="17" t="s">
         <v>7</v>
       </c>
@@ -12952,7 +12953,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="143" spans="1:29">
+    <row r="143" spans="1:29" hidden="1">
       <c r="A143" s="17" t="s">
         <v>7</v>
       </c>
@@ -13005,7 +13006,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="144" spans="1:29">
+    <row r="144" spans="1:29" hidden="1">
       <c r="A144" s="17" t="s">
         <v>7</v>
       </c>
@@ -13052,7 +13053,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" spans="1:29">
+    <row r="145" spans="1:29" hidden="1">
       <c r="A145" s="17" t="s">
         <v>7</v>
       </c>
@@ -13102,7 +13103,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="146" spans="1:29">
+    <row r="146" spans="1:29" hidden="1">
       <c r="A146" s="17" t="s">
         <v>7</v>
       </c>
@@ -13152,7 +13153,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="147" spans="1:29">
+    <row r="147" spans="1:29" hidden="1">
       <c r="A147" s="17" t="s">
         <v>7</v>
       </c>
@@ -13209,7 +13210,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="148" spans="1:29">
+    <row r="148" spans="1:29" hidden="1">
       <c r="A148" s="17" t="s">
         <v>7</v>
       </c>
@@ -13262,7 +13263,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="149" spans="1:29">
+    <row r="149" spans="1:29" hidden="1">
       <c r="A149" s="17" t="s">
         <v>7</v>
       </c>
@@ -13315,7 +13316,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="150" spans="1:29">
+    <row r="150" spans="1:29" hidden="1">
       <c r="A150" s="17" t="s">
         <v>7</v>
       </c>
@@ -13365,7 +13366,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="151" spans="1:29">
+    <row r="151" spans="1:29" hidden="1">
       <c r="A151" s="1" t="s">
         <v>31</v>
       </c>
@@ -13422,7 +13423,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="152" spans="1:29">
+    <row r="152" spans="1:29" hidden="1">
       <c r="A152" s="17" t="s">
         <v>31</v>
       </c>
@@ -13469,7 +13470,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="153" spans="1:29">
+    <row r="153" spans="1:29" hidden="1">
       <c r="A153" s="17" t="s">
         <v>31</v>
       </c>
@@ -13516,7 +13517,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="154" spans="1:29">
+    <row r="154" spans="1:29" hidden="1">
       <c r="A154" s="17" t="s">
         <v>31</v>
       </c>
@@ -13563,7 +13564,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="155" spans="1:29">
+    <row r="155" spans="1:29" hidden="1">
       <c r="A155" s="17" t="s">
         <v>31</v>
       </c>
@@ -13613,7 +13614,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="156" spans="1:29">
+    <row r="156" spans="1:29" hidden="1">
       <c r="A156" s="17" t="s">
         <v>31</v>
       </c>
@@ -13660,7 +13661,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="157" spans="1:29">
+    <row r="157" spans="1:29" hidden="1">
       <c r="A157" s="17" t="s">
         <v>31</v>
       </c>
@@ -13707,7 +13708,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="158" spans="1:29">
+    <row r="158" spans="1:29" hidden="1">
       <c r="A158" s="17" t="s">
         <v>31</v>
       </c>
@@ -13757,7 +13758,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="159" spans="1:29">
+    <row r="159" spans="1:29" hidden="1">
       <c r="A159" s="17" t="s">
         <v>31</v>
       </c>
@@ -13804,7 +13805,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="160" spans="1:29">
+    <row r="160" spans="1:29" hidden="1">
       <c r="A160" s="17" t="s">
         <v>31</v>
       </c>
@@ -13851,7 +13852,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="161" spans="1:32">
+    <row r="161" spans="1:32" hidden="1">
       <c r="A161" s="17" t="s">
         <v>31</v>
       </c>
@@ -13908,7 +13909,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="162" spans="1:32">
+    <row r="162" spans="1:32" hidden="1">
       <c r="A162" s="17" t="s">
         <v>31</v>
       </c>
@@ -13955,7 +13956,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="163" spans="1:32">
+    <row r="163" spans="1:32" hidden="1">
       <c r="A163" s="17" t="s">
         <v>31</v>
       </c>
@@ -14002,7 +14003,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="164" spans="1:32">
+    <row r="164" spans="1:32" hidden="1">
       <c r="A164" s="17" t="s">
         <v>31</v>
       </c>
@@ -14052,7 +14053,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="165" spans="1:32">
+    <row r="165" spans="1:32" hidden="1">
       <c r="A165" s="17" t="s">
         <v>31</v>
       </c>
@@ -14099,7 +14100,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="166" spans="1:32">
+    <row r="166" spans="1:32" hidden="1">
       <c r="A166" s="17" t="s">
         <v>31</v>
       </c>
@@ -14221,7 +14222,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="168" spans="1:32">
+    <row r="168" spans="1:32" hidden="1">
       <c r="A168" s="17" t="s">
         <v>31</v>
       </c>
@@ -14268,7 +14269,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="169" spans="1:32">
+    <row r="169" spans="1:32" hidden="1">
       <c r="A169" s="17" t="s">
         <v>31</v>
       </c>
@@ -14318,7 +14319,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="170" spans="1:32">
+    <row r="170" spans="1:32" hidden="1">
       <c r="A170" s="17" t="s">
         <v>31</v>
       </c>
@@ -14371,7 +14372,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="171" spans="1:32">
+    <row r="171" spans="1:32" hidden="1">
       <c r="A171" s="17" t="s">
         <v>31</v>
       </c>
@@ -14418,7 +14419,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="172" spans="1:32">
+    <row r="172" spans="1:32" hidden="1">
       <c r="A172" s="17" t="s">
         <v>31</v>
       </c>
@@ -14468,7 +14469,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="173" spans="1:32">
+    <row r="173" spans="1:32" hidden="1">
       <c r="A173" s="17" t="s">
         <v>31</v>
       </c>
@@ -14515,7 +14516,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="174" spans="1:32">
+    <row r="174" spans="1:32" hidden="1">
       <c r="A174" s="17" t="s">
         <v>31</v>
       </c>
@@ -14572,7 +14573,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="175" spans="1:32">
+    <row r="175" spans="1:32" hidden="1">
       <c r="A175" s="17" t="s">
         <v>31</v>
       </c>
@@ -14622,7 +14623,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="176" spans="1:32">
+    <row r="176" spans="1:32" hidden="1">
       <c r="A176" s="17" t="s">
         <v>31</v>
       </c>
@@ -14669,7 +14670,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="177" spans="1:29">
+    <row r="177" spans="1:32">
       <c r="A177" s="17" t="s">
         <v>31</v>
       </c>
@@ -14738,7 +14739,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="178" spans="1:29">
+    <row r="178" spans="1:32" hidden="1">
       <c r="A178" s="17" t="s">
         <v>31</v>
       </c>
@@ -14788,7 +14789,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="179" spans="1:29">
+    <row r="179" spans="1:32" hidden="1">
       <c r="A179" s="17" t="s">
         <v>31</v>
       </c>
@@ -14848,7 +14849,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="180" spans="1:29">
+    <row r="180" spans="1:32" hidden="1">
       <c r="A180" s="17" t="s">
         <v>31</v>
       </c>
@@ -14898,7 +14899,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="181" spans="1:29">
+    <row r="181" spans="1:32" hidden="1">
       <c r="A181" s="17" t="s">
         <v>31</v>
       </c>
@@ -14954,7 +14955,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="182" spans="1:29">
+    <row r="182" spans="1:32">
       <c r="A182" s="17" t="s">
         <v>31</v>
       </c>
@@ -14969,7 +14970,7 @@
       </c>
       <c r="F182" s="2">
         <f>SUM(K182:K189)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G182" s="18">
         <v>32</v>
@@ -14986,11 +14987,11 @@
       </c>
       <c r="K182" s="2">
         <f t="shared" si="97"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L182" s="2">
         <f t="shared" si="98"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M182" s="2" cm="1">
         <f t="array" ref="M182">MATCH(TRUE,P182:AD182&lt;&gt;"",0)-1</f>
@@ -15019,8 +15020,11 @@
       <c r="AC182" s="1" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="183" spans="1:29">
+      <c r="AF182" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="183" spans="1:32" hidden="1">
       <c r="A183" s="17" t="s">
         <v>31</v>
       </c>
@@ -15070,7 +15074,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="184" spans="1:29">
+    <row r="184" spans="1:32" hidden="1">
       <c r="A184" s="17" t="s">
         <v>31</v>
       </c>
@@ -15123,7 +15127,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="185" spans="1:29">
+    <row r="185" spans="1:32" hidden="1">
       <c r="A185" s="17" t="s">
         <v>31</v>
       </c>
@@ -15170,7 +15174,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="186" spans="1:29">
+    <row r="186" spans="1:32" hidden="1">
       <c r="A186" s="17" t="s">
         <v>31</v>
       </c>
@@ -15223,7 +15227,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="187" spans="1:29">
+    <row r="187" spans="1:32" hidden="1">
       <c r="A187" s="17" t="s">
         <v>31</v>
       </c>
@@ -15270,7 +15274,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="188" spans="1:29">
+    <row r="188" spans="1:32" hidden="1">
       <c r="A188" s="17" t="s">
         <v>31</v>
       </c>
@@ -15317,7 +15321,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="189" spans="1:29">
+    <row r="189" spans="1:32" hidden="1">
       <c r="A189" s="17" t="s">
         <v>31</v>
       </c>
@@ -15367,7 +15371,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="190" spans="1:29">
+    <row r="190" spans="1:32" hidden="1">
       <c r="A190" s="17" t="s">
         <v>31</v>
       </c>
@@ -15414,7 +15418,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="191" spans="1:29">
+    <row r="191" spans="1:32" hidden="1">
       <c r="A191" s="17" t="s">
         <v>31</v>
       </c>
@@ -15461,7 +15465,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="192" spans="1:29">
+    <row r="192" spans="1:32" hidden="1">
       <c r="A192" s="1" t="s">
         <v>169</v>
       </c>
@@ -15518,7 +15522,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="193" spans="1:29">
+    <row r="193" spans="1:29" hidden="1">
       <c r="A193" s="17" t="s">
         <v>169</v>
       </c>
@@ -15568,7 +15572,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="194" spans="1:29">
+    <row r="194" spans="1:29" hidden="1">
       <c r="A194" s="17" t="s">
         <v>169</v>
       </c>
@@ -15615,7 +15619,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="195" spans="1:29">
+    <row r="195" spans="1:29" hidden="1">
       <c r="A195" s="17" t="s">
         <v>169</v>
       </c>
@@ -15668,7 +15672,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="196" spans="1:29">
+    <row r="196" spans="1:29" hidden="1">
       <c r="A196" s="17" t="s">
         <v>169</v>
       </c>
@@ -15715,7 +15719,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="197" spans="1:29">
+    <row r="197" spans="1:29" hidden="1">
       <c r="A197" s="17" t="s">
         <v>169</v>
       </c>
@@ -15762,7 +15766,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="198" spans="1:29">
+    <row r="198" spans="1:29" hidden="1">
       <c r="A198" s="17" t="s">
         <v>169</v>
       </c>
@@ -15809,7 +15813,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="199" spans="1:29">
+    <row r="199" spans="1:29" hidden="1">
       <c r="A199" s="17" t="s">
         <v>169</v>
       </c>
@@ -15856,7 +15860,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="200" spans="1:29">
+    <row r="200" spans="1:29" hidden="1">
       <c r="A200" s="17" t="s">
         <v>169</v>
       </c>
@@ -15909,7 +15913,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="201" spans="1:29">
+    <row r="201" spans="1:29" hidden="1">
       <c r="A201" s="17" t="s">
         <v>169</v>
       </c>
@@ -15956,7 +15960,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="202" spans="1:29">
+    <row r="202" spans="1:29" hidden="1">
       <c r="A202" s="17" t="s">
         <v>169</v>
       </c>
@@ -16003,7 +16007,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="203" spans="1:29">
+    <row r="203" spans="1:29" hidden="1">
       <c r="A203" s="17" t="s">
         <v>169</v>
       </c>
@@ -16053,7 +16057,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="204" spans="1:29">
+    <row r="204" spans="1:29" hidden="1">
       <c r="A204" s="17" t="s">
         <v>169</v>
       </c>
@@ -16100,7 +16104,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="205" spans="1:29">
+    <row r="205" spans="1:29" hidden="1">
       <c r="A205" s="17" t="s">
         <v>169</v>
       </c>
@@ -16147,7 +16151,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="206" spans="1:29">
+    <row r="206" spans="1:29" hidden="1">
       <c r="A206" s="17" t="s">
         <v>169</v>
       </c>
@@ -16194,7 +16198,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="207" spans="1:29">
+    <row r="207" spans="1:29" hidden="1">
       <c r="A207" s="17" t="s">
         <v>169</v>
       </c>
@@ -16248,7 +16252,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="208" spans="1:29">
+    <row r="208" spans="1:29" hidden="1">
       <c r="A208" s="17" t="s">
         <v>169</v>
       </c>
@@ -16351,7 +16355,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="210" spans="1:30">
+    <row r="210" spans="1:30" hidden="1">
       <c r="A210" s="17" t="s">
         <v>169</v>
       </c>
@@ -16404,7 +16408,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="211" spans="1:30">
+    <row r="211" spans="1:30" hidden="1">
       <c r="A211" s="17" t="s">
         <v>169</v>
       </c>
@@ -16457,7 +16461,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="212" spans="1:30">
+    <row r="212" spans="1:30" hidden="1">
       <c r="A212" s="17" t="s">
         <v>169</v>
       </c>
@@ -16504,7 +16508,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="213" spans="1:30">
+    <row r="213" spans="1:30" hidden="1">
       <c r="A213" s="17" t="s">
         <v>169</v>
       </c>
@@ -16555,7 +16559,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="214" spans="1:30">
+    <row r="214" spans="1:30" hidden="1">
       <c r="A214" s="17" t="s">
         <v>169</v>
       </c>
@@ -16608,7 +16612,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="215" spans="1:30">
+    <row r="215" spans="1:30" hidden="1">
       <c r="A215" s="17" t="s">
         <v>169</v>
       </c>
@@ -17832,7 +17836,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD215" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AD215" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="14">
+      <filters>
+        <filter val="★★★★★"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
+++ b/AmateurFirstClassRadioOperatorExam/学習分野と出題傾向.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Users\amano\Documents\01_趣味\無線\アマチュア無線\◇1アマ対策\AmateurRadioOperator\AmateurFirstClassRadioOperatorExam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{668FFFCB-5FEA-4561-A29B-EADFEB2A49F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137701FD-1328-476B-8B61-5D906B41E8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-7240" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -176,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="622">
   <si>
     <t>無線工学の基礎</t>
     <rPh sb="0" eb="4">
@@ -5520,7 +5520,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AF434"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5628,7 +5627,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="2" spans="1:32" hidden="1">
+    <row r="2" spans="1:32">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -5750,7 +5749,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="4" spans="1:32" hidden="1">
+    <row r="4" spans="1:32">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -5801,7 +5800,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="5" spans="1:32" hidden="1">
+    <row r="5" spans="1:32">
       <c r="A5" s="17" t="s">
         <v>0</v>
       </c>
@@ -5856,7 +5855,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:32" hidden="1">
+    <row r="6" spans="1:32">
       <c r="A6" s="17" t="s">
         <v>0</v>
       </c>
@@ -5907,7 +5906,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="7" spans="1:32" hidden="1">
+    <row r="7" spans="1:32">
       <c r="A7" s="17" t="s">
         <v>0</v>
       </c>
@@ -5955,7 +5954,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="8" spans="1:32" hidden="1">
+    <row r="8" spans="1:32">
       <c r="A8" s="17" t="s">
         <v>0</v>
       </c>
@@ -6009,7 +6008,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:32" hidden="1">
+    <row r="9" spans="1:32">
       <c r="A9" s="17" t="s">
         <v>0</v>
       </c>
@@ -6057,7 +6056,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="10" spans="1:32" hidden="1">
+    <row r="10" spans="1:32">
       <c r="A10" s="17" t="s">
         <v>0</v>
       </c>
@@ -6108,7 +6107,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="11" spans="1:32" hidden="1">
+    <row r="11" spans="1:32">
       <c r="A11" s="17" t="s">
         <v>0</v>
       </c>
@@ -6156,7 +6155,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="12" spans="1:32" hidden="1">
+    <row r="12" spans="1:32">
       <c r="A12" s="17" t="s">
         <v>0</v>
       </c>
@@ -6211,7 +6210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:32" hidden="1">
+    <row r="13" spans="1:32">
       <c r="A13" s="17" t="s">
         <v>0</v>
       </c>
@@ -6268,7 +6267,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="14" spans="1:32" hidden="1">
+    <row r="14" spans="1:32">
       <c r="A14" s="17" t="s">
         <v>0</v>
       </c>
@@ -6316,7 +6315,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="15" spans="1:32" hidden="1">
+    <row r="15" spans="1:32">
       <c r="A15" s="17" t="s">
         <v>0</v>
       </c>
@@ -6364,7 +6363,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="16" spans="1:32" hidden="1">
+    <row r="16" spans="1:32">
       <c r="A16" s="17" t="s">
         <v>0</v>
       </c>
@@ -6421,7 +6420,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="17" spans="1:32" hidden="1">
+    <row r="17" spans="1:32">
       <c r="A17" s="17" t="s">
         <v>0</v>
       </c>
@@ -6479,7 +6478,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="18" spans="1:32" hidden="1">
+    <row r="18" spans="1:32">
       <c r="A18" s="17" t="s">
         <v>0</v>
       </c>
@@ -6527,7 +6526,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="19" spans="1:32" hidden="1">
+    <row r="19" spans="1:32">
       <c r="A19" s="17" t="s">
         <v>0</v>
       </c>
@@ -6575,7 +6574,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="20" spans="1:32" hidden="1">
+    <row r="20" spans="1:32">
       <c r="A20" s="17" t="s">
         <v>0</v>
       </c>
@@ -6686,7 +6685,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="22" spans="1:32" hidden="1">
+    <row r="22" spans="1:32">
       <c r="A22" s="17" t="s">
         <v>0</v>
       </c>
@@ -6737,7 +6736,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="23" spans="1:32" hidden="1">
+    <row r="23" spans="1:32">
       <c r="A23" s="17" t="s">
         <v>0</v>
       </c>
@@ -6795,7 +6794,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="24" spans="1:32" hidden="1">
+    <row r="24" spans="1:32">
       <c r="A24" s="17" t="s">
         <v>0</v>
       </c>
@@ -6843,7 +6842,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="25" spans="1:32" hidden="1">
+    <row r="25" spans="1:32">
       <c r="A25" s="17" t="s">
         <v>0</v>
       </c>
@@ -6894,7 +6893,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="26" spans="1:32" hidden="1">
+    <row r="26" spans="1:32">
       <c r="A26" s="17" t="s">
         <v>0</v>
       </c>
@@ -6949,7 +6948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:32" hidden="1">
+    <row r="27" spans="1:32">
       <c r="A27" s="17" t="s">
         <v>0</v>
       </c>
@@ -7003,7 +7002,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="1:32" hidden="1">
+    <row r="28" spans="1:32">
       <c r="A28" s="17" t="s">
         <v>0</v>
       </c>
@@ -7051,7 +7050,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:32" hidden="1">
+    <row r="29" spans="1:32">
       <c r="A29" s="17" t="s">
         <v>0</v>
       </c>
@@ -7102,7 +7101,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="30" spans="1:32" hidden="1">
+    <row r="30" spans="1:32">
       <c r="A30" s="17" t="s">
         <v>0</v>
       </c>
@@ -7153,7 +7152,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="31" spans="1:32" hidden="1">
+    <row r="31" spans="1:32">
       <c r="A31" s="17" t="s">
         <v>0</v>
       </c>
@@ -7201,7 +7200,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="32" spans="1:32" hidden="1">
+    <row r="32" spans="1:32">
       <c r="A32" s="17" t="s">
         <v>0</v>
       </c>
@@ -7249,7 +7248,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:29" hidden="1">
+    <row r="33" spans="1:32">
       <c r="A33" s="17" t="s">
         <v>0</v>
       </c>
@@ -7297,7 +7296,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="34" spans="1:29" hidden="1">
+    <row r="34" spans="1:32">
       <c r="A34" s="17" t="s">
         <v>0</v>
       </c>
@@ -7355,7 +7354,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="35" spans="1:29" hidden="1">
+    <row r="35" spans="1:32">
       <c r="A35" s="17" t="s">
         <v>0</v>
       </c>
@@ -7406,7 +7405,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="36" spans="1:29" hidden="1">
+    <row r="36" spans="1:32">
       <c r="A36" s="17" t="s">
         <v>0</v>
       </c>
@@ -7454,7 +7453,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="37" spans="1:29" hidden="1">
+    <row r="37" spans="1:32">
       <c r="A37" s="17" t="s">
         <v>0</v>
       </c>
@@ -7518,7 +7517,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="38" spans="1:29" hidden="1">
+    <row r="38" spans="1:32">
       <c r="A38" s="17" t="s">
         <v>0</v>
       </c>
@@ -7575,7 +7574,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="39" spans="1:29" hidden="1">
+    <row r="39" spans="1:32">
       <c r="A39" s="17" t="s">
         <v>0</v>
       </c>
@@ -7632,7 +7631,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="40" spans="1:29" hidden="1">
+    <row r="40" spans="1:32">
       <c r="A40" s="17" t="s">
         <v>0</v>
       </c>
@@ -7683,7 +7682,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="41" spans="1:29" hidden="1">
+    <row r="41" spans="1:32">
       <c r="A41" s="17" t="s">
         <v>0</v>
       </c>
@@ -7741,7 +7740,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="42" spans="1:29" hidden="1">
+    <row r="42" spans="1:32">
       <c r="A42" s="17" t="s">
         <v>0</v>
       </c>
@@ -7792,7 +7791,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="43" spans="1:29" hidden="1">
+    <row r="43" spans="1:32">
       <c r="A43" s="17" t="s">
         <v>0</v>
       </c>
@@ -7843,7 +7842,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="44" spans="1:29">
+    <row r="44" spans="1:32">
       <c r="A44" s="17" t="s">
         <v>0</v>
       </c>
@@ -7861,7 +7860,7 @@
       </c>
       <c r="F44" s="2">
         <f>SUM(K44:K53)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G44" s="18">
         <f t="shared" si="7"/>
@@ -7879,11 +7878,11 @@
       </c>
       <c r="K44" s="2">
         <f t="shared" si="21"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L44" s="2">
         <f t="shared" si="22"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M44" s="2" cm="1">
         <f t="array" ref="M44">MATCH(TRUE,P44:AD44&lt;&gt;"",0)-1</f>
@@ -7912,8 +7911,11 @@
       <c r="AA44" s="1" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="45" spans="1:29" hidden="1">
+      <c r="AF44" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="45" spans="1:32">
       <c r="A45" s="17" t="s">
         <v>0</v>
       </c>
@@ -7964,7 +7966,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="46" spans="1:29" hidden="1">
+    <row r="46" spans="1:32">
       <c r="A46" s="17" t="s">
         <v>0</v>
       </c>
@@ -8015,7 +8017,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="47" spans="1:29" hidden="1">
+    <row r="47" spans="1:32">
       <c r="A47" s="17" t="s">
         <v>0</v>
       </c>
@@ -8063,7 +8065,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="48" spans="1:29" hidden="1">
+    <row r="48" spans="1:32">
       <c r="A48" s="17" t="s">
         <v>0</v>
       </c>
@@ -8114,7 +8116,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="49" spans="1:28" hidden="1">
+    <row r="49" spans="1:28">
       <c r="A49" s="17" t="s">
         <v>0</v>
       </c>
@@ -8168,7 +8170,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="50" spans="1:28" hidden="1">
+    <row r="50" spans="1:28">
       <c r="A50" s="17" t="s">
         <v>0</v>
       </c>
@@ -8219,7 +8221,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="51" spans="1:28" hidden="1">
+    <row r="51" spans="1:28">
       <c r="A51" s="17" t="s">
         <v>0</v>
       </c>
@@ -8270,7 +8272,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:28" hidden="1">
+    <row r="52" spans="1:28">
       <c r="A52" s="17" t="s">
         <v>0</v>
       </c>
@@ -8321,7 +8323,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="53" spans="1:28" hidden="1">
+    <row r="53" spans="1:28">
       <c r="A53" s="17" t="s">
         <v>0</v>
       </c>
@@ -8372,7 +8374,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="54" spans="1:28" hidden="1">
+    <row r="54" spans="1:28">
       <c r="A54" s="17" t="s">
         <v>0</v>
       </c>
@@ -8420,7 +8422,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="55" spans="1:28" hidden="1">
+    <row r="55" spans="1:28">
       <c r="A55" s="17" t="s">
         <v>0</v>
       </c>
@@ -8481,7 +8483,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="56" spans="1:28" hidden="1">
+    <row r="56" spans="1:28">
       <c r="A56" s="17" t="s">
         <v>0</v>
       </c>
@@ -8532,7 +8534,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="57" spans="1:28" hidden="1">
+    <row r="57" spans="1:28">
       <c r="A57" s="17" t="s">
         <v>0</v>
       </c>
@@ -8580,7 +8582,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="58" spans="1:28" hidden="1">
+    <row r="58" spans="1:28">
       <c r="A58" s="17" t="s">
         <v>0</v>
       </c>
@@ -8628,7 +8630,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:28" hidden="1">
+    <row r="59" spans="1:28">
       <c r="A59" s="17" t="s">
         <v>0</v>
       </c>
@@ -8683,7 +8685,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="1:28" hidden="1">
+    <row r="60" spans="1:28">
       <c r="A60" s="17" t="s">
         <v>0</v>
       </c>
@@ -8734,7 +8736,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="61" spans="1:28" hidden="1">
+    <row r="61" spans="1:28">
       <c r="A61" s="17" t="s">
         <v>0</v>
       </c>
@@ -8785,7 +8787,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="62" spans="1:28" hidden="1">
+    <row r="62" spans="1:28">
       <c r="A62" s="17" t="s">
         <v>0</v>
       </c>
@@ -8833,7 +8835,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="63" spans="1:28" hidden="1">
+    <row r="63" spans="1:28">
       <c r="A63" s="17" t="s">
         <v>0</v>
       </c>
@@ -8881,7 +8883,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="64" spans="1:28" hidden="1">
+    <row r="64" spans="1:28">
       <c r="A64" s="17" t="s">
         <v>0</v>
       </c>
@@ -8929,7 +8931,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="65" spans="1:32" hidden="1">
+    <row r="65" spans="1:32">
       <c r="A65" s="17" t="s">
         <v>0</v>
       </c>
@@ -8983,7 +8985,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="66" spans="1:32" hidden="1">
+    <row r="66" spans="1:32">
       <c r="A66" s="17" t="s">
         <v>0</v>
       </c>
@@ -9113,7 +9115,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="68" spans="1:32" hidden="1">
+    <row r="68" spans="1:32">
       <c r="A68" s="17" t="s">
         <v>0</v>
       </c>
@@ -9170,7 +9172,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="69" spans="1:32" hidden="1">
+    <row r="69" spans="1:32">
       <c r="A69" s="17" t="s">
         <v>0</v>
       </c>
@@ -9221,7 +9223,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="70" spans="1:32" hidden="1">
+    <row r="70" spans="1:32">
       <c r="A70" s="17" t="s">
         <v>0</v>
       </c>
@@ -9269,7 +9271,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="71" spans="1:32" hidden="1">
+    <row r="71" spans="1:32">
       <c r="A71" s="17" t="s">
         <v>0</v>
       </c>
@@ -9317,7 +9319,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="72" spans="1:32" hidden="1">
+    <row r="72" spans="1:32">
       <c r="A72" s="17" t="s">
         <v>0</v>
       </c>
@@ -9365,7 +9367,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="73" spans="1:32" hidden="1">
+    <row r="73" spans="1:32">
       <c r="A73" s="17" t="s">
         <v>0</v>
       </c>
@@ -9426,7 +9428,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="74" spans="1:32" hidden="1">
+    <row r="74" spans="1:32">
       <c r="A74" s="17" t="s">
         <v>0</v>
       </c>
@@ -9480,7 +9482,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="75" spans="1:32" hidden="1">
+    <row r="75" spans="1:32">
       <c r="A75" s="17" t="s">
         <v>0</v>
       </c>
@@ -9528,7 +9530,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="76" spans="1:32" hidden="1">
+    <row r="76" spans="1:32">
       <c r="A76" s="17" t="s">
         <v>0</v>
       </c>
@@ -9576,7 +9578,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="77" spans="1:32" hidden="1">
+    <row r="77" spans="1:32">
       <c r="A77" s="17" t="s">
         <v>0</v>
       </c>
@@ -9624,7 +9626,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="78" spans="1:32" hidden="1">
+    <row r="78" spans="1:32">
       <c r="A78" s="17" t="s">
         <v>0</v>
       </c>
@@ -9679,7 +9681,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="1:32" hidden="1">
+    <row r="79" spans="1:32">
       <c r="A79" s="17" t="s">
         <v>0</v>
       </c>
@@ -9802,7 +9804,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="81" spans="1:29" hidden="1">
+    <row r="81" spans="1:29">
       <c r="A81" s="17" t="s">
         <v>7</v>
       </c>
@@ -9853,7 +9855,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="82" spans="1:29" hidden="1">
+    <row r="82" spans="1:29">
       <c r="A82" s="17" t="s">
         <v>7</v>
       </c>
@@ -9901,7 +9903,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:29" hidden="1">
+    <row r="83" spans="1:29">
       <c r="A83" s="17" t="s">
         <v>7</v>
       </c>
@@ -9949,7 +9951,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="84" spans="1:29" hidden="1">
+    <row r="84" spans="1:29">
       <c r="A84" s="17" t="s">
         <v>7</v>
       </c>
@@ -10006,7 +10008,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="85" spans="1:29" hidden="1">
+    <row r="85" spans="1:29">
       <c r="A85" s="17" t="s">
         <v>7</v>
       </c>
@@ -10054,7 +10056,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="86" spans="1:29" hidden="1">
+    <row r="86" spans="1:29">
       <c r="A86" s="17" t="s">
         <v>7</v>
       </c>
@@ -10109,7 +10111,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="87" spans="1:29" hidden="1">
+    <row r="87" spans="1:29">
       <c r="A87" s="17" t="s">
         <v>7</v>
       </c>
@@ -10160,7 +10162,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="88" spans="1:29" hidden="1">
+    <row r="88" spans="1:29">
       <c r="A88" s="17" t="s">
         <v>7</v>
       </c>
@@ -10211,7 +10213,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="89" spans="1:29" hidden="1">
+    <row r="89" spans="1:29">
       <c r="A89" s="17" t="s">
         <v>7</v>
       </c>
@@ -10262,7 +10264,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="90" spans="1:29" hidden="1">
+    <row r="90" spans="1:29">
       <c r="A90" s="17" t="s">
         <v>7</v>
       </c>
@@ -10317,7 +10319,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:29" hidden="1">
+    <row r="91" spans="1:29">
       <c r="A91" s="17" t="s">
         <v>7</v>
       </c>
@@ -10364,7 +10366,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="1:29" hidden="1">
+    <row r="92" spans="1:29">
       <c r="A92" s="17" t="s">
         <v>7</v>
       </c>
@@ -10414,7 +10416,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="93" spans="1:29" hidden="1">
+    <row r="93" spans="1:29">
       <c r="A93" s="17" t="s">
         <v>7</v>
       </c>
@@ -10467,7 +10469,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="94" spans="1:29" hidden="1">
+    <row r="94" spans="1:29">
       <c r="A94" s="17" t="s">
         <v>7</v>
       </c>
@@ -10514,7 +10516,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="95" spans="1:29" hidden="1">
+    <row r="95" spans="1:29">
       <c r="A95" s="17" t="s">
         <v>7</v>
       </c>
@@ -10568,7 +10570,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="96" spans="1:29" hidden="1">
+    <row r="96" spans="1:29">
       <c r="A96" s="17" t="s">
         <v>7</v>
       </c>
@@ -10615,7 +10617,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="97" spans="1:29" hidden="1">
+    <row r="97" spans="1:29">
       <c r="A97" s="17" t="s">
         <v>7</v>
       </c>
@@ -10665,7 +10667,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="98" spans="1:29" hidden="1">
+    <row r="98" spans="1:29">
       <c r="A98" s="17" t="s">
         <v>7</v>
       </c>
@@ -10712,7 +10714,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="99" spans="1:29" hidden="1">
+    <row r="99" spans="1:29">
       <c r="A99" s="17" t="s">
         <v>7</v>
       </c>
@@ -10762,7 +10764,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="100" spans="1:29" hidden="1">
+    <row r="100" spans="1:29">
       <c r="A100" s="17" t="s">
         <v>7</v>
       </c>
@@ -10809,7 +10811,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="101" spans="1:29" hidden="1">
+    <row r="101" spans="1:29">
       <c r="A101" s="17" t="s">
         <v>7</v>
       </c>
@@ -10859,7 +10861,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="102" spans="1:29" hidden="1">
+    <row r="102" spans="1:29">
       <c r="A102" s="17" t="s">
         <v>7</v>
       </c>
@@ -10909,7 +10911,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="103" spans="1:29" hidden="1">
+    <row r="103" spans="1:29">
       <c r="A103" s="17" t="s">
         <v>7</v>
       </c>
@@ -10959,7 +10961,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="104" spans="1:29" hidden="1">
+    <row r="104" spans="1:29">
       <c r="A104" s="17" t="s">
         <v>7</v>
       </c>
@@ -11006,7 +11008,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="105" spans="1:29" hidden="1">
+    <row r="105" spans="1:29">
       <c r="A105" s="17" t="s">
         <v>7</v>
       </c>
@@ -11056,7 +11058,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="106" spans="1:29" hidden="1">
+    <row r="106" spans="1:29">
       <c r="A106" s="17" t="s">
         <v>7</v>
       </c>
@@ -11116,7 +11118,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="107" spans="1:29" hidden="1">
+    <row r="107" spans="1:29">
       <c r="A107" s="17" t="s">
         <v>7</v>
       </c>
@@ -11166,7 +11168,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="108" spans="1:29" hidden="1">
+    <row r="108" spans="1:29">
       <c r="A108" s="17" t="s">
         <v>7</v>
       </c>
@@ -11213,7 +11215,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="109" spans="1:29" hidden="1">
+    <row r="109" spans="1:29">
       <c r="A109" s="17" t="s">
         <v>7</v>
       </c>
@@ -11260,7 +11262,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="110" spans="1:29" hidden="1">
+    <row r="110" spans="1:29">
       <c r="A110" s="17" t="s">
         <v>7</v>
       </c>
@@ -11313,7 +11315,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="111" spans="1:29" hidden="1">
+    <row r="111" spans="1:29">
       <c r="A111" s="17" t="s">
         <v>7</v>
       </c>
@@ -11366,7 +11368,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="112" spans="1:29" hidden="1">
+    <row r="112" spans="1:29">
       <c r="A112" s="17" t="s">
         <v>7</v>
       </c>
@@ -11416,7 +11418,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="113" spans="1:29" hidden="1">
+    <row r="113" spans="1:29">
       <c r="A113" s="17" t="s">
         <v>7</v>
       </c>
@@ -11470,7 +11472,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="114" spans="1:29" hidden="1">
+    <row r="114" spans="1:29">
       <c r="A114" s="17" t="s">
         <v>7</v>
       </c>
@@ -11520,7 +11522,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="115" spans="1:29" hidden="1">
+    <row r="115" spans="1:29">
       <c r="A115" s="17" t="s">
         <v>7</v>
       </c>
@@ -11570,7 +11572,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="116" spans="1:29" hidden="1">
+    <row r="116" spans="1:29">
       <c r="A116" s="17" t="s">
         <v>7</v>
       </c>
@@ -11620,7 +11622,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="117" spans="1:29" hidden="1">
+    <row r="117" spans="1:29">
       <c r="A117" s="17" t="s">
         <v>7</v>
       </c>
@@ -11673,7 +11675,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="118" spans="1:29" hidden="1">
+    <row r="118" spans="1:29">
       <c r="A118" s="17" t="s">
         <v>7</v>
       </c>
@@ -11723,7 +11725,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="119" spans="1:29" hidden="1">
+    <row r="119" spans="1:29">
       <c r="A119" s="17" t="s">
         <v>7</v>
       </c>
@@ -11770,7 +11772,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="120" spans="1:29" hidden="1">
+    <row r="120" spans="1:29">
       <c r="A120" s="17" t="s">
         <v>7</v>
       </c>
@@ -11817,7 +11819,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="121" spans="1:29" hidden="1">
+    <row r="121" spans="1:29">
       <c r="A121" s="17" t="s">
         <v>7</v>
       </c>
@@ -11874,7 +11876,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="122" spans="1:29" hidden="1">
+    <row r="122" spans="1:29">
       <c r="A122" s="17" t="s">
         <v>7</v>
       </c>
@@ -11924,7 +11926,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="123" spans="1:29" hidden="1">
+    <row r="123" spans="1:29">
       <c r="A123" s="17" t="s">
         <v>7</v>
       </c>
@@ -11981,7 +11983,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="124" spans="1:29" hidden="1">
+    <row r="124" spans="1:29">
       <c r="A124" s="17" t="s">
         <v>7</v>
       </c>
@@ -12031,7 +12033,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="125" spans="1:29" hidden="1">
+    <row r="125" spans="1:29">
       <c r="A125" s="17" t="s">
         <v>7</v>
       </c>
@@ -12081,7 +12083,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="126" spans="1:29" hidden="1">
+    <row r="126" spans="1:29">
       <c r="A126" s="17" t="s">
         <v>7</v>
       </c>
@@ -12137,7 +12139,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="127" spans="1:29" hidden="1">
+    <row r="127" spans="1:29">
       <c r="A127" s="17" t="s">
         <v>7</v>
       </c>
@@ -12187,7 +12189,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="128" spans="1:29" hidden="1">
+    <row r="128" spans="1:29">
       <c r="A128" s="17" t="s">
         <v>7</v>
       </c>
@@ -12234,7 +12236,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="129" spans="1:29" hidden="1">
+    <row r="129" spans="1:29">
       <c r="A129" s="17" t="s">
         <v>7</v>
       </c>
@@ -12288,7 +12290,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="130" spans="1:29" hidden="1">
+    <row r="130" spans="1:29">
       <c r="A130" s="17" t="s">
         <v>7</v>
       </c>
@@ -12335,7 +12337,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="131" spans="1:29" hidden="1">
+    <row r="131" spans="1:29">
       <c r="A131" s="17" t="s">
         <v>7</v>
       </c>
@@ -12382,7 +12384,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="132" spans="1:29" hidden="1">
+    <row r="132" spans="1:29">
       <c r="A132" s="17" t="s">
         <v>7</v>
       </c>
@@ -12439,7 +12441,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="133" spans="1:29" hidden="1">
+    <row r="133" spans="1:29">
       <c r="A133" s="17" t="s">
         <v>7</v>
       </c>
@@ -12486,7 +12488,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="134" spans="1:29" hidden="1">
+    <row r="134" spans="1:29">
       <c r="A134" s="17" t="s">
         <v>7</v>
       </c>
@@ -12533,7 +12535,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="135" spans="1:29" hidden="1">
+    <row r="135" spans="1:29">
       <c r="A135" s="17" t="s">
         <v>7</v>
       </c>
@@ -12589,7 +12591,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="136" spans="1:29" hidden="1">
+    <row r="136" spans="1:29">
       <c r="A136" s="17" t="s">
         <v>7</v>
       </c>
@@ -12639,7 +12641,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="137" spans="1:29" hidden="1">
+    <row r="137" spans="1:29">
       <c r="A137" s="17" t="s">
         <v>7</v>
       </c>
@@ -12696,7 +12698,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="138" spans="1:29" hidden="1">
+    <row r="138" spans="1:29">
       <c r="A138" s="17" t="s">
         <v>7</v>
       </c>
@@ -12749,7 +12751,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="139" spans="1:29" hidden="1">
+    <row r="139" spans="1:29">
       <c r="A139" s="17" t="s">
         <v>7</v>
       </c>
@@ -12799,7 +12801,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="140" spans="1:29" hidden="1">
+    <row r="140" spans="1:29">
       <c r="A140" s="17" t="s">
         <v>7</v>
       </c>
@@ -12846,7 +12848,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="141" spans="1:29" hidden="1">
+    <row r="141" spans="1:29">
       <c r="A141" s="17" t="s">
         <v>7</v>
       </c>
@@ -12893,7 +12895,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="142" spans="1:29" hidden="1">
+    <row r="142" spans="1:29">
       <c r="A142" s="17" t="s">
         <v>7</v>
       </c>
@@ -12953,7 +12955,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="143" spans="1:29" hidden="1">
+    <row r="143" spans="1:29">
       <c r="A143" s="17" t="s">
         <v>7</v>
       </c>
@@ -13006,7 +13008,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="144" spans="1:29" hidden="1">
+    <row r="144" spans="1:29">
       <c r="A144" s="17" t="s">
         <v>7</v>
       </c>
@@ -13053,7 +13055,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="145" spans="1:29" hidden="1">
+    <row r="145" spans="1:29">
       <c r="A145" s="17" t="s">
         <v>7</v>
       </c>
@@ -13103,7 +13105,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="146" spans="1:29" hidden="1">
+    <row r="146" spans="1:29">
       <c r="A146" s="17" t="s">
         <v>7</v>
       </c>
@@ -13153,7 +13155,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="147" spans="1:29" hidden="1">
+    <row r="147" spans="1:29">
       <c r="A147" s="17" t="s">
         <v>7</v>
       </c>
@@ -13210,7 +13212,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="148" spans="1:29" hidden="1">
+    <row r="148" spans="1:29">
       <c r="A148" s="17" t="s">
         <v>7</v>
       </c>
@@ -13263,7 +13265,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="149" spans="1:29" hidden="1">
+    <row r="149" spans="1:29">
       <c r="A149" s="17" t="s">
         <v>7</v>
       </c>
@@ -13316,7 +13318,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="150" spans="1:29" hidden="1">
+    <row r="150" spans="1:29">
       <c r="A150" s="17" t="s">
         <v>7</v>
       </c>
@@ -13366,7 +13368,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="151" spans="1:29" hidden="1">
+    <row r="151" spans="1:29">
       <c r="A151" s="1" t="s">
         <v>31</v>
       </c>
@@ -13423,7 +13425,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="152" spans="1:29" hidden="1">
+    <row r="152" spans="1:29">
       <c r="A152" s="17" t="s">
         <v>31</v>
       </c>
@@ -13470,7 +13472,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="153" spans="1:29" hidden="1">
+    <row r="153" spans="1:29">
       <c r="A153" s="17" t="s">
         <v>31</v>
       </c>
@@ -13517,7 +13519,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="154" spans="1:29" hidden="1">
+    <row r="154" spans="1:29">
       <c r="A154" s="17" t="s">
         <v>31</v>
       </c>
@@ -13564,7 +13566,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="155" spans="1:29" hidden="1">
+    <row r="155" spans="1:29">
       <c r="A155" s="17" t="s">
         <v>31</v>
       </c>
@@ -13614,7 +13616,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="156" spans="1:29" hidden="1">
+    <row r="156" spans="1:29">
       <c r="A156" s="17" t="s">
         <v>31</v>
       </c>
@@ -13661,7 +13663,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="157" spans="1:29" hidden="1">
+    <row r="157" spans="1:29">
       <c r="A157" s="17" t="s">
         <v>31</v>
       </c>
@@ -13708,7 +13710,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="158" spans="1:29" hidden="1">
+    <row r="158" spans="1:29">
       <c r="A158" s="17" t="s">
         <v>31</v>
       </c>
@@ -13758,7 +13760,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="159" spans="1:29" hidden="1">
+    <row r="159" spans="1:29">
       <c r="A159" s="17" t="s">
         <v>31</v>
       </c>
@@ -13805,7 +13807,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="160" spans="1:29" hidden="1">
+    <row r="160" spans="1:29">
       <c r="A160" s="17" t="s">
         <v>31</v>
       </c>
@@ -13852,7 +13854,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="161" spans="1:32" hidden="1">
+    <row r="161" spans="1:32">
       <c r="A161" s="17" t="s">
         <v>31</v>
       </c>
@@ -13909,7 +13911,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="162" spans="1:32" hidden="1">
+    <row r="162" spans="1:32">
       <c r="A162" s="17" t="s">
         <v>31</v>
       </c>
@@ -13956,7 +13958,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="163" spans="1:32" hidden="1">
+    <row r="163" spans="1:32">
       <c r="A163" s="17" t="s">
         <v>31</v>
       </c>
@@ -14003,7 +14005,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="164" spans="1:32" hidden="1">
+    <row r="164" spans="1:32">
       <c r="A164" s="17" t="s">
         <v>31</v>
       </c>
@@ -14053,7 +14055,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="165" spans="1:32" hidden="1">
+    <row r="165" spans="1:32">
       <c r="A165" s="17" t="s">
         <v>31</v>
       </c>
@@ -14100,7 +14102,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="166" spans="1:32" hidden="1">
+    <row r="166" spans="1:32">
       <c r="A166" s="17" t="s">
         <v>31</v>
       </c>
@@ -14222,7 +14224,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="168" spans="1:32" hidden="1">
+    <row r="168" spans="1:32">
       <c r="A168" s="17" t="s">
         <v>31</v>
       </c>
@@ -14269,7 +14271,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="169" spans="1:32" hidden="1">
+    <row r="169" spans="1:32">
       <c r="A169" s="17" t="s">
         <v>31</v>
       </c>
@@ -14319,7 +14321,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="170" spans="1:32" hidden="1">
+    <row r="170" spans="1:32">
       <c r="A170" s="17" t="s">
         <v>31</v>
       </c>
@@ -14372,7 +14374,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="171" spans="1:32" hidden="1">
+    <row r="171" spans="1:32">
       <c r="A171" s="17" t="s">
         <v>31</v>
       </c>
@@ -14419,7 +14421,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="172" spans="1:32" hidden="1">
+    <row r="172" spans="1:32">
       <c r="A172" s="17" t="s">
         <v>31</v>
       </c>
@@ -14469,7 +14471,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="173" spans="1:32" hidden="1">
+    <row r="173" spans="1:32">
       <c r="A173" s="17" t="s">
         <v>31</v>
       </c>
@@ -14516,7 +14518,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="174" spans="1:32" hidden="1">
+    <row r="174" spans="1:32">
       <c r="A174" s="17" t="s">
         <v>31</v>
       </c>
@@ -14573,7 +14575,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="175" spans="1:32" hidden="1">
+    <row r="175" spans="1:32">
       <c r="A175" s="17" t="s">
         <v>31</v>
       </c>
@@ -14623,7 +14625,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="176" spans="1:32" hidden="1">
+    <row r="176" spans="1:32">
       <c r="A176" s="17" t="s">
         <v>31</v>
       </c>
@@ -14739,7 +14741,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="178" spans="1:32" hidden="1">
+    <row r="178" spans="1:32">
       <c r="A178" s="17" t="s">
         <v>31</v>
       </c>
@@ -14789,7 +14791,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="179" spans="1:32" hidden="1">
+    <row r="179" spans="1:32">
       <c r="A179" s="17" t="s">
         <v>31</v>
       </c>
@@ -14849,7 +14851,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="180" spans="1:32" hidden="1">
+    <row r="180" spans="1:32">
       <c r="A180" s="17" t="s">
         <v>31</v>
       </c>
@@ -14899,7 +14901,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="181" spans="1:32" hidden="1">
+    <row r="181" spans="1:32">
       <c r="A181" s="17" t="s">
         <v>31</v>
       </c>
@@ -15024,7 +15026,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="183" spans="1:32" hidden="1">
+    <row r="183" spans="1:32">
       <c r="A183" s="17" t="s">
         <v>31</v>
       </c>
@@ -15074,7 +15076,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="184" spans="1:32" hidden="1">
+    <row r="184" spans="1:32">
       <c r="A184" s="17" t="s">
         <v>31</v>
       </c>
@@ -15127,7 +15129,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="185" spans="1:32" hidden="1">
+    <row r="185" spans="1:32">
       <c r="A185" s="17" t="s">
         <v>31</v>
       </c>
@@ -15174,7 +15176,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="186" spans="1:32" hidden="1">
+    <row r="186" spans="1:32">
       <c r="A186" s="17" t="s">
         <v>31</v>
       </c>
@@ -15227,7 +15229,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="187" spans="1:32" hidden="1">
+    <row r="187" spans="1:32">
       <c r="A187" s="17" t="s">
         <v>31</v>
       </c>
@@ -15274,7 +15276,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="188" spans="1:32" hidden="1">
+    <row r="188" spans="1:32">
       <c r="A188" s="17" t="s">
         <v>31</v>
       </c>
@@ -15321,7 +15323,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="189" spans="1:32" hidden="1">
+    <row r="189" spans="1:32">
       <c r="A189" s="17" t="s">
         <v>31</v>
       </c>
@@ -15371,7 +15373,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="190" spans="1:32" hidden="1">
+    <row r="190" spans="1:32">
       <c r="A190" s="17" t="s">
         <v>31</v>
       </c>
@@ -15418,7 +15420,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="191" spans="1:32" hidden="1">
+    <row r="191" spans="1:32">
       <c r="A191" s="17" t="s">
         <v>31</v>
       </c>
@@ -15465,7 +15467,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="192" spans="1:32" hidden="1">
+    <row r="192" spans="1:32">
       <c r="A192" s="1" t="s">
         <v>169</v>
       </c>
@@ -15522,7 +15524,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="193" spans="1:29" hidden="1">
+    <row r="193" spans="1:29">
       <c r="A193" s="17" t="s">
         <v>169</v>
       </c>
@@ -15572,7 +15574,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="194" spans="1:29" hidden="1">
+    <row r="194" spans="1:29">
       <c r="A194" s="17" t="s">
         <v>169</v>
       </c>
@@ -15619,7 +15621,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="195" spans="1:29" hidden="1">
+    <row r="195" spans="1:29">
       <c r="A195" s="17" t="s">
         <v>169</v>
       </c>
@@ -15672,7 +15674,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="196" spans="1:29" hidden="1">
+    <row r="196" spans="1:29">
       <c r="A196" s="17" t="s">
         <v>169</v>
       </c>
@@ -15719,7 +15721,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="197" spans="1:29" hidden="1">
+    <row r="197" spans="1:29">
       <c r="A197" s="17" t="s">
         <v>169</v>
       </c>
@@ -15766,7 +15768,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="198" spans="1:29" hidden="1">
+    <row r="198" spans="1:29">
       <c r="A198" s="17" t="s">
         <v>169</v>
       </c>
@@ -15813,7 +15815,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="199" spans="1:29" hidden="1">
+    <row r="199" spans="1:29">
       <c r="A199" s="17" t="s">
         <v>169</v>
       </c>
@@ -15860,7 +15862,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="200" spans="1:29" hidden="1">
+    <row r="200" spans="1:29">
       <c r="A200" s="17" t="s">
         <v>169</v>
       </c>
@@ -15913,7 +15915,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="201" spans="1:29" hidden="1">
+    <row r="201" spans="1:29">
       <c r="A201" s="17" t="s">
         <v>169</v>
       </c>
@@ -15960,7 +15962,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="202" spans="1:29" hidden="1">
+    <row r="202" spans="1:29">
       <c r="A202" s="17" t="s">
         <v>169</v>
       </c>
@@ -16007,7 +16009,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="203" spans="1:29" hidden="1">
+    <row r="203" spans="1:29">
       <c r="A203" s="17" t="s">
         <v>169</v>
       </c>
@@ -16057,7 +16059,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="204" spans="1:29" hidden="1">
+    <row r="204" spans="1:29">
       <c r="A204" s="17" t="s">
         <v>169</v>
       </c>
@@ -16104,7 +16106,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="205" spans="1:29" hidden="1">
+    <row r="205" spans="1:29">
       <c r="A205" s="17" t="s">
         <v>169</v>
       </c>
@@ -16151,7 +16153,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="206" spans="1:29" hidden="1">
+    <row r="206" spans="1:29">
       <c r="A206" s="17" t="s">
         <v>169</v>
       </c>
@@ -16198,7 +16200,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="207" spans="1:29" hidden="1">
+    <row r="207" spans="1:29">
       <c r="A207" s="17" t="s">
         <v>169</v>
       </c>
@@ -16252,7 +16254,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="208" spans="1:29" hidden="1">
+    <row r="208" spans="1:29">
       <c r="A208" s="17" t="s">
         <v>169</v>
       </c>
@@ -16355,7 +16357,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="210" spans="1:30" hidden="1">
+    <row r="210" spans="1:30">
       <c r="A210" s="17" t="s">
         <v>169</v>
       </c>
@@ -16408,7 +16410,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="211" spans="1:30" hidden="1">
+    <row r="211" spans="1:30">
       <c r="A211" s="17" t="s">
         <v>169</v>
       </c>
@@ -16461,7 +16463,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="212" spans="1:30" hidden="1">
+    <row r="212" spans="1:30">
       <c r="A212" s="17" t="s">
         <v>169</v>
       </c>
@@ -16508,7 +16510,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="213" spans="1:30" hidden="1">
+    <row r="213" spans="1:30">
       <c r="A213" s="17" t="s">
         <v>169</v>
       </c>
@@ -16559,7 +16561,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="214" spans="1:30" hidden="1">
+    <row r="214" spans="1:30">
       <c r="A214" s="17" t="s">
         <v>169</v>
       </c>
@@ -16612,7 +16614,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="215" spans="1:30" hidden="1">
+    <row r="215" spans="1:30">
       <c r="A215" s="17" t="s">
         <v>169</v>
       </c>
@@ -17836,13 +17838,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD215" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="14">
-      <filters>
-        <filter val="★★★★★"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AD215" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
